--- a/output/yearly_surface_area_iteration_1_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_1_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497651136956</v>
+        <v>10.84497658445214</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907256616925</v>
+        <v>37.78907282082383</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.555129421255953</v>
+        <v>3.942698780255191</v>
       </c>
       <c r="C2" t="n">
-        <v>3.621667280966483</v>
+        <v>10.96415836102838</v>
       </c>
       <c r="D2" t="n">
-        <v>25.85236229593126</v>
+        <v>32.76288438612455</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.02765316663493</v>
+        <v>14.03899217072939</v>
       </c>
       <c r="C3" t="n">
-        <v>19.48278319077795</v>
+        <v>27.45948328778329</v>
       </c>
       <c r="D3" t="n">
-        <v>76.11980824877644</v>
+        <v>71.67739988705962</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>41.67028130675587</v>
+        <v>28.94584931201296</v>
       </c>
       <c r="C4" t="n">
-        <v>74.27903130331367</v>
+        <v>76.30830380799182</v>
       </c>
       <c r="D4" t="n">
-        <v>95.38857044002859</v>
+        <v>115.5919564457237</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>51.76264770641309</v>
+        <v>36.81553890925539</v>
       </c>
       <c r="C5" t="n">
-        <v>135.5302705712722</v>
+        <v>128.9771046454247</v>
       </c>
       <c r="D5" t="n">
-        <v>68.94323253073227</v>
+        <v>97.34028487607128</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>47.0944373727195</v>
+        <v>35.38120551335081</v>
       </c>
       <c r="C6" t="n">
-        <v>144.4229412763398</v>
+        <v>126.1486895094897</v>
       </c>
       <c r="D6" t="n">
-        <v>46.49066253460771</v>
+        <v>60.53849043467533</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>32.45854259780804</v>
+        <v>24.43373686329462</v>
       </c>
       <c r="C7" t="n">
-        <v>100.6693913411722</v>
+        <v>101.6275771005171</v>
       </c>
       <c r="D7" t="n">
-        <v>39.22572952318131</v>
+        <v>43.05847256056086</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>17.19040230136165</v>
+        <v>12.85107744859075</v>
       </c>
       <c r="C8" t="n">
-        <v>50.06913291658733</v>
+        <v>62.25262192629025</v>
       </c>
       <c r="D8" t="n">
-        <v>36.04977569994287</v>
+        <v>36.38356991938679</v>
       </c>
     </row>
     <row r="9">
@@ -878,10 +878,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.320311793491715</v>
+        <v>6.989061906533041</v>
       </c>
       <c r="C9" t="n">
-        <v>28.51093507903161</v>
+        <v>36.83124687252333</v>
       </c>
       <c r="D9" t="n">
         <v>34.05780960802609</v>
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.409429850399925</v>
+        <v>5.267076433284139</v>
       </c>
       <c r="C10" t="n">
-        <v>28.61303684027329</v>
+        <v>29.75186417719959</v>
       </c>
       <c r="D10" t="n">
-        <v>34.87658719336794</v>
+        <v>34.73423377625215</v>
       </c>
     </row>
     <row r="11">
@@ -909,10 +909,10 @@
         <v>4.620104696185489</v>
       </c>
       <c r="C11" t="n">
-        <v>29.14219885286231</v>
+        <v>28.96450251839364</v>
       </c>
       <c r="D11" t="n">
-        <v>36.07235589714055</v>
+        <v>35.89465956267188</v>
       </c>
     </row>
     <row r="12">
@@ -937,10 +937,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>25.49598787928967</v>
+        <v>25.23582473766426</v>
       </c>
       <c r="D13" t="n">
-        <v>32.00006641992479</v>
+        <v>31.73990327829938</v>
       </c>
     </row>
     <row r="14">
@@ -951,7 +951,7 @@
         <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>23.96838845148163</v>
+        <v>23.35381438862312</v>
       </c>
       <c r="D14" t="n">
         <v>30.72870314292517</v>
@@ -968,7 +968,7 @@
         <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>29.02537087605695</v>
       </c>
     </row>
     <row r="16">
@@ -982,7 +982,7 @@
         <v>18.59921025695582</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -1007,10 +1007,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -1035,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.684597115475158</v>
+        <v>7.666426769485772</v>
       </c>
       <c r="C21" t="n">
-        <v>94.13631466457068</v>
+        <v>92.95542458001499</v>
       </c>
       <c r="D21" t="n">
-        <v>8.645171754909553</v>
+        <v>7.666426769485772</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.315403054970485</v>
+        <v>5.751078051477815</v>
       </c>
       <c r="C2" t="n">
-        <v>4.307908926235004</v>
+        <v>9.708503047296707</v>
       </c>
       <c r="D2" t="n">
-        <v>26.03791261203391</v>
+        <v>29.42396044398116</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.81305133003238</v>
+        <v>13.51866588747858</v>
       </c>
       <c r="C3" t="n">
-        <v>16.6357148484622</v>
+        <v>34.93058331710152</v>
       </c>
       <c r="D3" t="n">
-        <v>78.23056581290709</v>
+        <v>79.38902810391832</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>39.48785616021521</v>
+        <v>27.78444177788898</v>
       </c>
       <c r="C4" t="n">
-        <v>60.90370058065513</v>
+        <v>72.40291144049802</v>
       </c>
       <c r="D4" t="n">
-        <v>109.2105963681194</v>
+        <v>123.6197074233499</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>56.94136684631501</v>
+        <v>39.56443248114646</v>
       </c>
       <c r="C5" t="n">
-        <v>136.0702318086079</v>
+        <v>133.051357618049</v>
       </c>
       <c r="D5" t="n">
-        <v>83.76762286485911</v>
+        <v>112.6310053697153</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>57.19760299712343</v>
+        <v>41.78121879733577</v>
       </c>
       <c r="C6" t="n">
-        <v>175.9802394816493</v>
+        <v>162.6166897314417</v>
       </c>
       <c r="D6" t="n">
-        <v>56.07055663264809</v>
+        <v>74.94858323761002</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>43.11835917051991</v>
+        <v>32.39865598784899</v>
       </c>
       <c r="C7" t="n">
-        <v>150.9741437067787</v>
+        <v>137.6793162958684</v>
       </c>
       <c r="D7" t="n">
-        <v>42.81892612072463</v>
+        <v>49.10702016642545</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>25.36836067773758</v>
+        <v>19.10971906316416</v>
       </c>
       <c r="C8" t="n">
-        <v>87.53753404916685</v>
+        <v>95.04790398665493</v>
       </c>
       <c r="D8" t="n">
-        <v>38.38633523605029</v>
+        <v>39.47116644924301</v>
       </c>
     </row>
     <row r="9">
@@ -1189,10 +1189,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>12.53593643552752</v>
+        <v>9.651561680450389</v>
       </c>
       <c r="C9" t="n">
-        <v>44.15312125079604</v>
+        <v>55.69062027110455</v>
       </c>
       <c r="D9" t="n">
         <v>35.27812200440487</v>
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.548257187326225</v>
+        <v>5.978843518863076</v>
       </c>
       <c r="C10" t="n">
-        <v>31.31775176547326</v>
+        <v>36.30012136452581</v>
       </c>
       <c r="D10" t="n">
-        <v>35.73070769606267</v>
+        <v>35.58835427894688</v>
       </c>
     </row>
     <row r="11">
@@ -1220,10 +1220,10 @@
         <v>4.797801030654161</v>
       </c>
       <c r="C11" t="n">
-        <v>31.62994753542373</v>
+        <v>31.98534020436108</v>
       </c>
       <c r="D11" t="n">
-        <v>36.25005223160922</v>
+        <v>36.07235589714055</v>
       </c>
     </row>
     <row r="12">
@@ -1248,10 +1248,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>28.09761929554372</v>
+        <v>27.83745615391831</v>
       </c>
       <c r="D13" t="n">
-        <v>32.5203927031756</v>
+        <v>32.26022956155019</v>
       </c>
     </row>
     <row r="14">
@@ -1262,7 +1262,7 @@
         <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>25.50482360862789</v>
+        <v>25.19753657719863</v>
       </c>
       <c r="D14" t="n">
         <v>31.03599017435442</v>
@@ -1276,10 +1276,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>23.29196428325557</v>
+        <v>22.93362637120549</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>29.38370878810703</v>
       </c>
     </row>
     <row r="16">
@@ -1293,7 +1293,7 @@
         <v>19.83915760741954</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -1321,7 +1321,7 @@
         <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -1346,7 +1346,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.861887404213881</v>
+        <v>7.841989379539037</v>
       </c>
       <c r="C21" t="n">
-        <v>102.2045362547805</v>
+        <v>100.9656132615651</v>
       </c>
       <c r="D21" t="n">
-        <v>9.827359255267352</v>
+        <v>8.822238051981415</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9.090983741325465</v>
+        <v>6.118251692866123</v>
       </c>
       <c r="C2" t="n">
-        <v>12.25319309670444</v>
+        <v>11.04957041129785</v>
       </c>
       <c r="D2" t="n">
-        <v>23.34399691158066</v>
+        <v>30.81607868860313</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>23.80738182798515</v>
+        <v>15.76686813020378</v>
       </c>
       <c r="C3" t="n">
-        <v>16.53754007803752</v>
+        <v>36.25103397931348</v>
       </c>
       <c r="D3" t="n">
-        <v>79.4577504432156</v>
+        <v>82.43244598708344</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.5817030291954</v>
+        <v>26.22738991895354</v>
       </c>
       <c r="C4" t="n">
-        <v>51.42099950533519</v>
+        <v>77.98022014832415</v>
       </c>
       <c r="D4" t="n">
-        <v>118.3997548798696</v>
+        <v>130.5881526280937</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>57.48132808365076</v>
+        <v>40.12893741108838</v>
       </c>
       <c r="C5" t="n">
-        <v>125.2219196766807</v>
+        <v>131.5541923690726</v>
       </c>
       <c r="D5" t="n">
-        <v>99.37741136238341</v>
+        <v>127.2099587777805</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>65.04667589257669</v>
+        <v>46.4504108787336</v>
       </c>
       <c r="C6" t="n">
-        <v>191.7186369284299</v>
+        <v>183.5878024418578</v>
       </c>
       <c r="D6" t="n">
-        <v>65.69070238656259</v>
+        <v>87.99011974082464</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>53.41885608347744</v>
+        <v>39.88448223273092</v>
       </c>
       <c r="C7" t="n">
-        <v>193.9727296573805</v>
+        <v>177.144592258886</v>
       </c>
       <c r="D7" t="n">
-        <v>47.90928796724435</v>
+        <v>57.13182590093888</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>34.46425315758427</v>
+        <v>25.45180923259856</v>
       </c>
       <c r="C8" t="n">
-        <v>135.6039016490907</v>
+        <v>131.0142311317368</v>
       </c>
       <c r="D8" t="n">
-        <v>40.3056519978528</v>
+        <v>42.30841731451629</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>17.74999849278232</v>
+        <v>13.42343636016663</v>
       </c>
       <c r="C9" t="n">
-        <v>70.55624400880974</v>
+        <v>81.98280553853837</v>
       </c>
       <c r="D9" t="n">
-        <v>36.83124687252333</v>
+        <v>37.05312185368311</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.683558444063038</v>
+        <v>7.260024272905163</v>
       </c>
       <c r="C10" t="n">
-        <v>40.42837046088366</v>
+        <v>48.25780840225197</v>
       </c>
       <c r="D10" t="n">
-        <v>36.01541453029424</v>
+        <v>35.87306111317846</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.330890034060179</v>
+        <v>5.153193699591506</v>
       </c>
       <c r="C11" t="n">
-        <v>33.7623035490478</v>
+        <v>36.07235589714055</v>
       </c>
       <c r="D11" t="n">
-        <v>36.42774856607789</v>
+        <v>36.60544490054656</v>
       </c>
     </row>
     <row r="12">
@@ -1545,10 +1545,10 @@
         <v>4.122358610132356</v>
       </c>
       <c r="C12" t="n">
-        <v>32.54493639578176</v>
+        <v>32.97886888105885</v>
       </c>
       <c r="D12" t="n">
-        <v>36.23336252063703</v>
+        <v>35.58246379272139</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.121957699504857</v>
+        <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>30.43908757017236</v>
+        <v>29.91876128692155</v>
       </c>
       <c r="D13" t="n">
-        <v>32.780555844801</v>
+        <v>33.04071898642641</v>
       </c>
     </row>
     <row r="14">
@@ -1573,10 +1573,10 @@
         <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>27.3485457972034</v>
+        <v>27.04125876577415</v>
       </c>
       <c r="D14" t="n">
-        <v>31.34327720578367</v>
+        <v>31.03599017435442</v>
       </c>
     </row>
     <row r="15">
@@ -1590,7 +1590,7 @@
         <v>24.72531593145592</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>29.38370878810703</v>
       </c>
     </row>
     <row r="16">
@@ -1601,10 +1601,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>21.49242074137117</v>
+        <v>21.07910495788326</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>26.86552592671396</v>
       </c>
     </row>
     <row r="17">
@@ -1632,7 +1632,7 @@
         <v>18.72683745850791</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -1657,7 +1657,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8.023808867611754</v>
+        <v>8.001782759823191</v>
       </c>
       <c r="C21" t="n">
-        <v>110.3273719296616</v>
+        <v>109.024290102591</v>
       </c>
       <c r="D21" t="n">
-        <v>11.03273719296616</v>
+        <v>10.00222844977899</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.33798325216816</v>
+        <v>5.59890715731956</v>
       </c>
       <c r="C2" t="n">
-        <v>8.429285788663114</v>
+        <v>7.601672473983053</v>
       </c>
       <c r="D2" t="n">
-        <v>19.4376227963826</v>
+        <v>25.44395525096458</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>27.65092409011142</v>
+        <v>18.53048791765854</v>
       </c>
       <c r="C3" t="n">
-        <v>30.90050899116836</v>
+        <v>53.36780520285661</v>
       </c>
       <c r="D3" t="n">
-        <v>86.45270283597412</v>
+        <v>90.60549562493813</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.61852641587127</v>
+        <v>19.27170743436488</v>
       </c>
       <c r="C4" t="n">
-        <v>90.64083854229102</v>
+        <v>108.32996867741</v>
       </c>
       <c r="D4" t="n">
-        <v>113.0011242542164</v>
+        <v>130.9582715125948</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>36.64373306101221</v>
+        <v>26.1635763181775</v>
       </c>
       <c r="C5" t="n">
-        <v>114.5454133929966</v>
+        <v>109.6857622569749</v>
       </c>
       <c r="D5" t="n">
-        <v>65.9489020327795</v>
+        <v>86.76195336281188</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>33.16736444027425</v>
+        <v>24.75476836258333</v>
       </c>
       <c r="C6" t="n">
-        <v>127.7587557444544</v>
+        <v>116.6492987231975</v>
       </c>
       <c r="D6" t="n">
-        <v>31.55729820530948</v>
+        <v>37.59504658642736</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>22.81679839440012</v>
+        <v>16.82813739849458</v>
       </c>
       <c r="C7" t="n">
-        <v>95.33948305481626</v>
+        <v>92.10560611702725</v>
       </c>
       <c r="D7" t="n">
-        <v>28.32636651063322</v>
+        <v>29.70375853969149</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>12.2669375645639</v>
+        <v>9.262789589568655</v>
       </c>
       <c r="C8" t="n">
-        <v>51.98844967838984</v>
+        <v>60.4167537193487</v>
       </c>
       <c r="D8" t="n">
-        <v>27.12078032981814</v>
+        <v>27.28767743954009</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.212499472473814</v>
+        <v>5.214062057254808</v>
       </c>
       <c r="C9" t="n">
-        <v>30.84062238120929</v>
+        <v>36.83124687252333</v>
       </c>
       <c r="D9" t="n">
-        <v>27.40156017323271</v>
+        <v>27.29062268265283</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.843542262126263</v>
+        <v>3.701188845010476</v>
       </c>
       <c r="C10" t="n">
-        <v>26.47773558353648</v>
+        <v>28.18597658892593</v>
       </c>
       <c r="D10" t="n">
-        <v>28.47068342315751</v>
+        <v>28.61303684027329</v>
       </c>
     </row>
     <row r="11">
@@ -1842,10 +1842,10 @@
         <v>3.020837685967435</v>
       </c>
       <c r="C11" t="n">
-        <v>26.12136116689488</v>
+        <v>26.29905750136355</v>
       </c>
       <c r="D11" t="n">
-        <v>28.96450251839364</v>
+        <v>28.43141351498762</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.386628669023996</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>24.73415166079414</v>
+        <v>24.30021917551705</v>
       </c>
       <c r="D12" t="n">
-        <v>26.68684784454105</v>
+        <v>26.90381408717959</v>
       </c>
     </row>
     <row r="13">
@@ -1870,10 +1870,10 @@
         <v>1.560978849752429</v>
       </c>
       <c r="C13" t="n">
-        <v>22.63419332141022</v>
+        <v>22.37403017978481</v>
       </c>
       <c r="D13" t="n">
-        <v>25.75615102091507</v>
+        <v>25.49598787928967</v>
       </c>
     </row>
     <row r="14">
@@ -1887,7 +1887,7 @@
         <v>20.58823110575986</v>
       </c>
       <c r="D14" t="n">
-        <v>23.96838845148163</v>
+        <v>24.58296251434014</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>17.91689560250429</v>
+        <v>17.5585576904542</v>
       </c>
       <c r="D15" t="n">
-        <v>22.93362637120549</v>
+        <v>22.57528845915541</v>
       </c>
     </row>
     <row r="16">
@@ -1929,7 +1929,7 @@
         <v>16.05550195525234</v>
       </c>
       <c r="D17" t="n">
-        <v>17.47216389248049</v>
+        <v>17.9443845382232</v>
       </c>
     </row>
     <row r="18">
@@ -1954,7 +1954,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>16.85071759569225</v>
+        <v>16.24890625298896</v>
       </c>
       <c r="D19" t="n">
         <v>9.027170140549421</v>
@@ -1968,10 +1968,10 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>73.97468951499715</v>
+        <v>73.30219233758808</v>
       </c>
       <c r="D20" t="n">
-        <v>7.397468951499714</v>
+        <v>6.724971774090649</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.231733515931253</v>
+        <v>3.353650157707104</v>
       </c>
       <c r="C2" t="n">
-        <v>3.902447124381071</v>
+        <v>4.246058820867455</v>
       </c>
       <c r="D2" t="n">
-        <v>14.71639808665969</v>
+        <v>17.92769482725101</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>28.8879261974624</v>
+        <v>19.3747909433108</v>
       </c>
       <c r="C3" t="n">
-        <v>32.61856747360027</v>
+        <v>42.14642894331557</v>
       </c>
       <c r="D3" t="n">
-        <v>82.92822857772808</v>
+        <v>91.23381415565609</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.46683854779853</v>
+        <v>26.43159344143688</v>
       </c>
       <c r="C4" t="n">
-        <v>86.60781897324512</v>
+        <v>124.2450807109551</v>
       </c>
       <c r="D4" t="n">
-        <v>128.9034735676062</v>
+        <v>143.2870591825262</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>40.76707341884881</v>
+        <v>28.59340188618836</v>
       </c>
       <c r="C5" t="n">
-        <v>142.3288734231814</v>
+        <v>152.4408747769235</v>
       </c>
       <c r="D5" t="n">
-        <v>84.08669086873932</v>
+        <v>106.3723637551419</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>39.40637110076273</v>
+        <v>29.26295382048468</v>
       </c>
       <c r="C6" t="n">
-        <v>155.0493784271073</v>
+        <v>143.8594180941022</v>
       </c>
       <c r="D6" t="n">
-        <v>39.44662275663685</v>
+        <v>48.26173539306896</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>21.4992929753009</v>
+        <v>15.75017841923158</v>
       </c>
       <c r="C7" t="n">
-        <v>129.654510561355</v>
+        <v>121.6895914368006</v>
       </c>
       <c r="D7" t="n">
-        <v>30.96137734883166</v>
+        <v>33.11729530735765</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.18072369303942</v>
+        <v>7.927612711792993</v>
       </c>
       <c r="C8" t="n">
-        <v>73.1009340582175</v>
+        <v>79.69336989223483</v>
       </c>
       <c r="D8" t="n">
-        <v>28.28906009787184</v>
+        <v>28.03871443328891</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.881249585515139</v>
+        <v>4.437499623195581</v>
       </c>
       <c r="C9" t="n">
-        <v>35.72187196672443</v>
+        <v>41.71249645803847</v>
       </c>
       <c r="D9" t="n">
-        <v>28.39999758845172</v>
+        <v>28.28906009787183</v>
       </c>
     </row>
     <row r="10">
@@ -2139,7 +2139,7 @@
         <v>2.135301256736813</v>
       </c>
       <c r="C10" t="n">
-        <v>29.89421759431538</v>
+        <v>31.03304493124168</v>
       </c>
       <c r="D10" t="n">
         <v>29.89421759431538</v>
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
+        <v>28.96450251839364</v>
+      </c>
+      <c r="D11" t="n">
         <v>29.31989518733098</v>
-      </c>
-      <c r="D11" t="n">
-        <v>29.67528785626833</v>
       </c>
     </row>
     <row r="12">
@@ -2167,10 +2167,10 @@
         <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>20.82875929330033</v>
+        <v>20.39482680802324</v>
       </c>
       <c r="D12" t="n">
-        <v>28.42257778564941</v>
+        <v>28.20561154301086</v>
       </c>
     </row>
     <row r="13">
@@ -2184,7 +2184,7 @@
         <v>16.91060420565131</v>
       </c>
       <c r="D13" t="n">
-        <v>25.23582473766426</v>
+        <v>25.75615102091507</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>15.05706454003333</v>
+        <v>14.74977750860408</v>
       </c>
       <c r="D14" t="n">
-        <v>19.0517959486136</v>
+        <v>18.74450891718435</v>
       </c>
     </row>
     <row r="15">
@@ -2226,7 +2226,7 @@
         <v>13.63942085510094</v>
       </c>
       <c r="D16" t="n">
-        <v>14.87936820556466</v>
+        <v>15.29268398905256</v>
       </c>
     </row>
     <row r="17">
@@ -2251,7 +2251,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>14.44641746799181</v>
+        <v>13.9113649691773</v>
       </c>
       <c r="D18" t="n">
         <v>7.490734983403163</v>
@@ -2265,10 +2265,10 @@
         <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>64.39381366925254</v>
+        <v>63.79200232654924</v>
       </c>
       <c r="D19" t="n">
-        <v>6.018113427032947</v>
+        <v>5.416302084329653</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.062872910800801</v>
+        <v>2.89321048441535</v>
       </c>
       <c r="C2" t="n">
-        <v>9.284388039062087</v>
+        <v>3.646210973572654</v>
       </c>
       <c r="D2" t="n">
-        <v>21.01627310481147</v>
+        <v>14.61724156853076</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>23.27232932917064</v>
+        <v>15.36926030998382</v>
       </c>
       <c r="C3" t="n">
-        <v>23.45886139297754</v>
+        <v>28.8879261974624</v>
       </c>
       <c r="D3" t="n">
-        <v>76.66958696315466</v>
+        <v>84.88190650917923</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>46.86470840992574</v>
+        <v>31.5494442236755</v>
       </c>
       <c r="C4" t="n">
-        <v>83.91488502049611</v>
+        <v>114.6092269937726</v>
       </c>
       <c r="D4" t="n">
-        <v>139.1264124119282</v>
+        <v>154.2502357958504</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>48.67014243803564</v>
+        <v>33.62485887045326</v>
       </c>
       <c r="C5" t="n">
-        <v>150.7473599870978</v>
+        <v>189.1091515305419</v>
       </c>
       <c r="D5" t="n">
-        <v>106.666888066416</v>
+        <v>129.1243668010618</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>46.61141750223008</v>
+        <v>33.52962934314132</v>
       </c>
       <c r="C6" t="n">
-        <v>190.390332284584</v>
+        <v>190.752597187451</v>
       </c>
       <c r="D6" t="n">
-        <v>53.09193409796327</v>
+        <v>65.77120569831082</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>31.9794497181356</v>
+        <v>23.29589127407256</v>
       </c>
       <c r="C7" t="n">
-        <v>174.3898082007694</v>
+        <v>161.6938468894497</v>
       </c>
       <c r="D7" t="n">
-        <v>34.43480072645687</v>
+        <v>38.0279973240002</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>15.0207398749762</v>
+        <v>11.18210635137117</v>
       </c>
       <c r="C8" t="n">
-        <v>116.9948739150924</v>
+        <v>114.8252114887069</v>
       </c>
       <c r="D8" t="n">
-        <v>29.87458264023044</v>
+        <v>30.0414797499524</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.656249434793372</v>
+        <v>5.657812019574366</v>
       </c>
       <c r="C9" t="n">
-        <v>58.90780749792134</v>
+        <v>66.34061936677394</v>
       </c>
       <c r="D9" t="n">
-        <v>29.17656002251095</v>
+        <v>29.28749751309084</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.847068342315751</v>
+        <v>2.704714925199962</v>
       </c>
       <c r="C10" t="n">
-        <v>35.87306111317846</v>
+        <v>38.72012945549421</v>
       </c>
       <c r="D10" t="n">
-        <v>30.46363126277853</v>
+        <v>30.17892442854695</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>32.16303653882975</v>
+        <v>32.69612554223576</v>
       </c>
       <c r="D11" t="n">
-        <v>30.20837685967435</v>
+        <v>29.852984190737</v>
       </c>
     </row>
     <row r="12">
@@ -2478,10 +2478,10 @@
         <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>25.38505038870978</v>
+        <v>24.5171854181556</v>
       </c>
       <c r="D12" t="n">
-        <v>28.8565102709265</v>
+        <v>28.63954402828795</v>
       </c>
     </row>
     <row r="13">
@@ -2495,7 +2495,7 @@
         <v>18.99190933865455</v>
       </c>
       <c r="D13" t="n">
-        <v>26.01631416254048</v>
+        <v>26.53664044579129</v>
       </c>
     </row>
     <row r="14">
@@ -2506,7 +2506,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>16.59349969717959</v>
+        <v>15.97892563432109</v>
       </c>
       <c r="D14" t="n">
         <v>19.35908298004286</v>
@@ -2520,10 +2520,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>15.40853021815369</v>
+        <v>15.76686813020377</v>
       </c>
       <c r="D15" t="n">
-        <v>17.20021977840412</v>
+        <v>17.5585576904542</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
+        <v>14.46605242207675</v>
+      </c>
+      <c r="D16" t="n">
         <v>14.87936820556466</v>
-      </c>
-      <c r="D16" t="n">
-        <v>14.46605242207675</v>
       </c>
     </row>
     <row r="17">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>34.9050578767911</v>
+        <v>34.3032465340878</v>
       </c>
       <c r="D19" t="n">
-        <v>4.212679398923063</v>
+        <v>3.610868056219768</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.023782929080176</v>
+        <v>1.733766445699867</v>
       </c>
       <c r="C2" t="n">
-        <v>4.354051068334604</v>
+        <v>1.746529165855076</v>
       </c>
       <c r="D2" t="n">
-        <v>14.65062099047515</v>
+        <v>10.19741340401162</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.92380889416302</v>
+        <v>14.62804079327748</v>
       </c>
       <c r="C3" t="n">
-        <v>30.45872252425729</v>
+        <v>24.55841882173396</v>
       </c>
       <c r="D3" t="n">
-        <v>77.90658907050565</v>
+        <v>81.7501313326319</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>51.81664383014665</v>
+        <v>34.68907338185679</v>
       </c>
       <c r="C4" t="n">
-        <v>82.74071476621694</v>
+        <v>110.7038346262788</v>
       </c>
       <c r="D4" t="n">
-        <v>147.3073160314169</v>
+        <v>163.350055266514</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>50.6827252317416</v>
+        <v>35.29382996767284</v>
       </c>
       <c r="C5" t="n">
-        <v>175.7819264453914</v>
+        <v>223.715758105242</v>
       </c>
       <c r="D5" t="n">
-        <v>112.5573742918968</v>
+        <v>135.5793579564845</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>38.80259626265094</v>
+        <v>27.77364255314227</v>
       </c>
       <c r="C6" t="n">
-        <v>228.2268888062561</v>
+        <v>225.7312861420607</v>
       </c>
       <c r="D6" t="n">
-        <v>51.96488773348793</v>
+        <v>63.59761628110839</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.941177253203202</v>
+        <v>7.366053024963818</v>
       </c>
       <c r="C7" t="n">
-        <v>172.9525295617521</v>
+        <v>161.8735067193268</v>
       </c>
       <c r="D7" t="n">
-        <v>34.49468733641593</v>
+        <v>37.18958478457343</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.589670517353839</v>
+        <v>3.922082078466008</v>
       </c>
       <c r="C8" t="n">
-        <v>78.94233289848603</v>
+        <v>83.7823490804228</v>
       </c>
       <c r="D8" t="n">
-        <v>31.37665662772806</v>
+        <v>31.54355373745002</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.996874830438012</v>
+        <v>1.885937339858122</v>
       </c>
       <c r="C9" t="n">
-        <v>27.29062268265283</v>
+        <v>29.50937249425062</v>
       </c>
       <c r="D9" t="n">
-        <v>31.8390597964283</v>
+        <v>31.61718481526852</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.281180754042088</v>
+        <v>1.1388273369263</v>
       </c>
       <c r="C10" t="n">
-        <v>25.19655482949439</v>
+        <v>25.62361508084176</v>
       </c>
       <c r="D10" t="n">
-        <v>23.63066724122073</v>
+        <v>23.34596040698915</v>
       </c>
     </row>
     <row r="11">
@@ -2775,10 +2775,10 @@
         <v>0.7107853378746906</v>
       </c>
       <c r="C11" t="n">
-        <v>20.25738212942868</v>
+        <v>19.54659679155399</v>
       </c>
       <c r="D11" t="n">
-        <v>23.10052348092744</v>
+        <v>22.92282714645877</v>
       </c>
     </row>
     <row r="12">
@@ -2792,7 +2792,7 @@
         <v>15.4046032273367</v>
       </c>
       <c r="D12" t="n">
-        <v>21.26269177857742</v>
+        <v>21.47965802121596</v>
       </c>
     </row>
     <row r="13">
@@ -2803,7 +2803,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.52848336452105</v>
+        <v>13.00815708127024</v>
       </c>
       <c r="D13" t="n">
         <v>15.86995163914969</v>
@@ -2817,10 +2817,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>12.90605532002857</v>
+        <v>13.21334235145782</v>
       </c>
       <c r="D14" t="n">
-        <v>14.44249047717483</v>
+        <v>14.74977750860408</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
+        <v>12.18348900970292</v>
+      </c>
+      <c r="D15" t="n">
         <v>12.541826921753</v>
-      </c>
-      <c r="D15" t="n">
-        <v>12.18348900970292</v>
       </c>
     </row>
     <row r="16">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>29.96293993361265</v>
+        <v>29.42788743479814</v>
       </c>
       <c r="D18" t="n">
-        <v>3.21031499288707</v>
+        <v>2.675262494072558</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.794454876913922</v>
+        <v>2.542726553999239</v>
       </c>
       <c r="C2" t="n">
-        <v>5.964117303299373</v>
+        <v>5.388813148610742</v>
       </c>
       <c r="D2" t="n">
-        <v>13.06018970959532</v>
+        <v>14.85384276525424</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.87133429748144</v>
+        <v>10.49979169691964</v>
       </c>
       <c r="C3" t="n">
-        <v>23.61594102565702</v>
+        <v>15.67851083682156</v>
       </c>
       <c r="D3" t="n">
-        <v>72.78186605433729</v>
+        <v>72.8554971321558</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>48.05164138436013</v>
+        <v>31.52391878336508</v>
       </c>
       <c r="C4" t="n">
-        <v>79.34583120493146</v>
+        <v>86.79925977557325</v>
       </c>
       <c r="D4" t="n">
-        <v>151.3148101601524</v>
+        <v>165.9408874580214</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>62.39006660488482</v>
+        <v>42.38695713085605</v>
       </c>
       <c r="C5" t="n">
-        <v>166.2835174068035</v>
+        <v>216.4262814012094</v>
       </c>
       <c r="D5" t="n">
-        <v>133.7140373184156</v>
+        <v>157.1532637573082</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>50.71708640139023</v>
+        <v>35.54221213684728</v>
       </c>
       <c r="C6" t="n">
-        <v>253.7061869745735</v>
+        <v>284.1766904712818</v>
       </c>
       <c r="D6" t="n">
-        <v>69.11209313586272</v>
+        <v>84.08570912103508</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>21.61906619521901</v>
+        <v>15.27108553955913</v>
       </c>
       <c r="C7" t="n">
-        <v>243.1995230437241</v>
+        <v>233.1385725706028</v>
       </c>
       <c r="D7" t="n">
-        <v>39.88448223273092</v>
+        <v>44.43586458961913</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6.258641614573416</v>
+        <v>5.090361846519712</v>
       </c>
       <c r="C8" t="n">
-        <v>139.1921895081128</v>
+        <v>135.3535559845078</v>
       </c>
       <c r="D8" t="n">
-        <v>33.12907627980861</v>
+        <v>33.71321616383547</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.551562283337459</v>
+        <v>2.218749811597791</v>
       </c>
       <c r="C9" t="n">
-        <v>53.13905798776709</v>
+        <v>56.02343274284421</v>
       </c>
       <c r="D9" t="n">
-        <v>32.61562223048752</v>
+        <v>32.50468473990763</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.281180754042088</v>
+        <v>1.1388273369263</v>
       </c>
       <c r="C10" t="n">
-        <v>28.75539025738908</v>
+        <v>29.75186417719959</v>
       </c>
       <c r="D10" t="n">
-        <v>24.76949457814703</v>
+        <v>24.62714116103124</v>
       </c>
     </row>
     <row r="11">
@@ -3086,10 +3086,10 @@
         <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
+        <v>22.7451308119901</v>
+      </c>
+      <c r="D11" t="n">
         <v>23.63361248433346</v>
-      </c>
-      <c r="D11" t="n">
-        <v>24.16670148773948</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.57426565372215</v>
+        <v>17.7912318963607</v>
       </c>
       <c r="D12" t="n">
-        <v>21.47965802121596</v>
+        <v>21.69662426385451</v>
       </c>
     </row>
     <row r="13">
@@ -3114,7 +3114,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>15.60978849752428</v>
+        <v>15.08946221427348</v>
       </c>
       <c r="D13" t="n">
         <v>15.86995163914969</v>
@@ -3131,7 +3131,7 @@
         <v>13.82791641431633</v>
       </c>
       <c r="D14" t="n">
-        <v>14.13520344574558</v>
+        <v>14.44249047717483</v>
       </c>
     </row>
     <row r="15">
@@ -3142,7 +3142,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.61684065790326</v>
+        <v>13.25850274585317</v>
       </c>
       <c r="D15" t="n">
         <v>11.82515109765283</v>
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33.99988649347554</v>
+        <v>33.52766584773283</v>
       </c>
       <c r="D17" t="n">
-        <v>4.722206457427158</v>
+        <v>4.249985811684442</v>
       </c>
     </row>
     <row r="18">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.66839026014283</v>
+        <v>1.644427404613408</v>
       </c>
       <c r="C2" t="n">
-        <v>4.523893421169302</v>
+        <v>3.038509144643878</v>
       </c>
       <c r="D2" t="n">
-        <v>10.8973995171396</v>
+        <v>11.20468654856885</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.37416904850505</v>
+        <v>9.807659565425636</v>
       </c>
       <c r="C3" t="n">
-        <v>23.88101290580366</v>
+        <v>18.36359080793659</v>
       </c>
       <c r="D3" t="n">
-        <v>67.92221491831558</v>
+        <v>69.75808312525712</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>42.72958707963818</v>
+        <v>27.68234001664731</v>
       </c>
       <c r="C4" t="n">
-        <v>71.98174167537614</v>
+        <v>68.53580723346982</v>
       </c>
       <c r="D4" t="n">
-        <v>153.2547436237441</v>
+        <v>165.4176159316578</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>68.25600913775951</v>
+        <v>45.82307409571988</v>
       </c>
       <c r="C5" t="n">
-        <v>164.197303535279</v>
+        <v>202.6327261565417</v>
       </c>
       <c r="D5" t="n">
-        <v>150.3301172127929</v>
+        <v>170.971362694582</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>60.21647718768238</v>
+        <v>41.37870223859457</v>
       </c>
       <c r="C6" t="n">
-        <v>270.2093658829624</v>
+        <v>317.2635515998078</v>
       </c>
       <c r="D6" t="n">
-        <v>82.59639785369266</v>
+        <v>100.5486363735499</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>19.46314823669301</v>
+        <v>13.71403368062369</v>
       </c>
       <c r="C7" t="n">
-        <v>292.6658628699039</v>
+        <v>293.6240486292488</v>
       </c>
       <c r="D7" t="n">
-        <v>45.39405034896402</v>
+        <v>49.94543270585223</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.090361846519712</v>
+        <v>4.172427743048944</v>
       </c>
       <c r="C8" t="n">
-        <v>184.6716519073462</v>
+        <v>177.0778334149972</v>
       </c>
       <c r="D8" t="n">
-        <v>34.13045893814036</v>
+        <v>35.04839304161113</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.885937339858122</v>
+        <v>1.664062358698343</v>
       </c>
       <c r="C9" t="n">
-        <v>63.34530712111692</v>
+        <v>64.34374453633593</v>
       </c>
       <c r="D9" t="n">
-        <v>32.39374724932775</v>
+        <v>31.94999728700819</v>
       </c>
     </row>
     <row r="10">
@@ -3383,10 +3383,10 @@
         <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>30.03657101143117</v>
+        <v>30.46363126277853</v>
       </c>
       <c r="D10" t="n">
-        <v>25.33890824661018</v>
+        <v>25.0542014123786</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>23.27821981539612</v>
+        <v>22.7451308119901</v>
       </c>
       <c r="D11" t="n">
-        <v>24.34439782220815</v>
+        <v>23.98900515327081</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.14033316844506</v>
+        <v>16.70640068316797</v>
       </c>
       <c r="D12" t="n">
-        <v>19.96089432274615</v>
+        <v>20.17786056538469</v>
       </c>
     </row>
     <row r="13">
@@ -3428,7 +3428,7 @@
         <v>11.44717823151781</v>
       </c>
       <c r="D13" t="n">
-        <v>16.1301147807751</v>
+        <v>16.3902779224005</v>
       </c>
     </row>
     <row r="14">
@@ -3439,7 +3439,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.36962016288231</v>
+        <v>11.06233313145306</v>
       </c>
       <c r="D14" t="n">
         <v>11.06233313145306</v>
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>28.51878906066559</v>
       </c>
       <c r="D16" t="n">
-        <v>3.719842051391165</v>
+        <v>3.306526267903257</v>
       </c>
     </row>
     <row r="17">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.048146695237099</v>
+        <v>2.057743188101315</v>
       </c>
       <c r="C2" t="n">
-        <v>3.974114706791088</v>
+        <v>6.829037030740813</v>
       </c>
       <c r="D2" t="n">
-        <v>15.86406115292421</v>
+        <v>13.1897804065559</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>12.33075116533994</v>
+        <v>7.795076771719675</v>
       </c>
       <c r="C3" t="n">
-        <v>20.97994843975434</v>
+        <v>15.39380400258999</v>
       </c>
       <c r="D3" t="n">
-        <v>61.9580976150162</v>
+        <v>63.64179492779948</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>36.28441340125786</v>
+        <v>23.39406604449724</v>
       </c>
       <c r="C4" t="n">
-        <v>66.30233120630834</v>
+        <v>58.51707191163113</v>
       </c>
       <c r="D4" t="n">
-        <v>151.9529461679128</v>
+        <v>162.673631098288</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>67.29880512611886</v>
+        <v>44.59588946541137</v>
       </c>
       <c r="C5" t="n">
-        <v>150.3792045980052</v>
+        <v>170.529576227671</v>
       </c>
       <c r="D5" t="n">
-        <v>165.1545075469197</v>
+        <v>185.525772410041</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>72.09071567054754</v>
+        <v>48.3422387048172</v>
       </c>
       <c r="C6" t="n">
-        <v>267.5527565952705</v>
+        <v>320.2824257903667</v>
       </c>
       <c r="D6" t="n">
-        <v>101.9976959850181</v>
+        <v>121.6807557074624</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>36.65060529494193</v>
+        <v>25.51169584255761</v>
       </c>
       <c r="C7" t="n">
-        <v>333.2689844221435</v>
+        <v>358.1818141651105</v>
       </c>
       <c r="D7" t="n">
-        <v>53.59851591335461</v>
+        <v>61.14422876819559</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.930378028456486</v>
+        <v>7.260024272905162</v>
       </c>
       <c r="C8" t="n">
-        <v>265.1160587933299</v>
+        <v>258.2732772947296</v>
       </c>
       <c r="D8" t="n">
-        <v>37.46840113257952</v>
+        <v>38.38633523605029</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.773437264497239</v>
+        <v>2.32968730217768</v>
       </c>
       <c r="C9" t="n">
-        <v>122.8078020719377</v>
+        <v>117.9265524864226</v>
       </c>
       <c r="D9" t="n">
-        <v>33.28124717396686</v>
+        <v>32.9484347022272</v>
       </c>
     </row>
     <row r="10">
@@ -3694,10 +3694,10 @@
         <v>0.7117670855789376</v>
       </c>
       <c r="C10" t="n">
-        <v>45.26838664282043</v>
+        <v>45.98015372839937</v>
       </c>
       <c r="D10" t="n">
-        <v>26.47773558353648</v>
+        <v>26.1930287493049</v>
       </c>
     </row>
     <row r="11">
@@ -3711,7 +3711,7 @@
         <v>27.18753917370691</v>
       </c>
       <c r="D11" t="n">
-        <v>24.87748682561417</v>
+        <v>24.52209415667683</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>19.96089432274615</v>
+        <v>19.30999559483051</v>
       </c>
       <c r="D12" t="n">
-        <v>20.17786056538469</v>
+        <v>20.61179305066178</v>
       </c>
     </row>
     <row r="13">
@@ -3736,7 +3736,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.52848336452105</v>
+        <v>13.26832022289564</v>
       </c>
       <c r="D13" t="n">
         <v>16.65044106402591</v>
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.98419422574081</v>
+        <v>11.67690719431156</v>
       </c>
       <c r="D14" t="n">
-        <v>11.36962016288231</v>
+        <v>11.06233313145306</v>
       </c>
     </row>
     <row r="15">
@@ -3764,7 +3764,7 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>20.42526098685489</v>
+        <v>20.78359889890498</v>
       </c>
       <c r="D15" t="n">
         <v>6.450082416901544</v>
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.10547327717769</v>
+        <v>27.27884171020187</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>2.89321048441535</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.259042525200916</v>
+        <v>4.393320976504477</v>
       </c>
       <c r="C2" t="n">
-        <v>1.761255381418778</v>
+        <v>5.475206946584461</v>
       </c>
       <c r="D2" t="n">
-        <v>5.904230693340318</v>
+        <v>22.5900146747191</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.610868056219768</v>
+        <v>1.487347771933918</v>
       </c>
       <c r="C2" t="n">
-        <v>2.288453898599315</v>
+        <v>3.932881303212722</v>
       </c>
       <c r="D2" t="n">
-        <v>11.67592544660732</v>
+        <v>9.81256830394687</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.24439842509522</v>
+        <v>10.37707323388879</v>
       </c>
       <c r="C3" t="n">
-        <v>22.37403017978481</v>
+        <v>20.9455872701057</v>
       </c>
       <c r="D3" t="n">
-        <v>68.48181110973626</v>
+        <v>68.99231991594461</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>50.52760909447059</v>
+        <v>33.3489877655599</v>
       </c>
       <c r="C4" t="n">
-        <v>93.42311153612647</v>
+        <v>88.10105723140452</v>
       </c>
       <c r="D4" t="n">
-        <v>156.2667455803733</v>
+        <v>168.3785670076662</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>42.46058820867456</v>
+        <v>28.05344064885261</v>
       </c>
       <c r="C5" t="n">
-        <v>226.0474089028282</v>
+        <v>264.7037247575463</v>
       </c>
       <c r="D5" t="n">
-        <v>149.3729132011522</v>
+        <v>169.9159839125167</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>22.74218556887737</v>
+        <v>15.81890075852886</v>
       </c>
       <c r="C6" t="n">
-        <v>271.9401870855495</v>
+        <v>295.5276574277834</v>
       </c>
       <c r="D6" t="n">
-        <v>80.66431837173494</v>
+        <v>94.63164296005432</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>6.527640485537042</v>
+        <v>4.790928796724434</v>
       </c>
       <c r="C7" t="n">
-        <v>186.4270168025396</v>
+        <v>181.6360880058151</v>
       </c>
       <c r="D7" t="n">
-        <v>33.17718191731671</v>
+        <v>34.73423377625215</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.919316761802514</v>
+        <v>1.585522542358599</v>
       </c>
       <c r="C8" t="n">
-        <v>90.45823346930109</v>
+        <v>86.86994561027902</v>
       </c>
       <c r="D8" t="n">
-        <v>24.53387512912779</v>
+        <v>24.28352946454485</v>
       </c>
     </row>
     <row r="9">
@@ -4302,10 +4302,10 @@
         <v>0.4437499623195582</v>
       </c>
       <c r="C9" t="n">
-        <v>34.50155957034565</v>
+        <v>35.05624702324509</v>
       </c>
       <c r="D9" t="n">
-        <v>20.1906232855399</v>
+        <v>19.96874830438012</v>
       </c>
     </row>
     <row r="10">
@@ -4319,7 +4319,7 @@
         <v>21.21065915025234</v>
       </c>
       <c r="D10" t="n">
-        <v>19.50241814486289</v>
+        <v>19.21771131063132</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>15.99267010218054</v>
+        <v>15.45958109877452</v>
       </c>
       <c r="D11" t="n">
-        <v>16.17036643664921</v>
+        <v>16.52575910558656</v>
       </c>
     </row>
     <row r="12">
@@ -4344,7 +4344,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>10.84831213192725</v>
+        <v>10.63134588928871</v>
       </c>
       <c r="D12" t="n">
         <v>13.4519070435898</v>
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>9.886199381765381</v>
+        <v>9.626036240139976</v>
       </c>
       <c r="D13" t="n">
-        <v>9.365873098514571</v>
+        <v>9.105709956889166</v>
       </c>
     </row>
     <row r="14">
@@ -4372,7 +4372,7 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>16.90078672860884</v>
+        <v>17.20807376003809</v>
       </c>
       <c r="D14" t="n">
         <v>5.223879534297279</v>
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>23.65030219530566</v>
+        <v>22.93362637120549</v>
       </c>
       <c r="D15" t="n">
-        <v>2.5083653843506</v>
+        <v>2.150027472300515</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.054839002717578</v>
+        <v>5.766786014745764</v>
       </c>
       <c r="C2" t="n">
-        <v>5.591053175685585</v>
+        <v>5.584180941755857</v>
       </c>
       <c r="D2" t="n">
-        <v>19.78516148368597</v>
+        <v>33.54337381100077</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.41343895667492</v>
+        <v>9.341329405908402</v>
       </c>
       <c r="C3" t="n">
-        <v>4.50622196249286</v>
+        <v>13.79355524466769</v>
       </c>
       <c r="D3" t="n">
-        <v>8.330129270534187</v>
+        <v>22.11386703815941</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>1.008254892261474</v>
       </c>
       <c r="C4" t="n">
-        <v>1.454950097693773</v>
+        <v>1.493238258159399</v>
       </c>
       <c r="D4" t="n">
         <v>19.62906359871073</v>
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.68784528777852</v>
+        <v>4.736932672990861</v>
       </c>
       <c r="C5" t="n">
-        <v>9.424777960769381</v>
+        <v>9.449321653375552</v>
       </c>
       <c r="D5" t="n">
         <v>28.49522711576368</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.130834486572086</v>
+        <v>8.050331174823848</v>
       </c>
       <c r="C6" t="n">
-        <v>18.47551004622073</v>
+        <v>18.27425176685013</v>
       </c>
       <c r="D6" t="n">
-        <v>32.52333794628834</v>
+        <v>32.8453511932813</v>
       </c>
     </row>
     <row r="7">
@@ -4588,7 +4588,7 @@
         <v>20.9603134856694</v>
       </c>
       <c r="D7" t="n">
-        <v>32.69808903764427</v>
+        <v>32.21899615797182</v>
       </c>
     </row>
     <row r="8">
@@ -4596,7 +4596,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.762098260402782</v>
+        <v>8.845546815263761</v>
       </c>
       <c r="C8" t="n">
         <v>21.69662426385451</v>
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.874999246391162</v>
+        <v>8.764061755811273</v>
       </c>
       <c r="C9" t="n">
         <v>22.74218556887735</v>
       </c>
       <c r="D9" t="n">
-        <v>39.2718716652809</v>
+        <v>39.60468413702056</v>
       </c>
     </row>
     <row r="10">
@@ -4630,7 +4630,7 @@
         <v>25.62361508084176</v>
       </c>
       <c r="D10" t="n">
-        <v>50.67781649322036</v>
+        <v>50.1084028247572</v>
       </c>
     </row>
     <row r="11">
@@ -4655,7 +4655,7 @@
         <v>5.641122308602172</v>
       </c>
       <c r="C12" t="n">
-        <v>25.60201663134832</v>
+        <v>25.81898287398687</v>
       </c>
       <c r="D12" t="n">
         <v>43.17628228507047</v>
@@ -4666,10 +4666,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.682936549257286</v>
+        <v>4.943099690882691</v>
       </c>
       <c r="C13" t="n">
-        <v>24.19517217116264</v>
+        <v>23.93500902953724</v>
       </c>
       <c r="D13" t="n">
         <v>44.22773407631881</v>
@@ -4697,7 +4697,7 @@
         <v>5.375068680751286</v>
       </c>
       <c r="C15" t="n">
-        <v>26.15866757965626</v>
+        <v>25.80032966760617</v>
       </c>
       <c r="D15" t="n">
         <v>42.28387362191012</v>
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39944223566286</v>
+        <v>13.39643286038406</v>
       </c>
       <c r="C21" t="n">
-        <v>70.15002111611732</v>
+        <v>70.13426615142244</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576404968901513</v>
+        <v>1.576050924751066</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.034402227377644</v>
+        <v>4.929355223023235</v>
       </c>
       <c r="C2" t="n">
-        <v>11.28322636490859</v>
+        <v>6.729880512611885</v>
       </c>
       <c r="D2" t="n">
-        <v>21.44627859927157</v>
+        <v>32.21703266256333</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.82286880707485</v>
+        <v>15.66378462125786</v>
       </c>
       <c r="C3" t="n">
-        <v>15.50670498857837</v>
+        <v>18.78574232076272</v>
       </c>
       <c r="D3" t="n">
-        <v>22.93362637120549</v>
+        <v>44.94440990041898</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>17.84228277698153</v>
+        <v>10.98870205363455</v>
       </c>
       <c r="C4" t="n">
-        <v>7.530004891573036</v>
+        <v>21.58175978245763</v>
       </c>
       <c r="D4" t="n">
-        <v>19.4376227963826</v>
+        <v>26.66132240423063</v>
       </c>
     </row>
     <row r="5">
@@ -4868,10 +4868,10 @@
         <v>3.067961575771283</v>
       </c>
       <c r="C5" t="n">
-        <v>5.399612373357458</v>
+        <v>5.522330836388309</v>
       </c>
       <c r="D5" t="n">
-        <v>29.10881943091793</v>
+        <v>29.40334374219198</v>
       </c>
     </row>
     <row r="6">
@@ -4882,10 +4882,10 @@
         <v>7.446556336712058</v>
       </c>
       <c r="C6" t="n">
-        <v>16.54343056426301</v>
+        <v>16.50317890838889</v>
       </c>
       <c r="D6" t="n">
-        <v>34.77743067523902</v>
+        <v>34.57617239586842</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.521970983489814</v>
+        <v>9.581857593448868</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>24.07441720354028</v>
       </c>
       <c r="D7" t="n">
-        <v>35.27321326588365</v>
+        <v>34.97378021608837</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.596583809012571</v>
+        <v>9.513135254151592</v>
       </c>
       <c r="C8" t="n">
         <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>36.80081269369168</v>
+        <v>36.63391558396972</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.318749208710722</v>
+        <v>9.429686699290611</v>
       </c>
       <c r="C9" t="n">
-        <v>25.5156228333746</v>
+        <v>25.73749781453438</v>
       </c>
       <c r="D9" t="n">
-        <v>40.27030908049991</v>
+        <v>40.60312155223957</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.968265278294615</v>
+        <v>8.825911861178826</v>
       </c>
       <c r="C10" t="n">
         <v>27.3318560862312</v>
       </c>
       <c r="D10" t="n">
-        <v>50.1084028247572</v>
+        <v>49.68134257340984</v>
       </c>
     </row>
     <row r="11">
@@ -4949,7 +4949,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7.463246047684251</v>
+        <v>7.640942382152923</v>
       </c>
       <c r="C11" t="n">
         <v>29.49759152179966</v>
@@ -4966,7 +4966,7 @@
         <v>6.075054793879263</v>
       </c>
       <c r="C12" t="n">
-        <v>29.07347651356504</v>
+        <v>28.8565102709265</v>
       </c>
       <c r="D12" t="n">
         <v>44.69504598354028</v>
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.943099690882691</v>
+        <v>5.203262832508096</v>
       </c>
       <c r="C13" t="n">
         <v>26.79680358741669</v>
       </c>
       <c r="D13" t="n">
-        <v>44.22773407631881</v>
+        <v>44.74806035956962</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.302018440009523</v>
+        <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
-        <v>25.81211064005714</v>
+        <v>25.50482360862789</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>44.86390658867074</v>
       </c>
     </row>
     <row r="15">
@@ -5005,7 +5005,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.0167307687012</v>
+        <v>4.658392856651115</v>
       </c>
       <c r="C15" t="n">
         <v>26.51700549170635</v>
@@ -5022,10 +5022,10 @@
         <v>5.373105185342793</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>28.9321048441535</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>40.91826256530281</v>
       </c>
     </row>
     <row r="17">
@@ -5039,7 +5039,7 @@
         <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>36.36098972218912</v>
       </c>
     </row>
     <row r="18">
@@ -5050,7 +5050,7 @@
         <v>5.885577486959628</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>34.24335992412875</v>
       </c>
       <c r="D18" t="n">
         <v>31.56809743005619</v>
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.44435184043759</v>
+        <v>15.43545028491652</v>
       </c>
       <c r="C21" t="n">
-        <v>86.16322605717814</v>
+        <v>86.113564747429</v>
       </c>
       <c r="D21" t="n">
-        <v>3.251442492723703</v>
+        <v>3.249568481035056</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.004949796250239</v>
+        <v>4.191080949429634</v>
       </c>
       <c r="C2" t="n">
-        <v>7.319910882864218</v>
+        <v>7.890306299031615</v>
       </c>
       <c r="D2" t="n">
-        <v>25.54311176909351</v>
+        <v>28.49915410658066</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.9133695223148</v>
+        <v>16.46390900021901</v>
       </c>
       <c r="C3" t="n">
-        <v>32.73146845958865</v>
+        <v>23.18397203578843</v>
       </c>
       <c r="D3" t="n">
-        <v>34.76859494590079</v>
+        <v>60.28912651779663</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.5029011709484</v>
+        <v>21.95187866695868</v>
       </c>
       <c r="C4" t="n">
-        <v>25.93384735538374</v>
+        <v>36.09297259892973</v>
       </c>
       <c r="D4" t="n">
-        <v>26.55922064298896</v>
+        <v>43.16351956491527</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>15.56070111231195</v>
+        <v>9.989282890711298</v>
       </c>
       <c r="C5" t="n">
-        <v>10.18563243156066</v>
+        <v>25.08365384350601</v>
       </c>
       <c r="D5" t="n">
-        <v>29.45243112740432</v>
+        <v>32.20132469929538</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.916993413495527</v>
+        <v>5.957245069369646</v>
       </c>
       <c r="C6" t="n">
-        <v>12.19625172985813</v>
+        <v>12.3572583533546</v>
       </c>
       <c r="D6" t="n">
-        <v>36.6290068454485</v>
+        <v>36.54850353370026</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.581857593448868</v>
+        <v>9.521970983489814</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>24.25407703341745</v>
       </c>
       <c r="D7" t="n">
-        <v>37.42913122440964</v>
+        <v>37.4890178343687</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.34762080276138</v>
+        <v>10.43106935762236</v>
       </c>
       <c r="C8" t="n">
-        <v>29.87458264023044</v>
+        <v>29.29044275620359</v>
       </c>
       <c r="D8" t="n">
-        <v>38.55323234577224</v>
+        <v>37.88564390688441</v>
       </c>
     </row>
     <row r="9">
@@ -5235,10 +5235,10 @@
         <v>10.09531164276995</v>
       </c>
       <c r="C9" t="n">
-        <v>29.39843500367073</v>
+        <v>29.7312474754104</v>
       </c>
       <c r="D9" t="n">
-        <v>41.26874649571891</v>
+        <v>41.49062147687869</v>
       </c>
     </row>
     <row r="10">
@@ -5252,7 +5252,7 @@
         <v>29.89421759431538</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>48.9695754878309</v>
       </c>
     </row>
     <row r="11">
@@ -5266,7 +5266,7 @@
         <v>31.45225120095506</v>
       </c>
       <c r="D11" t="n">
-        <v>49.75497365122833</v>
+        <v>49.57727731675966</v>
       </c>
     </row>
     <row r="12">
@@ -5277,10 +5277,10 @@
         <v>6.725953521794898</v>
       </c>
       <c r="C12" t="n">
-        <v>32.11100391050467</v>
+        <v>31.46010518258904</v>
       </c>
       <c r="D12" t="n">
-        <v>45.77987719673301</v>
+        <v>46.2138096820101</v>
       </c>
     </row>
     <row r="13">
@@ -5288,7 +5288,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.203262832508096</v>
+        <v>5.463425974133501</v>
       </c>
       <c r="C13" t="n">
         <v>29.91876128692155</v>
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.302018440009523</v>
+        <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
         <v>27.9631198600619</v>
       </c>
       <c r="D14" t="n">
-        <v>45.7857676829585</v>
+        <v>45.47848065152925</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
         <v>27.5920192278566</v>
       </c>
       <c r="D15" t="n">
-        <v>43.35888735806038</v>
+        <v>43.00054944601029</v>
       </c>
     </row>
     <row r="16">
@@ -5333,10 +5333,10 @@
         <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>28.9321048441535</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>41.33157834879071</v>
       </c>
     </row>
     <row r="17">
@@ -5347,10 +5347,10 @@
         <v>5.194427103169874</v>
       </c>
       <c r="C17" t="n">
-        <v>32.58322455624739</v>
+        <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
-        <v>37.30543101367455</v>
+        <v>36.83321036793183</v>
       </c>
     </row>
     <row r="18">
@@ -5375,7 +5375,7 @@
         <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>36.71049190490098</v>
       </c>
       <c r="D19" t="n">
         <v>24.67426505083508</v>
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.74072701862709</v>
+        <v>16.72352431963762</v>
       </c>
       <c r="C21" t="n">
-        <v>102.1184348136253</v>
+        <v>102.0134983497895</v>
       </c>
       <c r="D21" t="n">
-        <v>5.022218105588127</v>
+        <v>4.180881079909405</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.724390937013903</v>
+        <v>4.247040568571702</v>
       </c>
       <c r="C2" t="n">
-        <v>12.09611346402495</v>
+        <v>9.428704951586367</v>
       </c>
       <c r="D2" t="n">
-        <v>23.16728232481623</v>
+        <v>22.14920995551229</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.94634803363169</v>
+        <v>15.28581175512284</v>
       </c>
       <c r="C3" t="n">
-        <v>30.21819433671682</v>
+        <v>27.37112599440108</v>
       </c>
       <c r="D3" t="n">
-        <v>46.4464838879166</v>
+        <v>68.53580723346982</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.97436105316512</v>
+        <v>27.0569667290421</v>
       </c>
       <c r="C4" t="n">
-        <v>56.94725733254049</v>
+        <v>47.75809882079034</v>
       </c>
       <c r="D4" t="n">
-        <v>37.13951565165684</v>
+        <v>62.56285420083224</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>30.53235360207581</v>
+        <v>21.42664364518664</v>
       </c>
       <c r="C5" t="n">
-        <v>30.92505268377453</v>
+        <v>47.51658888554563</v>
       </c>
       <c r="D5" t="n">
-        <v>32.49584901056943</v>
+        <v>39.68715094417732</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>13.48430471782994</v>
+        <v>9.700649065662736</v>
       </c>
       <c r="C6" t="n">
-        <v>14.32958949118645</v>
+        <v>26.56609287691869</v>
       </c>
       <c r="D6" t="n">
-        <v>38.11831811279092</v>
+        <v>38.84284791852506</v>
       </c>
     </row>
     <row r="7">
@@ -5518,10 +5518,10 @@
         <v>8.683558444063037</v>
       </c>
       <c r="C7" t="n">
-        <v>21.02020009562846</v>
+        <v>21.08008670558751</v>
       </c>
       <c r="D7" t="n">
-        <v>39.46527596301753</v>
+        <v>39.52516257297658</v>
       </c>
     </row>
     <row r="8">
@@ -5532,10 +5532,10 @@
         <v>10.76486357706628</v>
       </c>
       <c r="C8" t="n">
-        <v>31.87734795689393</v>
+        <v>31.37665662772806</v>
       </c>
       <c r="D8" t="n">
-        <v>40.38910055271378</v>
+        <v>39.8884092235479</v>
       </c>
     </row>
     <row r="9">
@@ -5546,10 +5546,10 @@
         <v>10.76093658624928</v>
       </c>
       <c r="C9" t="n">
-        <v>34.16874709860598</v>
+        <v>33.61405964570653</v>
       </c>
       <c r="D9" t="n">
-        <v>41.93437143919824</v>
+        <v>42.3781214015178</v>
       </c>
     </row>
     <row r="10">
@@ -5560,10 +5560,10 @@
         <v>9.964739198105127</v>
       </c>
       <c r="C10" t="n">
-        <v>33.02599277086271</v>
+        <v>33.59540643932586</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>48.54251523648354</v>
       </c>
     </row>
     <row r="11">
@@ -5577,7 +5577,7 @@
         <v>33.93999988351647</v>
       </c>
       <c r="D11" t="n">
-        <v>50.82115165804038</v>
+        <v>50.6434553235717</v>
       </c>
     </row>
     <row r="12">
@@ -5588,10 +5588,10 @@
         <v>7.376852249710534</v>
       </c>
       <c r="C12" t="n">
-        <v>34.71459882216721</v>
+        <v>33.84673385161303</v>
       </c>
       <c r="D12" t="n">
-        <v>46.86470840992573</v>
+        <v>47.08167465256428</v>
       </c>
     </row>
     <row r="13">
@@ -5602,7 +5602,7 @@
         <v>5.723589115758904</v>
       </c>
       <c r="C13" t="n">
-        <v>33.30088212805181</v>
+        <v>33.04071898642641</v>
       </c>
       <c r="D13" t="n">
         <v>45.78871292607123</v>
@@ -5613,10 +5613,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.302018440009523</v>
+        <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
-        <v>30.42141611149592</v>
+        <v>30.72870314292517</v>
       </c>
       <c r="D14" t="n">
         <v>45.7857676829585</v>
@@ -5630,10 +5630,10 @@
         <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>29.38370878810703</v>
+        <v>29.02537087605695</v>
       </c>
       <c r="D15" t="n">
-        <v>44.07556318216055</v>
+        <v>43.00054944601029</v>
       </c>
     </row>
     <row r="16">
@@ -5644,10 +5644,10 @@
         <v>4.546473618366978</v>
       </c>
       <c r="C16" t="n">
-        <v>30.17205219461722</v>
+        <v>29.75873641112932</v>
       </c>
       <c r="D16" t="n">
-        <v>41.33157834879071</v>
+        <v>41.74489413227862</v>
       </c>
     </row>
     <row r="17">
@@ -5658,10 +5658,10 @@
         <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>32.58322455624739</v>
+        <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
-        <v>37.30543101367455</v>
+        <v>36.83321036793183</v>
       </c>
     </row>
     <row r="18">
@@ -5672,7 +5672,7 @@
         <v>4.815472489330605</v>
       </c>
       <c r="C18" t="n">
-        <v>35.31346492175777</v>
+        <v>34.77841242294325</v>
       </c>
       <c r="D18" t="n">
         <v>32.1031499288707</v>
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.06951608387178</v>
+        <v>18.04264308835436</v>
       </c>
       <c r="C21" t="n">
-        <v>117.8820811185921</v>
+        <v>117.7067668145023</v>
       </c>
       <c r="D21" t="n">
-        <v>6.883625174808297</v>
+        <v>6.014214362784787</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.338564089244908</v>
+        <v>5.232715263635499</v>
       </c>
       <c r="C2" t="n">
-        <v>7.927612711792993</v>
+        <v>11.03877118655113</v>
       </c>
       <c r="D2" t="n">
-        <v>34.1834733141697</v>
+        <v>26.8851608807989</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.2534551386117</v>
+        <v>13.22905031472577</v>
       </c>
       <c r="C3" t="n">
-        <v>37.41931374736718</v>
+        <v>30.55689729468197</v>
       </c>
       <c r="D3" t="n">
-        <v>50.54528055314703</v>
+        <v>65.98326320242812</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>24.87454158250144</v>
+        <v>20.73942025221387</v>
       </c>
       <c r="C4" t="n">
-        <v>55.97729060074463</v>
+        <v>49.07265899677682</v>
       </c>
       <c r="D4" t="n">
-        <v>44.73333414400592</v>
+        <v>71.31808022730529</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>25.20637230653686</v>
+        <v>18.87409961414493</v>
       </c>
       <c r="C5" t="n">
-        <v>53.16163818496479</v>
+        <v>51.51721078035138</v>
       </c>
       <c r="D5" t="n">
-        <v>30.704159450319</v>
+        <v>42.11697651218817</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>14.89311267342412</v>
+        <v>10.50568218314512</v>
       </c>
       <c r="C6" t="n">
-        <v>21.9774041072691</v>
+        <v>34.77743067523902</v>
       </c>
       <c r="D6" t="n">
-        <v>30.95352336719769</v>
+        <v>32.96610616090365</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>6.168320825782709</v>
+        <v>5.150248456478767</v>
       </c>
       <c r="C7" t="n">
-        <v>13.41460063082842</v>
+        <v>19.22360179685679</v>
       </c>
       <c r="D7" t="n">
-        <v>30.72183090899544</v>
+        <v>30.84160412891355</v>
       </c>
     </row>
     <row r="8">
@@ -5843,10 +5843,10 @@
         <v>4.840016181936775</v>
       </c>
       <c r="C8" t="n">
-        <v>18.69247628885927</v>
+        <v>18.35868206941536</v>
       </c>
       <c r="D8" t="n">
-        <v>30.37527396939631</v>
+        <v>30.0414797499524</v>
       </c>
     </row>
     <row r="9">
@@ -5857,10 +5857,10 @@
         <v>4.881249585515139</v>
       </c>
       <c r="C9" t="n">
-        <v>21.96562313481813</v>
+        <v>21.85468564423824</v>
       </c>
       <c r="D9" t="n">
-        <v>29.95312245657017</v>
+        <v>30.06405994715006</v>
       </c>
     </row>
     <row r="10">
@@ -5874,7 +5874,7 @@
         <v>21.35301256736813</v>
       </c>
       <c r="D10" t="n">
-        <v>33.73775985644164</v>
+        <v>33.45305302221006</v>
       </c>
     </row>
     <row r="11">
@@ -5888,7 +5888,7 @@
         <v>20.43507846389736</v>
       </c>
       <c r="D11" t="n">
-        <v>34.47308888692249</v>
+        <v>34.65078522139116</v>
       </c>
     </row>
     <row r="12">
@@ -5902,7 +5902,7 @@
         <v>19.96089432274615</v>
       </c>
       <c r="D12" t="n">
-        <v>32.11100391050467</v>
+        <v>31.67707142522758</v>
       </c>
     </row>
     <row r="13">
@@ -5913,10 +5913,10 @@
         <v>2.341468274628643</v>
       </c>
       <c r="C13" t="n">
-        <v>19.25207248027995</v>
+        <v>18.73174619702914</v>
       </c>
       <c r="D13" t="n">
-        <v>30.17892442854696</v>
+        <v>30.43908757017236</v>
       </c>
     </row>
     <row r="14">
@@ -5930,7 +5930,7 @@
         <v>17.51536079146734</v>
       </c>
       <c r="D14" t="n">
-        <v>29.80684204863741</v>
+        <v>29.49955501720816</v>
       </c>
     </row>
     <row r="15">
@@ -5941,10 +5941,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>16.12520604225386</v>
+        <v>15.76686813020377</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>27.95035713990669</v>
       </c>
     </row>
     <row r="16">
@@ -5980,10 +5980,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.605157496443535</v>
+        <v>1.070104997629023</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>17.12167996206437</v>
       </c>
       <c r="D18" t="n">
         <v>20.33199495495144</v>
@@ -6011,7 +6011,7 @@
         <v>1.34499435481813</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.08745766113597</v>
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.062807193124709</v>
+        <v>7.049601222762625</v>
       </c>
       <c r="C21" t="n">
-        <v>66.21381743554414</v>
+        <v>66.09001146339961</v>
       </c>
       <c r="D21" t="n">
-        <v>5.297105394843531</v>
+        <v>4.406000764226641</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.870851271395926</v>
+        <v>4.220533380557038</v>
       </c>
       <c r="C2" t="n">
-        <v>6.024003913258428</v>
+        <v>5.237624002156734</v>
       </c>
       <c r="D2" t="n">
-        <v>24.85097963759951</v>
+        <v>21.50812870463912</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>23.66502841086936</v>
+        <v>16.29210315197582</v>
       </c>
       <c r="C3" t="n">
-        <v>33.26652095840317</v>
+        <v>38.96065764303467</v>
       </c>
       <c r="D3" t="n">
-        <v>67.04355072301468</v>
+        <v>72.62478642165779</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.15303913533804</v>
+        <v>24.0704902127233</v>
       </c>
       <c r="C4" t="n">
-        <v>79.79252641036376</v>
+        <v>65.65143247839271</v>
       </c>
       <c r="D4" t="n">
-        <v>60.4187172147572</v>
+        <v>88.6626169182337</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>32.64311116620645</v>
+        <v>25.86905200690346</v>
       </c>
       <c r="C5" t="n">
-        <v>83.9394287131023</v>
+        <v>75.5209421491859</v>
       </c>
       <c r="D5" t="n">
-        <v>40.91433557448583</v>
+        <v>59.98478472948013</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>25.84156307118455</v>
+        <v>19.11953654020664</v>
       </c>
       <c r="C6" t="n">
-        <v>58.6064109527176</v>
+        <v>62.47056991663305</v>
       </c>
       <c r="D6" t="n">
-        <v>34.21390749300134</v>
+        <v>39.40637110076273</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>12.87562114119692</v>
+        <v>9.342311153612647</v>
       </c>
       <c r="C7" t="n">
-        <v>24.01453059358123</v>
+        <v>37.36924461445059</v>
       </c>
       <c r="D7" t="n">
-        <v>32.93763547748049</v>
+        <v>33.59638818703009</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6.091744504851458</v>
+        <v>5.507604620824606</v>
       </c>
       <c r="C8" t="n">
-        <v>18.60902773399829</v>
+        <v>22.86490403190821</v>
       </c>
       <c r="D8" t="n">
-        <v>32.3780392860598</v>
+        <v>32.12769362147687</v>
       </c>
     </row>
     <row r="9">
@@ -6165,10 +6165,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.103124566674919</v>
+        <v>5.214062057254808</v>
       </c>
       <c r="C9" t="n">
-        <v>23.40781051235669</v>
+        <v>23.07499804061703</v>
       </c>
       <c r="D9" t="n">
         <v>31.39530983410874</v>
@@ -6182,10 +6182,10 @@
         <v>4.697662764820988</v>
       </c>
       <c r="C10" t="n">
-        <v>24.76949457814703</v>
+        <v>24.62714116103124</v>
       </c>
       <c r="D10" t="n">
-        <v>33.73775985644164</v>
+        <v>33.59540643932586</v>
       </c>
     </row>
     <row r="11">
@@ -6196,7 +6196,7 @@
         <v>4.08701569277947</v>
       </c>
       <c r="C11" t="n">
-        <v>23.45591614986479</v>
+        <v>23.10052348092744</v>
       </c>
       <c r="D11" t="n">
         <v>35.36157055926586</v>
@@ -6224,10 +6224,10 @@
         <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>21.33337761328319</v>
+        <v>20.81305133003238</v>
       </c>
       <c r="D13" t="n">
-        <v>30.95941385342317</v>
+        <v>30.69925071179776</v>
       </c>
     </row>
     <row r="14">
@@ -6235,10 +6235,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>19.66637001147211</v>
+        <v>19.35908298004286</v>
       </c>
       <c r="D14" t="n">
         <v>30.11412908006666</v>
@@ -6255,7 +6255,7 @@
         <v>17.5585576904542</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -6269,7 +6269,7 @@
         <v>16.53263133951629</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -6294,10 +6294,10 @@
         <v>1.070104997629023</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>17.12167996206437</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.203622685406589</v>
+        <v>0.6018113427032947</v>
       </c>
       <c r="C19" t="n">
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>15.64709491028566</v>
       </c>
     </row>
     <row r="20">
@@ -6322,7 +6322,7 @@
         <v>0.672497177409065</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.28419173838191</v>
+        <v>7.26851249290506</v>
       </c>
       <c r="C21" t="n">
-        <v>75.57348928571233</v>
+        <v>75.41081711389</v>
       </c>
       <c r="D21" t="n">
-        <v>6.373667771084172</v>
+        <v>5.451384369678795</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.457535487908019</v>
+        <v>3.811144587886118</v>
       </c>
       <c r="C2" t="n">
-        <v>3.421390749300134</v>
+        <v>7.019496085364694</v>
       </c>
       <c r="D2" t="n">
-        <v>27.69313924139403</v>
+        <v>19.76847177271377</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.78498155723672</v>
+        <v>15.32017292477148</v>
       </c>
       <c r="C3" t="n">
-        <v>27.38585220996478</v>
+        <v>27.85709110800325</v>
       </c>
       <c r="D3" t="n">
-        <v>71.36814936022188</v>
+        <v>72.97821559518665</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>41.10872161992669</v>
+        <v>28.18008610270045</v>
       </c>
       <c r="C4" t="n">
-        <v>81.09432386619503</v>
+        <v>84.13185126313466</v>
       </c>
       <c r="D4" t="n">
-        <v>80.44342513827939</v>
+        <v>105.1903395192287</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>42.58330667170541</v>
+        <v>31.66136346195964</v>
       </c>
       <c r="C5" t="n">
-        <v>120.215006385022</v>
+        <v>100.4818775296611</v>
       </c>
       <c r="D5" t="n">
-        <v>52.98983233672161</v>
+        <v>78.3189231062893</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>36.10573531908495</v>
+        <v>27.53213261789756</v>
       </c>
       <c r="C6" t="n">
-        <v>99.66309994431923</v>
+        <v>94.14862308956488</v>
       </c>
       <c r="D6" t="n">
-        <v>39.72838434775569</v>
+        <v>48.66425195181016</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>22.39759212468673</v>
+        <v>16.5287043486993</v>
       </c>
       <c r="C7" t="n">
-        <v>56.77250624118454</v>
+        <v>66.17470400475625</v>
       </c>
       <c r="D7" t="n">
-        <v>35.75230614555609</v>
+        <v>37.66867766424586</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.43106935762236</v>
+        <v>8.011061266653972</v>
       </c>
       <c r="C8" t="n">
-        <v>25.78560345204247</v>
+        <v>37.38495257771854</v>
       </c>
       <c r="D8" t="n">
-        <v>33.96356182841841</v>
+        <v>33.88011327355743</v>
       </c>
     </row>
     <row r="9">
@@ -6476,10 +6476,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.879687000734146</v>
+        <v>5.657812019574366</v>
       </c>
       <c r="C9" t="n">
-        <v>23.96249796525614</v>
+        <v>26.29218526743382</v>
       </c>
       <c r="D9" t="n">
         <v>32.9484347022272</v>
@@ -6493,10 +6493,10 @@
         <v>4.982369599052563</v>
       </c>
       <c r="C10" t="n">
-        <v>27.18950266911542</v>
+        <v>26.90479583488384</v>
       </c>
       <c r="D10" t="n">
-        <v>34.02246669067321</v>
+        <v>33.88011327355743</v>
       </c>
     </row>
     <row r="11">
@@ -6504,7 +6504,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.264712027248144</v>
+        <v>4.442408361716816</v>
       </c>
       <c r="C11" t="n">
         <v>26.47675383583222</v>
@@ -6521,7 +6521,7 @@
         <v>3.471459882216721</v>
       </c>
       <c r="C12" t="n">
-        <v>24.95111790343269</v>
+        <v>24.73415166079414</v>
       </c>
       <c r="D12" t="n">
         <v>34.06370009425158</v>
@@ -6535,10 +6535,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>23.41468274628643</v>
+        <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
-        <v>31.47974013667398</v>
+        <v>31.21957699504857</v>
       </c>
     </row>
     <row r="14">
@@ -6549,7 +6549,7 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>21.81737923147687</v>
+        <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
         <v>30.42141611149592</v>
@@ -6580,7 +6580,7 @@
         <v>17.3592629064921</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -6608,7 +6608,7 @@
         <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -6630,10 +6630,10 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.672497177409065</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.492061639327416</v>
+        <v>7.474616157350301</v>
       </c>
       <c r="C21" t="n">
-        <v>85.22220114734937</v>
+        <v>84.08943177019088</v>
       </c>
       <c r="D21" t="n">
-        <v>7.492061639327416</v>
+        <v>6.540289137681514</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_iteration_1_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_1_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497658445214</v>
+        <v>10.84497620036111</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907282082383</v>
+        <v>37.78907148246743</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.942698780255191</v>
+        <v>4.570035563268902</v>
       </c>
       <c r="C2" t="n">
-        <v>10.96415836102838</v>
+        <v>7.448519832120549</v>
       </c>
       <c r="D2" t="n">
-        <v>32.76288438612455</v>
+        <v>25.47733467290897</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.03899217072939</v>
+        <v>14.27952035826986</v>
       </c>
       <c r="C3" t="n">
-        <v>27.45948328778329</v>
+        <v>26.03594911662541</v>
       </c>
       <c r="D3" t="n">
-        <v>71.67739988705962</v>
+        <v>69.55191610736527</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.94584931201296</v>
+        <v>29.62227348023901</v>
       </c>
       <c r="C4" t="n">
-        <v>76.30830380799182</v>
+        <v>62.46075243959057</v>
       </c>
       <c r="D4" t="n">
-        <v>115.5919564457237</v>
+        <v>83.92764774065132</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>36.81553890925539</v>
+        <v>38.31270415823178</v>
       </c>
       <c r="C5" t="n">
-        <v>128.9771046454247</v>
+        <v>97.78207134298233</v>
       </c>
       <c r="D5" t="n">
-        <v>97.34028487607128</v>
+        <v>59.88660995905545</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>35.38120551335081</v>
+        <v>38.48058301565798</v>
       </c>
       <c r="C6" t="n">
-        <v>126.1486895094897</v>
+        <v>89.35867604054471</v>
       </c>
       <c r="D6" t="n">
-        <v>60.53849043467533</v>
+        <v>43.14977509705582</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>24.43373686329462</v>
+        <v>28.7455727803466</v>
       </c>
       <c r="C7" t="n">
-        <v>101.6275771005171</v>
+        <v>82.88306818333271</v>
       </c>
       <c r="D7" t="n">
-        <v>43.05847256056086</v>
+        <v>38.80652325346792</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>12.85107744859075</v>
+        <v>15.27108553955913</v>
       </c>
       <c r="C8" t="n">
-        <v>62.25262192629025</v>
+        <v>66.00780689503429</v>
       </c>
       <c r="D8" t="n">
-        <v>36.38356991938679</v>
+        <v>36.63391558396972</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.989061906533041</v>
+        <v>7.654686850012379</v>
       </c>
       <c r="C9" t="n">
-        <v>36.83124687252333</v>
+        <v>41.71249645803847</v>
       </c>
       <c r="D9" t="n">
-        <v>34.05780960802609</v>
+        <v>34.16874709860598</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.267076433284139</v>
+        <v>5.551783267515713</v>
       </c>
       <c r="C10" t="n">
-        <v>29.75186417719959</v>
+        <v>31.31775176547326</v>
       </c>
       <c r="D10" t="n">
-        <v>34.73423377625215</v>
+        <v>35.58835427894688</v>
       </c>
     </row>
     <row r="11">
@@ -906,10 +906,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.620104696185489</v>
+        <v>4.797801030654161</v>
       </c>
       <c r="C11" t="n">
-        <v>28.96450251839364</v>
+        <v>30.20837685967435</v>
       </c>
       <c r="D11" t="n">
         <v>35.89465956267188</v>
@@ -923,7 +923,7 @@
         <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>27.77167905773377</v>
+        <v>28.42257778564941</v>
       </c>
       <c r="D12" t="n">
         <v>34.93156506480576</v>
@@ -937,10 +937,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>25.23582473766426</v>
+        <v>25.75615102091507</v>
       </c>
       <c r="D13" t="n">
-        <v>31.73990327829938</v>
+        <v>32.5203927031756</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>23.35381438862312</v>
+        <v>23.96838845148163</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>30.42141611149592</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>21.14193681095506</v>
+        <v>21.50027472300514</v>
       </c>
       <c r="D15" t="n">
-        <v>29.02537087605695</v>
+        <v>29.38370878810703</v>
       </c>
     </row>
     <row r="16">
@@ -979,10 +979,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>18.59921025695582</v>
+        <v>19.42584182393164</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>27.27884171020187</v>
       </c>
     </row>
     <row r="17">
@@ -1010,7 +1010,7 @@
         <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>21.40209995258047</v>
       </c>
     </row>
     <row r="19">
@@ -1024,7 +1024,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>16.85071759569225</v>
       </c>
     </row>
     <row r="20">
@@ -1035,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.666426769485772</v>
+        <v>7.717424320421113</v>
       </c>
       <c r="C21" t="n">
-        <v>92.95542458001499</v>
+        <v>96.46780400526391</v>
       </c>
       <c r="D21" t="n">
-        <v>7.666426769485772</v>
+        <v>8.682102360473753</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.751078051477815</v>
+        <v>5.158102438112742</v>
       </c>
       <c r="C2" t="n">
-        <v>9.708503047296707</v>
+        <v>10.28773419280233</v>
       </c>
       <c r="D2" t="n">
-        <v>29.42396044398116</v>
+        <v>19.91180693753381</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.51866588747858</v>
+        <v>14.79493790299943</v>
       </c>
       <c r="C3" t="n">
-        <v>34.93058331710152</v>
+        <v>27.48893571891069</v>
       </c>
       <c r="D3" t="n">
-        <v>79.38902810391832</v>
+        <v>73.09111658117503</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.78444177788898</v>
+        <v>28.23113698332128</v>
       </c>
       <c r="C4" t="n">
-        <v>72.40291144049802</v>
+        <v>63.76254989542184</v>
       </c>
       <c r="D4" t="n">
-        <v>123.6197074233499</v>
+        <v>98.11979255324322</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>39.56443248114646</v>
+        <v>41.25794727097221</v>
       </c>
       <c r="C5" t="n">
-        <v>133.051357618049</v>
+        <v>105.513334513926</v>
       </c>
       <c r="D5" t="n">
-        <v>112.6310053697153</v>
+        <v>74.04832059281568</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>41.78121879733577</v>
+        <v>45.48437113775474</v>
       </c>
       <c r="C6" t="n">
-        <v>162.6166897314417</v>
+        <v>121.8417623309589</v>
       </c>
       <c r="D6" t="n">
-        <v>74.94858323761002</v>
+        <v>51.52211951887262</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>32.39865598784899</v>
+        <v>37.06981156465531</v>
       </c>
       <c r="C7" t="n">
-        <v>137.6793162958684</v>
+        <v>105.0411138681832</v>
       </c>
       <c r="D7" t="n">
-        <v>49.10702016642545</v>
+        <v>41.98051358129786</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>19.10971906316416</v>
+        <v>22.94835258676919</v>
       </c>
       <c r="C8" t="n">
-        <v>95.04790398665493</v>
+        <v>88.28857104291565</v>
       </c>
       <c r="D8" t="n">
-        <v>39.47116644924301</v>
+        <v>38.97047512007713</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.651561680450389</v>
+        <v>11.53749902030851</v>
       </c>
       <c r="C9" t="n">
-        <v>55.69062027110455</v>
+        <v>61.12655730951914</v>
       </c>
       <c r="D9" t="n">
-        <v>35.27812200440487</v>
+        <v>35.94374694788421</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.978843518863076</v>
+        <v>6.548257187326225</v>
       </c>
       <c r="C10" t="n">
-        <v>36.30012136452581</v>
+        <v>40.57072387799944</v>
       </c>
       <c r="D10" t="n">
-        <v>35.58835427894688</v>
+        <v>35.87306111317846</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.797801030654161</v>
+        <v>5.153193699591506</v>
       </c>
       <c r="C11" t="n">
-        <v>31.98534020436108</v>
+        <v>33.40691088011046</v>
       </c>
       <c r="D11" t="n">
-        <v>36.07235589714055</v>
+        <v>36.60544490054656</v>
       </c>
     </row>
     <row r="12">
@@ -1234,10 +1234,10 @@
         <v>3.905392367493811</v>
       </c>
       <c r="C12" t="n">
-        <v>30.15830772675777</v>
+        <v>31.67707142522758</v>
       </c>
       <c r="D12" t="n">
-        <v>35.58246379272139</v>
+        <v>35.36549755008285</v>
       </c>
     </row>
     <row r="13">
@@ -1248,10 +1248,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>27.83745615391831</v>
+        <v>28.61794557879453</v>
       </c>
       <c r="D13" t="n">
-        <v>32.26022956155019</v>
+        <v>33.30088212805181</v>
       </c>
     </row>
     <row r="14">
@@ -1262,10 +1262,10 @@
         <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>25.19753657719863</v>
+        <v>25.81211064005714</v>
       </c>
       <c r="D14" t="n">
-        <v>31.03599017435442</v>
+        <v>30.72870314292517</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>22.93362637120549</v>
+        <v>23.65030219530566</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>29.74204670015712</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>19.83915760741954</v>
+        <v>20.66578917439536</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>27.27884171020187</v>
       </c>
     </row>
     <row r="17">
@@ -1321,7 +1321,7 @@
         <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>21.40209995258047</v>
       </c>
     </row>
     <row r="19">
@@ -1335,7 +1335,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>16.85071759569225</v>
       </c>
     </row>
     <row r="20">
@@ -1346,7 +1346,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.841989379539037</v>
+        <v>7.907117735236974</v>
       </c>
       <c r="C21" t="n">
-        <v>100.9656132615651</v>
+        <v>105.7576997087945</v>
       </c>
       <c r="D21" t="n">
-        <v>8.822238051981415</v>
+        <v>9.883897169046218</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.118251692866123</v>
+        <v>7.099017649408686</v>
       </c>
       <c r="C2" t="n">
-        <v>11.04957041129785</v>
+        <v>6.80842032895163</v>
       </c>
       <c r="D2" t="n">
-        <v>30.81607868860313</v>
+        <v>27.75695284217007</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.76686813020378</v>
+        <v>15.81595551541612</v>
       </c>
       <c r="C3" t="n">
-        <v>36.25103397931348</v>
+        <v>33.472687976295</v>
       </c>
       <c r="D3" t="n">
-        <v>82.43244598708344</v>
+        <v>71.68230862558086</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>26.22738991895354</v>
+        <v>27.77167905773377</v>
       </c>
       <c r="C4" t="n">
-        <v>77.98022014832415</v>
+        <v>65.98326320242812</v>
       </c>
       <c r="D4" t="n">
-        <v>130.5881526280937</v>
+        <v>108.3044432370996</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>40.12893741108838</v>
+        <v>42.04334543436966</v>
       </c>
       <c r="C5" t="n">
-        <v>131.5541923690726</v>
+        <v>109.8575681052181</v>
       </c>
       <c r="D5" t="n">
-        <v>127.2099587777805</v>
+        <v>89.38812847167209</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>46.4504108787336</v>
+        <v>49.99255659565609</v>
       </c>
       <c r="C6" t="n">
-        <v>183.5878024418578</v>
+        <v>141.6053253651515</v>
       </c>
       <c r="D6" t="n">
-        <v>87.99011974082464</v>
+        <v>60.37748381117885</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>39.88448223273092</v>
+        <v>44.73529763941441</v>
       </c>
       <c r="C7" t="n">
-        <v>177.144592258886</v>
+        <v>137.8589761257456</v>
       </c>
       <c r="D7" t="n">
-        <v>57.13182590093888</v>
+        <v>46.59178254814513</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>25.45180923259856</v>
+        <v>30.62561963397925</v>
       </c>
       <c r="C8" t="n">
-        <v>131.0142311317368</v>
+        <v>111.2369236296849</v>
       </c>
       <c r="D8" t="n">
-        <v>42.30841731451629</v>
+        <v>40.80634332701867</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>13.42343636016663</v>
+        <v>16.75156107756332</v>
       </c>
       <c r="C9" t="n">
-        <v>81.98280553853837</v>
+        <v>83.6468678972367</v>
       </c>
       <c r="D9" t="n">
-        <v>37.05312185368311</v>
+        <v>37.71874679716245</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.260024272905163</v>
+        <v>8.541205026947251</v>
       </c>
       <c r="C10" t="n">
-        <v>48.25780840225197</v>
+        <v>54.52135875534661</v>
       </c>
       <c r="D10" t="n">
-        <v>35.87306111317846</v>
+        <v>36.44247478164161</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.153193699591506</v>
+        <v>5.508586368528851</v>
       </c>
       <c r="C11" t="n">
-        <v>36.07235589714055</v>
+        <v>39.80397892098267</v>
       </c>
       <c r="D11" t="n">
-        <v>36.60544490054656</v>
+        <v>37.13853390395258</v>
       </c>
     </row>
     <row r="12">
@@ -1542,10 +1542,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4.122358610132356</v>
+        <v>4.339324852770901</v>
       </c>
       <c r="C12" t="n">
-        <v>32.97886888105885</v>
+        <v>34.49763257952867</v>
       </c>
       <c r="D12" t="n">
         <v>35.58246379272139</v>
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>3.121957699504857</v>
       </c>
       <c r="C13" t="n">
-        <v>29.91876128692155</v>
+        <v>31.73990327829938</v>
       </c>
       <c r="D13" t="n">
-        <v>33.04071898642641</v>
+        <v>33.82120841130262</v>
       </c>
     </row>
     <row r="14">
@@ -1573,7 +1573,7 @@
         <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>27.04125876577415</v>
+        <v>27.9631198600619</v>
       </c>
       <c r="D14" t="n">
         <v>31.03599017435442</v>
@@ -1587,10 +1587,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>24.72531593145592</v>
+        <v>25.083653843506</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>29.74204670015712</v>
       </c>
     </row>
     <row r="16">
@@ -1601,10 +1601,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>21.07910495788326</v>
+        <v>22.31905230834699</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>27.27884171020187</v>
       </c>
     </row>
     <row r="17">
@@ -1615,7 +1615,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>19.36104647545135</v>
+        <v>19.83326712119407</v>
       </c>
       <c r="D17" t="n">
         <v>24.55547357862122</v>
@@ -1632,7 +1632,7 @@
         <v>18.72683745850791</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>21.40209995258047</v>
       </c>
     </row>
     <row r="19">
@@ -1646,7 +1646,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>16.85071759569225</v>
       </c>
     </row>
     <row r="20">
@@ -1657,7 +1657,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8.001782759823191</v>
+        <v>8.082186654701907</v>
       </c>
       <c r="C21" t="n">
-        <v>109.024290102591</v>
+        <v>114.1608864976644</v>
       </c>
       <c r="D21" t="n">
-        <v>10.00222844977899</v>
+        <v>11.11300665021512</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.59890715731956</v>
+        <v>6.33423618780042</v>
       </c>
       <c r="C2" t="n">
-        <v>7.601672473983053</v>
+        <v>4.519966430352315</v>
       </c>
       <c r="D2" t="n">
-        <v>25.44395525096458</v>
+        <v>22.53307330787279</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.53048791765854</v>
+        <v>19.34042977366217</v>
       </c>
       <c r="C3" t="n">
-        <v>53.36780520285661</v>
+        <v>46.50538875017141</v>
       </c>
       <c r="D3" t="n">
-        <v>90.60549562493813</v>
+        <v>79.56574269068275</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>19.27170743436488</v>
+        <v>20.1906232855399</v>
       </c>
       <c r="C4" t="n">
-        <v>108.32996867741</v>
+        <v>92.83602640898688</v>
       </c>
       <c r="D4" t="n">
-        <v>130.9582715125948</v>
+        <v>103.4163214176548</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>26.1635763181775</v>
+        <v>28.1516154192773</v>
       </c>
       <c r="C5" t="n">
-        <v>109.6857622569749</v>
+        <v>84.6021084134689</v>
       </c>
       <c r="D5" t="n">
-        <v>86.76195336281188</v>
+        <v>60.94198874112077</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>24.75476836258333</v>
+        <v>27.77364255314227</v>
       </c>
       <c r="C6" t="n">
-        <v>116.6492987231975</v>
+        <v>90.76748399613888</v>
       </c>
       <c r="D6" t="n">
-        <v>37.59504658642736</v>
+        <v>30.67176177607885</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>16.82813739849458</v>
+        <v>20.30156077611979</v>
       </c>
       <c r="C7" t="n">
-        <v>92.10560611702725</v>
+        <v>78.2119126065264</v>
       </c>
       <c r="D7" t="n">
-        <v>29.70375853969149</v>
+        <v>28.68568617038755</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.262789589568655</v>
+        <v>11.59934912567606</v>
       </c>
       <c r="C8" t="n">
-        <v>60.4167537193487</v>
+        <v>61.58503348740241</v>
       </c>
       <c r="D8" t="n">
-        <v>27.28767743954009</v>
+        <v>27.78836876870596</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.214062057254808</v>
+        <v>6.101561981893925</v>
       </c>
       <c r="C9" t="n">
-        <v>36.83124687252333</v>
+        <v>41.60155896745857</v>
       </c>
       <c r="D9" t="n">
-        <v>27.29062268265283</v>
+        <v>27.73437264497238</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.701188845010476</v>
+        <v>3.98589567924205</v>
       </c>
       <c r="C10" t="n">
-        <v>28.18597658892593</v>
+        <v>31.17539834835747</v>
       </c>
       <c r="D10" t="n">
-        <v>28.61303684027329</v>
+        <v>29.04009709162065</v>
       </c>
     </row>
     <row r="11">
@@ -1839,10 +1839,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.020837685967435</v>
+        <v>3.198534020436107</v>
       </c>
       <c r="C11" t="n">
-        <v>26.29905750136355</v>
+        <v>27.54293184264426</v>
       </c>
       <c r="D11" t="n">
         <v>28.43141351498762</v>
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.169662426385451</v>
+        <v>2.386628669023996</v>
       </c>
       <c r="C12" t="n">
-        <v>24.30021917551705</v>
+        <v>25.81898287398687</v>
       </c>
       <c r="D12" t="n">
-        <v>26.90381408717959</v>
+        <v>27.55471281509523</v>
       </c>
     </row>
     <row r="13">
@@ -1870,7 +1870,7 @@
         <v>1.560978849752429</v>
       </c>
       <c r="C13" t="n">
-        <v>22.37403017978481</v>
+        <v>23.15451960466103</v>
       </c>
       <c r="D13" t="n">
         <v>25.49598787928967</v>
@@ -1884,10 +1884,10 @@
         <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>20.58823110575986</v>
+        <v>20.89551813718911</v>
       </c>
       <c r="D14" t="n">
-        <v>24.58296251434014</v>
+        <v>24.89024954576939</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>17.5585576904542</v>
+        <v>18.63357142660446</v>
       </c>
       <c r="D15" t="n">
-        <v>22.57528845915541</v>
+        <v>22.93362637120549</v>
       </c>
     </row>
     <row r="16">
@@ -1912,7 +1912,7 @@
         <v>0.4133157834879072</v>
       </c>
       <c r="C16" t="n">
-        <v>16.53263133951629</v>
+        <v>16.94594712300419</v>
       </c>
       <c r="D16" t="n">
         <v>20.66578917439536</v>
@@ -1929,7 +1929,7 @@
         <v>16.05550195525234</v>
       </c>
       <c r="D17" t="n">
-        <v>17.9443845382232</v>
+        <v>18.41660518396592</v>
       </c>
     </row>
     <row r="18">
@@ -1943,7 +1943,7 @@
         <v>16.05157496443535</v>
       </c>
       <c r="D18" t="n">
-        <v>13.9113649691773</v>
+        <v>14.44641746799181</v>
       </c>
     </row>
     <row r="19">
@@ -1954,7 +1954,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>16.24890625298896</v>
+        <v>16.85071759569225</v>
       </c>
       <c r="D19" t="n">
         <v>9.027170140549421</v>
@@ -1968,10 +1968,10 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>73.30219233758808</v>
+        <v>75.31968386981528</v>
       </c>
       <c r="D20" t="n">
-        <v>6.724971774090649</v>
+        <v>7.397468951499714</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.353650157707104</v>
+        <v>3.792491381505428</v>
       </c>
       <c r="C2" t="n">
-        <v>4.246058820867455</v>
+        <v>2.487748682561417</v>
       </c>
       <c r="D2" t="n">
-        <v>17.92769482725101</v>
+        <v>16.26952295477814</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.3747909433108</v>
+        <v>21.18611545764617</v>
       </c>
       <c r="C3" t="n">
-        <v>42.14642894331557</v>
+        <v>31.9018916495001</v>
       </c>
       <c r="D3" t="n">
-        <v>91.23381415565609</v>
+        <v>80.38550202372883</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>26.43159344143688</v>
+        <v>27.97588258021711</v>
       </c>
       <c r="C4" t="n">
-        <v>124.2450807109551</v>
+        <v>107.0536966618892</v>
       </c>
       <c r="D4" t="n">
-        <v>143.2870591825262</v>
+        <v>117.1490083046591</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>28.59340188618836</v>
+        <v>31.02322745419922</v>
       </c>
       <c r="C5" t="n">
-        <v>152.4408747769235</v>
+        <v>127.4799393964484</v>
       </c>
       <c r="D5" t="n">
-        <v>106.3723637551419</v>
+        <v>79.37430188835464</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>29.26295382048468</v>
+        <v>33.2881194078966</v>
       </c>
       <c r="C6" t="n">
-        <v>143.8594180941022</v>
+        <v>113.751179500261</v>
       </c>
       <c r="D6" t="n">
-        <v>48.26173539306896</v>
+        <v>37.83655652167208</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>15.75017841923158</v>
+        <v>19.3433750167749</v>
       </c>
       <c r="C7" t="n">
-        <v>121.6895914368006</v>
+        <v>101.2083708308037</v>
       </c>
       <c r="D7" t="n">
-        <v>33.11729530735765</v>
+        <v>31.08115056874977</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>7.927612711792993</v>
+        <v>9.846929473595507</v>
       </c>
       <c r="C8" t="n">
-        <v>79.69336989223483</v>
+        <v>78.35819301445918</v>
       </c>
       <c r="D8" t="n">
-        <v>28.03871443328891</v>
+        <v>29.04009709162065</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.437499623195581</v>
+        <v>4.992187076095029</v>
       </c>
       <c r="C9" t="n">
-        <v>41.71249645803847</v>
+        <v>48.7015583645715</v>
       </c>
       <c r="D9" t="n">
-        <v>28.28906009787183</v>
+        <v>29.06562253193106</v>
       </c>
     </row>
     <row r="10">
@@ -2136,10 +2136,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.135301256736813</v>
+        <v>2.2776546738526</v>
       </c>
       <c r="C10" t="n">
-        <v>31.03304493124168</v>
+        <v>33.88011327355743</v>
       </c>
       <c r="D10" t="n">
         <v>29.89421759431538</v>
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.599267010218054</v>
+        <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>28.96450251839364</v>
+        <v>30.74146586308036</v>
       </c>
       <c r="D11" t="n">
-        <v>29.31989518733098</v>
+        <v>29.67528785626833</v>
       </c>
     </row>
     <row r="12">
@@ -2167,10 +2167,10 @@
         <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>20.39482680802324</v>
+        <v>21.69662426385451</v>
       </c>
       <c r="D12" t="n">
-        <v>28.20561154301086</v>
+        <v>28.63954402828795</v>
       </c>
     </row>
     <row r="13">
@@ -2181,10 +2181,10 @@
         <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>16.91060420565131</v>
+        <v>17.17076734727672</v>
       </c>
       <c r="D13" t="n">
-        <v>25.75615102091507</v>
+        <v>26.27647730416588</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>14.74977750860408</v>
+        <v>15.36435157146258</v>
       </c>
       <c r="D14" t="n">
-        <v>18.74450891718435</v>
+        <v>19.0517959486136</v>
       </c>
     </row>
     <row r="15">
@@ -2209,7 +2209,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.97517856995334</v>
+        <v>14.33351648200343</v>
       </c>
       <c r="D15" t="n">
         <v>17.5585576904542</v>
@@ -2226,7 +2226,7 @@
         <v>13.63942085510094</v>
       </c>
       <c r="D16" t="n">
-        <v>15.29268398905256</v>
+        <v>15.70599977254047</v>
       </c>
     </row>
     <row r="17">
@@ -2240,7 +2240,7 @@
         <v>13.69439872653876</v>
       </c>
       <c r="D17" t="n">
-        <v>11.8055161435679</v>
+        <v>12.27773678931061</v>
       </c>
     </row>
     <row r="18">
@@ -2251,7 +2251,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>13.9113649691773</v>
+        <v>14.44641746799181</v>
       </c>
       <c r="D18" t="n">
         <v>7.490734983403163</v>
@@ -2265,10 +2265,10 @@
         <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>63.79200232654924</v>
+        <v>65.59743635465912</v>
       </c>
       <c r="D19" t="n">
-        <v>5.416302084329653</v>
+        <v>6.018113427032947</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.89321048441535</v>
+        <v>3.401755795215198</v>
       </c>
       <c r="C2" t="n">
-        <v>3.646210973572654</v>
+        <v>7.064656479760047</v>
       </c>
       <c r="D2" t="n">
-        <v>14.61724156853076</v>
+        <v>16.57779173391164</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.36926030998382</v>
+        <v>16.95969159086365</v>
       </c>
       <c r="C3" t="n">
-        <v>28.8879261974624</v>
+        <v>19.76749002500953</v>
       </c>
       <c r="D3" t="n">
-        <v>84.88190650917923</v>
+        <v>74.99079838889261</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.5494442236755</v>
+        <v>34.47210713921825</v>
       </c>
       <c r="C4" t="n">
-        <v>114.6092269937726</v>
+        <v>92.55524656557229</v>
       </c>
       <c r="D4" t="n">
-        <v>154.2502357958504</v>
+        <v>129.4522705342802</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>33.62485887045326</v>
+        <v>36.37375244234433</v>
       </c>
       <c r="C5" t="n">
-        <v>189.1091515305419</v>
+        <v>164.4181967687346</v>
       </c>
       <c r="D5" t="n">
-        <v>129.1243668010618</v>
+        <v>100.7518581483289</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>33.52962934314132</v>
+        <v>37.6755498981756</v>
       </c>
       <c r="C6" t="n">
-        <v>190.752597187451</v>
+        <v>156.4984380385756</v>
       </c>
       <c r="D6" t="n">
-        <v>65.77120569831082</v>
+        <v>51.4818678629985</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>23.29589127407256</v>
+        <v>28.02693346083794</v>
       </c>
       <c r="C7" t="n">
-        <v>161.6938468894497</v>
+        <v>132.7686142792259</v>
       </c>
       <c r="D7" t="n">
-        <v>38.0279973240002</v>
+        <v>34.43480072645687</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.18210635137117</v>
+        <v>14.18625432636641</v>
       </c>
       <c r="C8" t="n">
-        <v>114.8252114887069</v>
+        <v>105.4789733442773</v>
       </c>
       <c r="D8" t="n">
-        <v>30.0414797499524</v>
+        <v>30.62561963397925</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.657812019574366</v>
+        <v>6.767186925373262</v>
       </c>
       <c r="C9" t="n">
-        <v>66.34061936677394</v>
+        <v>70.88905648054941</v>
       </c>
       <c r="D9" t="n">
-        <v>29.28749751309084</v>
+        <v>30.17499743772996</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.704714925199962</v>
+        <v>2.989421759431538</v>
       </c>
       <c r="C10" t="n">
-        <v>38.72012945549421</v>
+        <v>44.84132639147307</v>
       </c>
       <c r="D10" t="n">
-        <v>30.17892442854695</v>
+        <v>30.60598467989432</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.599267010218054</v>
+        <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>32.69612554223576</v>
+        <v>35.00617789032851</v>
       </c>
       <c r="D11" t="n">
-        <v>29.852984190737</v>
+        <v>30.03068052520567</v>
       </c>
     </row>
     <row r="12">
@@ -2478,10 +2478,10 @@
         <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>24.5171854181556</v>
+        <v>26.68684784454105</v>
       </c>
       <c r="D12" t="n">
-        <v>28.63954402828795</v>
+        <v>29.29044275620359</v>
       </c>
     </row>
     <row r="13">
@@ -2492,7 +2492,7 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>18.99190933865455</v>
+        <v>19.77239876353076</v>
       </c>
       <c r="D13" t="n">
         <v>26.53664044579129</v>
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>15.97892563432109</v>
+        <v>16.90078672860884</v>
       </c>
       <c r="D14" t="n">
-        <v>19.35908298004286</v>
+        <v>19.97365704290136</v>
       </c>
     </row>
     <row r="15">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.46605242207675</v>
+        <v>14.87936820556466</v>
       </c>
       <c r="D16" t="n">
-        <v>14.87936820556466</v>
+        <v>15.29268398905256</v>
       </c>
     </row>
     <row r="17">
@@ -2551,7 +2551,7 @@
         <v>14.63884001802419</v>
       </c>
       <c r="D17" t="n">
-        <v>10.86107485208246</v>
+        <v>11.33329549782518</v>
       </c>
     </row>
     <row r="18">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>34.3032465340878</v>
+        <v>36.10868056219768</v>
       </c>
       <c r="D19" t="n">
-        <v>3.610868056219768</v>
+        <v>4.212679398923063</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.733766445699867</v>
+        <v>1.984112110282804</v>
       </c>
       <c r="C2" t="n">
-        <v>1.746529165855076</v>
+        <v>3.186753047985146</v>
       </c>
       <c r="D2" t="n">
-        <v>10.19741340401162</v>
+        <v>11.45797745626452</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.62804079327748</v>
+        <v>16.49827016986765</v>
       </c>
       <c r="C3" t="n">
-        <v>24.55841882173396</v>
+        <v>24.5780537758189</v>
       </c>
       <c r="D3" t="n">
-        <v>81.7501313326319</v>
+        <v>74.07286428542184</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.68907338185679</v>
+        <v>38.31368590593603</v>
       </c>
       <c r="C4" t="n">
-        <v>110.7038346262788</v>
+        <v>85.28049607710342</v>
       </c>
       <c r="D4" t="n">
-        <v>163.350055266514</v>
+        <v>138.0160557584251</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>35.29382996767284</v>
+        <v>38.68085954732433</v>
       </c>
       <c r="C5" t="n">
-        <v>223.715758105242</v>
+        <v>191.5389770985527</v>
       </c>
       <c r="D5" t="n">
-        <v>135.5793579564845</v>
+        <v>109.3421505604885</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>27.77364255314227</v>
+        <v>33.40887437551896</v>
       </c>
       <c r="C6" t="n">
-        <v>225.7312861420607</v>
+        <v>192.4431667341641</v>
       </c>
       <c r="D6" t="n">
-        <v>63.59761628110839</v>
+        <v>50.83784136901259</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.366053024963818</v>
+        <v>9.402197763571703</v>
       </c>
       <c r="C7" t="n">
-        <v>161.8735067193268</v>
+        <v>139.4759145946401</v>
       </c>
       <c r="D7" t="n">
-        <v>37.18958478457343</v>
+        <v>34.85400699617026</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>3.922082078466008</v>
+        <v>4.673119072214817</v>
       </c>
       <c r="C8" t="n">
-        <v>83.7823490804228</v>
+        <v>86.28580572625216</v>
       </c>
       <c r="D8" t="n">
-        <v>31.54355373745002</v>
+        <v>32.3780392860598</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.885937339858122</v>
+        <v>2.107812321017901</v>
       </c>
       <c r="C9" t="n">
-        <v>29.50937249425062</v>
+        <v>34.16874709860598</v>
       </c>
       <c r="D9" t="n">
-        <v>31.61718481526852</v>
+        <v>32.50468473990763</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.1388273369263</v>
+        <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>25.62361508084176</v>
+        <v>27.47420950334699</v>
       </c>
       <c r="D10" t="n">
-        <v>23.34596040698915</v>
+        <v>23.48831382410494</v>
       </c>
     </row>
     <row r="11">
@@ -2775,10 +2775,10 @@
         <v>0.7107853378746906</v>
       </c>
       <c r="C11" t="n">
-        <v>19.54659679155399</v>
+        <v>21.32356013624072</v>
       </c>
       <c r="D11" t="n">
-        <v>22.92282714645877</v>
+        <v>23.45591614986479</v>
       </c>
     </row>
     <row r="12">
@@ -2789,7 +2789,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>15.4046032273367</v>
+        <v>16.05550195525234</v>
       </c>
       <c r="D12" t="n">
         <v>21.47965802121596</v>
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.00815708127024</v>
+        <v>13.78864650614645</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>16.3902779224005</v>
       </c>
     </row>
     <row r="14">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.18348900970292</v>
+        <v>12.541826921753</v>
       </c>
       <c r="D15" t="n">
-        <v>12.541826921753</v>
+        <v>12.90016483380309</v>
       </c>
     </row>
     <row r="16">
@@ -2848,7 +2848,7 @@
         <v>12.39947350463721</v>
       </c>
       <c r="D16" t="n">
-        <v>9.092947236733956</v>
+        <v>9.506263020221864</v>
       </c>
     </row>
     <row r="17">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>29.42788743479814</v>
+        <v>31.03304493124168</v>
       </c>
       <c r="D18" t="n">
-        <v>2.675262494072558</v>
+        <v>3.21031499288707</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.542726553999239</v>
+        <v>2.821542902005333</v>
       </c>
       <c r="C2" t="n">
-        <v>5.388813148610742</v>
+        <v>5.6018524004323</v>
       </c>
       <c r="D2" t="n">
-        <v>14.85384276525424</v>
+        <v>9.715375281226436</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>10.49979169691964</v>
+        <v>11.70243263462198</v>
       </c>
       <c r="C3" t="n">
-        <v>15.67851083682156</v>
+        <v>18.18687622117216</v>
       </c>
       <c r="D3" t="n">
-        <v>72.8554971321558</v>
+        <v>67.26935269499145</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.52391878336508</v>
+        <v>35.54417563225577</v>
       </c>
       <c r="C4" t="n">
-        <v>86.79925977557325</v>
+        <v>73.8578615381918</v>
       </c>
       <c r="D4" t="n">
-        <v>165.9408874580214</v>
+        <v>142.725499495697</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>42.38695713085605</v>
+        <v>47.17297718905925</v>
       </c>
       <c r="C5" t="n">
-        <v>216.4262814012094</v>
+        <v>174.849266126357</v>
       </c>
       <c r="D5" t="n">
-        <v>157.1532637573082</v>
+        <v>129.9833960422777</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>35.54221213684728</v>
+        <v>41.53970886209105</v>
       </c>
       <c r="C6" t="n">
-        <v>284.1766904712818</v>
+        <v>248.0709551521968</v>
       </c>
       <c r="D6" t="n">
-        <v>84.08570912103508</v>
+        <v>69.15234479173684</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>15.27108553955913</v>
+        <v>19.52303484665207</v>
       </c>
       <c r="C7" t="n">
-        <v>233.1385725706028</v>
+        <v>201.2190094624262</v>
       </c>
       <c r="D7" t="n">
-        <v>44.43586458961913</v>
+        <v>39.64493579289469</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.090361846519712</v>
+        <v>6.342090169434394</v>
       </c>
       <c r="C8" t="n">
-        <v>135.3535559845078</v>
+        <v>130.0128484734051</v>
       </c>
       <c r="D8" t="n">
-        <v>33.71321616383547</v>
+        <v>34.21390749300134</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.218749811597791</v>
+        <v>2.662499773917349</v>
       </c>
       <c r="C9" t="n">
-        <v>56.02343274284421</v>
+        <v>61.90311974357836</v>
       </c>
       <c r="D9" t="n">
-        <v>32.50468473990763</v>
+        <v>33.50312215512664</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.1388273369263</v>
+        <v>1.423534171157875</v>
       </c>
       <c r="C10" t="n">
-        <v>29.75186417719959</v>
+        <v>32.88363935374691</v>
       </c>
       <c r="D10" t="n">
-        <v>24.62714116103124</v>
+        <v>25.0542014123786</v>
       </c>
     </row>
     <row r="11">
@@ -3086,10 +3086,10 @@
         <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>22.7451308119901</v>
+        <v>25.41057582902019</v>
       </c>
       <c r="D11" t="n">
-        <v>23.63361248433346</v>
+        <v>24.16670148773948</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.7912318963607</v>
+        <v>18.44213062427633</v>
       </c>
       <c r="D12" t="n">
-        <v>21.69662426385451</v>
+        <v>21.91359050649305</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>15.08946221427348</v>
+        <v>16.3902779224005</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>16.3902779224005</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.82791641431633</v>
+        <v>14.13520344574558</v>
       </c>
       <c r="D14" t="n">
-        <v>14.44249047717483</v>
+        <v>14.74977750860408</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.25850274585317</v>
+        <v>13.61684065790326</v>
       </c>
       <c r="D15" t="n">
-        <v>11.82515109765283</v>
+        <v>12.18348900970292</v>
       </c>
     </row>
     <row r="16">
@@ -3156,7 +3156,7 @@
         <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>23.55899965881071</v>
+        <v>23.1456838753228</v>
       </c>
       <c r="D16" t="n">
         <v>8.266315669758143</v>
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33.52766584773283</v>
+        <v>35.41654843070368</v>
       </c>
       <c r="D17" t="n">
-        <v>4.249985811684442</v>
+        <v>4.722206457427158</v>
       </c>
     </row>
     <row r="18">
@@ -3184,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>0.5350524988145117</v>
+        <v>1.070104997629023</v>
       </c>
       <c r="D18" t="n">
         <v>1.070104997629023</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.644427404613408</v>
+        <v>1.93306122966197</v>
       </c>
       <c r="C2" t="n">
-        <v>3.038509144643878</v>
+        <v>2.911863690796039</v>
       </c>
       <c r="D2" t="n">
-        <v>11.20468654856885</v>
+        <v>7.381760988231767</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>9.807659565425636</v>
+        <v>10.95139564087317</v>
       </c>
       <c r="C3" t="n">
-        <v>18.36359080793659</v>
+        <v>20.30745126234527</v>
       </c>
       <c r="D3" t="n">
-        <v>69.75808312525712</v>
+        <v>61.75193059712438</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.68234001664731</v>
+        <v>31.30695254072654</v>
       </c>
       <c r="C4" t="n">
-        <v>68.53580723346982</v>
+        <v>63.21375292874787</v>
       </c>
       <c r="D4" t="n">
-        <v>165.4176159316578</v>
+        <v>144.0783478321491</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>45.82307409571988</v>
+        <v>51.44357970253288</v>
       </c>
       <c r="C5" t="n">
-        <v>202.6327261565417</v>
+        <v>163.9518666092173</v>
       </c>
       <c r="D5" t="n">
-        <v>170.971362694582</v>
+        <v>145.1513980728909</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>41.37870223859457</v>
+        <v>48.46299367243955</v>
       </c>
       <c r="C6" t="n">
-        <v>317.2635515998078</v>
+        <v>271.0546506563189</v>
       </c>
       <c r="D6" t="n">
-        <v>100.5486363735499</v>
+        <v>82.11337798320324</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>13.71403368062369</v>
+        <v>18.92416874706152</v>
       </c>
       <c r="C7" t="n">
-        <v>293.6240486292488</v>
+        <v>259.30902112271</v>
       </c>
       <c r="D7" t="n">
-        <v>49.94543270585223</v>
+        <v>44.55563780953724</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.172427743048944</v>
+        <v>5.257258956241669</v>
       </c>
       <c r="C8" t="n">
-        <v>177.0778334149972</v>
+        <v>170.5688461358408</v>
       </c>
       <c r="D8" t="n">
-        <v>35.04839304161113</v>
+        <v>36.13322425480386</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.664062358698343</v>
+        <v>1.996874830438012</v>
       </c>
       <c r="C9" t="n">
-        <v>64.34374453633593</v>
+        <v>73.99530621678632</v>
       </c>
       <c r="D9" t="n">
-        <v>31.94999728700819</v>
+        <v>33.05937219280708</v>
       </c>
     </row>
     <row r="10">
@@ -3383,10 +3383,10 @@
         <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>30.46363126277853</v>
+        <v>34.30717352490479</v>
       </c>
       <c r="D10" t="n">
-        <v>25.0542014123786</v>
+        <v>25.76596849795754</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>22.7451308119901</v>
+        <v>24.6997904911455</v>
       </c>
       <c r="D11" t="n">
-        <v>23.98900515327081</v>
+        <v>24.52209415667683</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>16.70640068316797</v>
+        <v>18.44213062427633</v>
       </c>
       <c r="D12" t="n">
-        <v>20.17786056538469</v>
+        <v>20.39482680802324</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>11.44717823151781</v>
+        <v>11.70734137314322</v>
       </c>
       <c r="D13" t="n">
-        <v>16.3902779224005</v>
+        <v>16.65044106402591</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.06233313145306</v>
+        <v>11.36962016288231</v>
       </c>
       <c r="D14" t="n">
-        <v>11.06233313145306</v>
+        <v>11.67690719431156</v>
       </c>
     </row>
     <row r="15">
@@ -3453,7 +3453,7 @@
         <v>1.075013736150257</v>
       </c>
       <c r="C15" t="n">
-        <v>19.70858516275472</v>
+        <v>19.35024725070463</v>
       </c>
       <c r="D15" t="n">
         <v>6.808420328951629</v>
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.51878906066559</v>
+        <v>30.17205219461722</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>3.719842051391165</v>
       </c>
     </row>
     <row r="17">
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>0.4722206457427158</v>
       </c>
       <c r="D17" t="n">
         <v>0.4722206457427158</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.057743188101315</v>
+        <v>3.229949946972006</v>
       </c>
       <c r="C2" t="n">
-        <v>6.829037030740813</v>
+        <v>6.444191930676063</v>
       </c>
       <c r="D2" t="n">
-        <v>13.1897804065559</v>
+        <v>14.31584502332699</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>7.795076771719675</v>
+        <v>8.816094384136358</v>
       </c>
       <c r="C3" t="n">
-        <v>15.39380400258999</v>
+        <v>15.99757884070178</v>
       </c>
       <c r="D3" t="n">
-        <v>63.64179492779948</v>
+        <v>54.51645001682538</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>23.39406604449724</v>
+        <v>26.30396623988479</v>
       </c>
       <c r="C4" t="n">
-        <v>58.51707191163113</v>
+        <v>57.29185077673112</v>
       </c>
       <c r="D4" t="n">
-        <v>162.673631098288</v>
+        <v>142.2277534096439</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>44.59588946541137</v>
+        <v>49.79915229791947</v>
       </c>
       <c r="C5" t="n">
-        <v>170.529576227671</v>
+        <v>142.6233977344554</v>
       </c>
       <c r="D5" t="n">
-        <v>185.525772410041</v>
+        <v>159.7303514809561</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>48.3422387048172</v>
+        <v>57.03659637362695</v>
       </c>
       <c r="C6" t="n">
-        <v>320.2824257903667</v>
+        <v>267.7540148746411</v>
       </c>
       <c r="D6" t="n">
-        <v>121.6807557074624</v>
+        <v>101.9976959850181</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>25.51169584255761</v>
+        <v>32.69808903764427</v>
       </c>
       <c r="C7" t="n">
-        <v>358.1818141651105</v>
+        <v>318.1775587124615</v>
       </c>
       <c r="D7" t="n">
-        <v>61.14422876819559</v>
+        <v>53.95783557310894</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>7.260024272905162</v>
+        <v>10.2641722479004</v>
       </c>
       <c r="C8" t="n">
-        <v>258.2732772947296</v>
+        <v>239.6642495607313</v>
       </c>
       <c r="D8" t="n">
-        <v>38.38633523605029</v>
+        <v>38.80357801035517</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.32968730217768</v>
+        <v>2.884374755077128</v>
       </c>
       <c r="C9" t="n">
-        <v>117.9265524864226</v>
+        <v>127.0234267139735</v>
       </c>
       <c r="D9" t="n">
-        <v>32.9484347022272</v>
+        <v>34.27968458918587</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.7117670855789376</v>
+        <v>0.8541205026947251</v>
       </c>
       <c r="C10" t="n">
-        <v>45.98015372839937</v>
+        <v>53.52488483553611</v>
       </c>
       <c r="D10" t="n">
-        <v>26.1930287493049</v>
+        <v>27.3318560862312</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>27.18753917370691</v>
+        <v>30.20837685967435</v>
       </c>
       <c r="D11" t="n">
-        <v>24.52209415667683</v>
+        <v>24.6997904911455</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>19.30999559483051</v>
+        <v>21.47965802121596</v>
       </c>
       <c r="D12" t="n">
-        <v>20.61179305066178</v>
+        <v>20.82875929330033</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.26832022289564</v>
+        <v>14.04880964777186</v>
       </c>
       <c r="D13" t="n">
-        <v>16.65044106402591</v>
+        <v>16.91060420565131</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.67690719431156</v>
+        <v>11.98419422574081</v>
       </c>
       <c r="D14" t="n">
-        <v>11.06233313145306</v>
+        <v>11.98419422574081</v>
       </c>
     </row>
     <row r="15">
@@ -3764,7 +3764,7 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>20.78359889890498</v>
+        <v>19.70858516275472</v>
       </c>
       <c r="D15" t="n">
         <v>6.450082416901544</v>
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>27.27884171020187</v>
+        <v>29.75873641112932</v>
       </c>
       <c r="D16" t="n">
-        <v>2.89321048441535</v>
+        <v>3.306526267903257</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.393320976504477</v>
+        <v>4.870450360768427</v>
       </c>
       <c r="C2" t="n">
-        <v>5.475206946584461</v>
+        <v>6.939974521320702</v>
       </c>
       <c r="D2" t="n">
-        <v>22.5900146747191</v>
+        <v>8.588328916751097</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.487347771933918</v>
+        <v>2.284526907782328</v>
       </c>
       <c r="C2" t="n">
-        <v>3.932881303212722</v>
+        <v>3.607922813107028</v>
       </c>
       <c r="D2" t="n">
-        <v>9.81256830394687</v>
+        <v>10.53611636197677</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>10.37707323388879</v>
+        <v>12.16385405561798</v>
       </c>
       <c r="C3" t="n">
-        <v>20.9455872701057</v>
+        <v>21.24502031990098</v>
       </c>
       <c r="D3" t="n">
-        <v>68.99231991594461</v>
+        <v>60.06332454581985</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.3489877655599</v>
+        <v>37.30543101367455</v>
       </c>
       <c r="C4" t="n">
-        <v>88.10105723140452</v>
+        <v>81.86008707550754</v>
       </c>
       <c r="D4" t="n">
-        <v>168.3785670076662</v>
+        <v>147.4732313934346</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>28.05344064885261</v>
+        <v>33.96847056693964</v>
       </c>
       <c r="C5" t="n">
-        <v>264.7037247575463</v>
+        <v>219.248806050919</v>
       </c>
       <c r="D5" t="n">
-        <v>169.9159839125167</v>
+        <v>146.9921750183537</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>15.81890075852886</v>
+        <v>20.28683456055609</v>
       </c>
       <c r="C6" t="n">
-        <v>295.5276574277834</v>
+        <v>267.2709950041517</v>
       </c>
       <c r="D6" t="n">
-        <v>94.63164296005432</v>
+        <v>80.54356340411259</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>4.790928796724434</v>
+        <v>6.767186925373263</v>
       </c>
       <c r="C7" t="n">
-        <v>181.6360880058151</v>
+        <v>168.520920424782</v>
       </c>
       <c r="D7" t="n">
-        <v>34.73423377625215</v>
+        <v>34.6743471662931</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.585522542358599</v>
+        <v>2.002765316663493</v>
       </c>
       <c r="C8" t="n">
-        <v>86.86994561027902</v>
+        <v>93.6292785540183</v>
       </c>
       <c r="D8" t="n">
-        <v>24.28352946454485</v>
+        <v>25.20146356801562</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.4437499623195582</v>
+        <v>0.5546874528994477</v>
       </c>
       <c r="C9" t="n">
-        <v>35.05624702324509</v>
+        <v>40.82499653339935</v>
       </c>
       <c r="D9" t="n">
-        <v>19.96874830438012</v>
+        <v>20.85624822901923</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>21.21065915025234</v>
+        <v>23.63066724122073</v>
       </c>
       <c r="D10" t="n">
-        <v>19.21771131063132</v>
+        <v>19.3600647277471</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>15.45958109877452</v>
+        <v>17.23654444346124</v>
       </c>
       <c r="D11" t="n">
-        <v>16.52575910558656</v>
+        <v>16.70345544005523</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>10.63134588928871</v>
+        <v>11.28224461720434</v>
       </c>
       <c r="D12" t="n">
-        <v>13.4519070435898</v>
+        <v>13.66887328622834</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>9.626036240139976</v>
+        <v>9.886199381765381</v>
       </c>
       <c r="D13" t="n">
-        <v>9.105709956889166</v>
+        <v>9.886199381765381</v>
       </c>
     </row>
     <row r="14">
@@ -4372,7 +4372,7 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>17.20807376003809</v>
+        <v>16.28621266575034</v>
       </c>
       <c r="D14" t="n">
         <v>5.223879534297279</v>
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>22.93362637120549</v>
+        <v>25.083653843506</v>
       </c>
       <c r="D15" t="n">
-        <v>2.150027472300515</v>
+        <v>2.5083653843506</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.766786014745764</v>
+        <v>6.94095626902495</v>
       </c>
       <c r="C2" t="n">
-        <v>5.584180941755857</v>
+        <v>3.787582642984194</v>
       </c>
       <c r="D2" t="n">
-        <v>33.54337381100077</v>
+        <v>10.94943214546467</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>9.341329405908402</v>
+        <v>10.35252954128262</v>
       </c>
       <c r="C3" t="n">
-        <v>13.79355524466769</v>
+        <v>17.48492661263569</v>
       </c>
       <c r="D3" t="n">
-        <v>22.11386703815941</v>
+        <v>10.34762080276138</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>1.008254892261474</v>
       </c>
       <c r="C4" t="n">
-        <v>1.493238258159399</v>
+        <v>1.454950097693773</v>
       </c>
       <c r="D4" t="n">
         <v>19.62906359871073</v>
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.736932672990861</v>
+        <v>4.68784528777852</v>
       </c>
       <c r="C5" t="n">
-        <v>9.449321653375552</v>
+        <v>9.424777960769381</v>
       </c>
       <c r="D5" t="n">
         <v>28.49522711576368</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.050331174823848</v>
+        <v>8.130834486572086</v>
       </c>
       <c r="C6" t="n">
-        <v>18.27425176685013</v>
+        <v>18.47551004622073</v>
       </c>
       <c r="D6" t="n">
-        <v>32.8453511932813</v>
+        <v>32.52333794628834</v>
       </c>
     </row>
     <row r="7">
@@ -4588,7 +4588,7 @@
         <v>20.9603134856694</v>
       </c>
       <c r="D7" t="n">
-        <v>32.21899615797182</v>
+        <v>32.69808903764427</v>
       </c>
     </row>
     <row r="8">
@@ -4596,7 +4596,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.845546815263761</v>
+        <v>8.762098260402782</v>
       </c>
       <c r="C8" t="n">
         <v>21.69662426385451</v>
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.764061755811273</v>
+        <v>8.874999246391162</v>
       </c>
       <c r="C9" t="n">
         <v>22.74218556887735</v>
       </c>
       <c r="D9" t="n">
-        <v>39.60468413702056</v>
+        <v>39.2718716652809</v>
       </c>
     </row>
     <row r="10">
@@ -4630,7 +4630,7 @@
         <v>25.62361508084176</v>
       </c>
       <c r="D10" t="n">
-        <v>50.1084028247572</v>
+        <v>50.67781649322036</v>
       </c>
     </row>
     <row r="11">
@@ -4697,7 +4697,7 @@
         <v>5.375068680751286</v>
       </c>
       <c r="C15" t="n">
-        <v>25.80032966760617</v>
+        <v>26.15866757965626</v>
       </c>
       <c r="D15" t="n">
         <v>42.28387362191012</v>
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39643286038406</v>
+        <v>13.3985002576928</v>
       </c>
       <c r="C21" t="n">
-        <v>70.13426615142244</v>
+        <v>70.14508958439173</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576050924751066</v>
+        <v>1.576294147963859</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.929355223023235</v>
+        <v>4.322635141798706</v>
       </c>
       <c r="C2" t="n">
-        <v>6.729880512611885</v>
+        <v>3.499930565639879</v>
       </c>
       <c r="D2" t="n">
-        <v>32.21703266256333</v>
+        <v>14.54753748152924</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.66378462125786</v>
+        <v>18.48140053244621</v>
       </c>
       <c r="C3" t="n">
-        <v>18.78574232076272</v>
+        <v>15.76686813020378</v>
       </c>
       <c r="D3" t="n">
-        <v>44.94440990041898</v>
+        <v>17.04314014572463</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>10.98870205363455</v>
+        <v>12.12458414744811</v>
       </c>
       <c r="C4" t="n">
-        <v>21.58175978245763</v>
+        <v>27.60576369571606</v>
       </c>
       <c r="D4" t="n">
-        <v>26.66132240423063</v>
+        <v>20.49692856926491</v>
       </c>
     </row>
     <row r="5">
@@ -4868,10 +4868,10 @@
         <v>3.067961575771283</v>
       </c>
       <c r="C5" t="n">
-        <v>5.522330836388309</v>
+        <v>5.399612373357458</v>
       </c>
       <c r="D5" t="n">
-        <v>29.40334374219198</v>
+        <v>29.10881943091793</v>
       </c>
     </row>
     <row r="6">
@@ -4882,10 +4882,10 @@
         <v>7.446556336712058</v>
       </c>
       <c r="C6" t="n">
-        <v>16.50317890838889</v>
+        <v>16.54343056426301</v>
       </c>
       <c r="D6" t="n">
-        <v>34.57617239586842</v>
+        <v>34.77743067523902</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.581857593448868</v>
+        <v>9.521970983489814</v>
       </c>
       <c r="C7" t="n">
-        <v>24.07441720354028</v>
+        <v>24.49362347325367</v>
       </c>
       <c r="D7" t="n">
-        <v>34.97378021608837</v>
+        <v>35.27321326588365</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.513135254151592</v>
+        <v>9.596583809012571</v>
       </c>
       <c r="C8" t="n">
         <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>36.63391558396972</v>
+        <v>36.80081269369168</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.429686699290611</v>
+        <v>9.318749208710722</v>
       </c>
       <c r="C9" t="n">
-        <v>25.73749781453438</v>
+        <v>25.5156228333746</v>
       </c>
       <c r="D9" t="n">
-        <v>40.60312155223957</v>
+        <v>40.27030908049991</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.825911861178826</v>
+        <v>8.968265278294615</v>
       </c>
       <c r="C10" t="n">
         <v>27.3318560862312</v>
       </c>
       <c r="D10" t="n">
-        <v>49.68134257340984</v>
+        <v>50.1084028247572</v>
       </c>
     </row>
     <row r="11">
@@ -4949,7 +4949,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7.640942382152923</v>
+        <v>7.463246047684251</v>
       </c>
       <c r="C11" t="n">
         <v>29.49759152179966</v>
@@ -4966,7 +4966,7 @@
         <v>6.075054793879263</v>
       </c>
       <c r="C12" t="n">
-        <v>28.8565102709265</v>
+        <v>29.29044275620359</v>
       </c>
       <c r="D12" t="n">
         <v>44.69504598354028</v>
@@ -4983,7 +4983,7 @@
         <v>26.79680358741669</v>
       </c>
       <c r="D13" t="n">
-        <v>44.74806035956962</v>
+        <v>44.22773407631881</v>
       </c>
     </row>
     <row r="14">
@@ -4997,7 +4997,7 @@
         <v>25.50482360862789</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>45.47848065152925</v>
       </c>
     </row>
     <row r="15">
@@ -5005,7 +5005,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>5.0167307687012</v>
       </c>
       <c r="C15" t="n">
         <v>26.51700549170635</v>
@@ -5022,10 +5022,10 @@
         <v>5.373105185342793</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>29.34542062764141</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>40.5049467818149</v>
       </c>
     </row>
     <row r="17">
@@ -5039,7 +5039,7 @@
         <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
-        <v>36.36098972218912</v>
+        <v>36.83321036793183</v>
       </c>
     </row>
     <row r="18">
@@ -5050,7 +5050,7 @@
         <v>5.885577486959628</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>34.77841242294325</v>
       </c>
       <c r="D18" t="n">
         <v>31.56809743005619</v>
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.43545028491652</v>
+        <v>15.44338816602797</v>
       </c>
       <c r="C21" t="n">
-        <v>86.113564747429</v>
+        <v>86.15784976836656</v>
       </c>
       <c r="D21" t="n">
-        <v>3.249568481035056</v>
+        <v>3.251239613900625</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.191080949429634</v>
+        <v>4.111559385385641</v>
       </c>
       <c r="C2" t="n">
-        <v>7.890306299031615</v>
+        <v>3.033600406122644</v>
       </c>
       <c r="D2" t="n">
-        <v>28.49915410658066</v>
+        <v>17.33668270929442</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.46390900021901</v>
+        <v>16.49827016986765</v>
       </c>
       <c r="C3" t="n">
-        <v>23.18397203578843</v>
+        <v>14.46114368355552</v>
       </c>
       <c r="D3" t="n">
-        <v>60.28912651779663</v>
+        <v>24.72531593145592</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>21.95187866695868</v>
+        <v>25.4233385491754</v>
       </c>
       <c r="C4" t="n">
-        <v>36.09297259892973</v>
+        <v>34.34447993766616</v>
       </c>
       <c r="D4" t="n">
-        <v>43.16351956491527</v>
+        <v>24.44060909722434</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>9.989282890711298</v>
+        <v>11.04466167277662</v>
       </c>
       <c r="C5" t="n">
-        <v>25.08365384350601</v>
+        <v>31.83316931020283</v>
       </c>
       <c r="D5" t="n">
-        <v>32.20132469929538</v>
+        <v>29.82058651649687</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.957245069369646</v>
+        <v>5.916993413495527</v>
       </c>
       <c r="C6" t="n">
-        <v>12.3572583533546</v>
+        <v>12.19625172985813</v>
       </c>
       <c r="D6" t="n">
-        <v>36.54850353370026</v>
+        <v>36.6290068454485</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.521970983489814</v>
+        <v>9.581857593448868</v>
       </c>
       <c r="C7" t="n">
-        <v>24.25407703341745</v>
+        <v>24.49362347325367</v>
       </c>
       <c r="D7" t="n">
-        <v>37.4890178343687</v>
+        <v>37.42913122440964</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.43106935762236</v>
+        <v>10.34762080276138</v>
       </c>
       <c r="C8" t="n">
-        <v>29.29044275620359</v>
+        <v>29.87458264023044</v>
       </c>
       <c r="D8" t="n">
-        <v>37.88564390688441</v>
+        <v>38.55323234577224</v>
       </c>
     </row>
     <row r="9">
@@ -5235,10 +5235,10 @@
         <v>10.09531164276995</v>
       </c>
       <c r="C9" t="n">
-        <v>29.7312474754104</v>
+        <v>29.39843500367073</v>
       </c>
       <c r="D9" t="n">
-        <v>41.49062147687869</v>
+        <v>41.26874649571891</v>
       </c>
     </row>
     <row r="10">
@@ -5252,7 +5252,7 @@
         <v>29.89421759431538</v>
       </c>
       <c r="D10" t="n">
-        <v>48.9695754878309</v>
+        <v>49.25428232206248</v>
       </c>
     </row>
     <row r="11">
@@ -5266,7 +5266,7 @@
         <v>31.45225120095506</v>
       </c>
       <c r="D11" t="n">
-        <v>49.57727731675966</v>
+        <v>49.75497365122833</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.725953521794898</v>
+        <v>6.508987279156352</v>
       </c>
       <c r="C12" t="n">
-        <v>31.46010518258904</v>
+        <v>32.11100391050467</v>
       </c>
       <c r="D12" t="n">
-        <v>46.2138096820101</v>
+        <v>45.77987719673301</v>
       </c>
     </row>
     <row r="13">
@@ -5308,7 +5308,7 @@
         <v>27.9631198600619</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>45.7857676829585</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.30005494460103</v>
+        <v>4.658392856651115</v>
       </c>
       <c r="C15" t="n">
         <v>27.5920192278566</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>43.35888735806038</v>
       </c>
     </row>
     <row r="16">
@@ -5333,10 +5333,10 @@
         <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>29.75873641112932</v>
       </c>
       <c r="D16" t="n">
-        <v>41.33157834879071</v>
+        <v>40.91826256530281</v>
       </c>
     </row>
     <row r="17">
@@ -5347,10 +5347,10 @@
         <v>5.194427103169874</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>32.58322455624739</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>37.30543101367455</v>
       </c>
     </row>
     <row r="18">
@@ -5375,7 +5375,7 @@
         <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>37.31230324760427</v>
       </c>
       <c r="D19" t="n">
         <v>24.67426505083508</v>
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.72352431963762</v>
+        <v>16.7411718735065</v>
       </c>
       <c r="C21" t="n">
-        <v>102.0134983497895</v>
+        <v>102.1211484283897</v>
       </c>
       <c r="D21" t="n">
-        <v>4.180881079909405</v>
+        <v>5.02235156205195</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.247040568571702</v>
+        <v>4.417864669110647</v>
       </c>
       <c r="C2" t="n">
-        <v>9.428704951586367</v>
+        <v>7.330710107610932</v>
       </c>
       <c r="D2" t="n">
-        <v>22.14920995551229</v>
+        <v>26.40606800112646</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.28581175512284</v>
+        <v>15.17781950765569</v>
       </c>
       <c r="C3" t="n">
-        <v>27.37112599440108</v>
+        <v>12.88543861823939</v>
       </c>
       <c r="D3" t="n">
-        <v>68.53580723346982</v>
+        <v>32.39767424014475</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.0569667290421</v>
+        <v>28.8692729910817</v>
       </c>
       <c r="C4" t="n">
-        <v>47.75809882079034</v>
+        <v>35.40378571054848</v>
       </c>
       <c r="D4" t="n">
-        <v>62.56285420083224</v>
+        <v>30.71986741358695</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>21.42664364518664</v>
+        <v>24.86276061005048</v>
       </c>
       <c r="C5" t="n">
-        <v>47.51658888554563</v>
+        <v>49.23464736797755</v>
       </c>
       <c r="D5" t="n">
-        <v>39.68715094417732</v>
+        <v>32.0295188510522</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>9.700649065662736</v>
+        <v>10.465430527271</v>
       </c>
       <c r="C6" t="n">
-        <v>26.56609287691869</v>
+        <v>32.28182801104362</v>
       </c>
       <c r="D6" t="n">
-        <v>38.84284791852506</v>
+        <v>37.8768081775462</v>
       </c>
     </row>
     <row r="7">
@@ -5518,10 +5518,10 @@
         <v>8.683558444063037</v>
       </c>
       <c r="C7" t="n">
-        <v>21.08008670558751</v>
+        <v>21.19985992550562</v>
       </c>
       <c r="D7" t="n">
-        <v>39.52516257297658</v>
+        <v>40.00425545264903</v>
       </c>
     </row>
     <row r="8">
@@ -5532,10 +5532,10 @@
         <v>10.76486357706628</v>
       </c>
       <c r="C8" t="n">
-        <v>31.37665662772806</v>
+        <v>31.87734795689393</v>
       </c>
       <c r="D8" t="n">
-        <v>39.8884092235479</v>
+        <v>40.38910055271378</v>
       </c>
     </row>
     <row r="9">
@@ -5546,10 +5546,10 @@
         <v>10.76093658624928</v>
       </c>
       <c r="C9" t="n">
-        <v>33.61405964570653</v>
+        <v>33.9468721174462</v>
       </c>
       <c r="D9" t="n">
-        <v>42.3781214015178</v>
+        <v>41.93437143919824</v>
       </c>
     </row>
     <row r="10">
@@ -5560,10 +5560,10 @@
         <v>9.964739198105127</v>
       </c>
       <c r="C10" t="n">
-        <v>33.59540643932586</v>
+        <v>33.45305302221006</v>
       </c>
       <c r="D10" t="n">
-        <v>48.54251523648354</v>
+        <v>49.25428232206248</v>
       </c>
     </row>
     <row r="11">
@@ -5577,7 +5577,7 @@
         <v>33.93999988351647</v>
       </c>
       <c r="D11" t="n">
-        <v>50.6434553235717</v>
+        <v>50.46575898910303</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.376852249710534</v>
+        <v>7.159886007071988</v>
       </c>
       <c r="C12" t="n">
-        <v>33.84673385161303</v>
+        <v>34.28066633689012</v>
       </c>
       <c r="D12" t="n">
-        <v>47.08167465256428</v>
+        <v>47.29864089520282</v>
       </c>
     </row>
     <row r="13">
@@ -5602,7 +5602,7 @@
         <v>5.723589115758904</v>
       </c>
       <c r="C13" t="n">
-        <v>33.04071898642641</v>
+        <v>33.30088212805181</v>
       </c>
       <c r="D13" t="n">
         <v>45.78871292607123</v>
@@ -5630,10 +5630,10 @@
         <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>29.02537087605695</v>
+        <v>29.38370878810703</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>44.07556318216055</v>
       </c>
     </row>
     <row r="16">
@@ -5644,10 +5644,10 @@
         <v>4.546473618366978</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>30.17205219461722</v>
       </c>
       <c r="D16" t="n">
-        <v>41.74489413227862</v>
+        <v>40.91826256530281</v>
       </c>
     </row>
     <row r="17">
@@ -5658,10 +5658,10 @@
         <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>33.0554452019901</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>37.77765165941727</v>
       </c>
     </row>
     <row r="18">
@@ -5672,7 +5672,7 @@
         <v>4.815472489330605</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>35.31346492175777</v>
       </c>
       <c r="D18" t="n">
         <v>32.1031499288707</v>
@@ -5700,7 +5700,7 @@
         <v>4.707480241863455</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>39.67733346713483</v>
       </c>
       <c r="D20" t="n">
         <v>16.13993225781756</v>
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.04264308835436</v>
+        <v>18.0751107693642</v>
       </c>
       <c r="C21" t="n">
-        <v>117.7067668145023</v>
+        <v>117.9185797810903</v>
       </c>
       <c r="D21" t="n">
-        <v>6.014214362784787</v>
+        <v>6.885756483567316</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.232715263635499</v>
+        <v>4.784056562794707</v>
       </c>
       <c r="C2" t="n">
-        <v>11.03877118655113</v>
+        <v>9.740900721536853</v>
       </c>
       <c r="D2" t="n">
-        <v>26.8851608807989</v>
+        <v>29.46813909067226</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.22905031472577</v>
+        <v>13.55302705712722</v>
       </c>
       <c r="C3" t="n">
-        <v>30.55689729468197</v>
+        <v>20.68051538995906</v>
       </c>
       <c r="D3" t="n">
-        <v>65.98326320242812</v>
+        <v>42.57348919466293</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>20.73942025221387</v>
+        <v>21.19887817780138</v>
       </c>
       <c r="C4" t="n">
-        <v>49.07265899677682</v>
+        <v>28.15456066239003</v>
       </c>
       <c r="D4" t="n">
-        <v>71.31808022730529</v>
+        <v>34.2423781764245</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>18.87409961414493</v>
+        <v>21.25483779694345</v>
       </c>
       <c r="C5" t="n">
-        <v>51.51721078035138</v>
+        <v>42.87783098297945</v>
       </c>
       <c r="D5" t="n">
-        <v>42.11697651218817</v>
+        <v>29.15790681613028</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>10.50568218314512</v>
+        <v>12.15600007398401</v>
       </c>
       <c r="C6" t="n">
-        <v>34.77743067523902</v>
+        <v>38.52083467153211</v>
       </c>
       <c r="D6" t="n">
-        <v>32.96610616090365</v>
+        <v>30.43025184083414</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.150248456478767</v>
+        <v>5.389794896314989</v>
       </c>
       <c r="C7" t="n">
-        <v>19.22360179685679</v>
+        <v>21.97838585497334</v>
       </c>
       <c r="D7" t="n">
-        <v>30.84160412891355</v>
+        <v>31.38058361854505</v>
       </c>
     </row>
     <row r="8">
@@ -5843,10 +5843,10 @@
         <v>4.840016181936775</v>
       </c>
       <c r="C8" t="n">
-        <v>18.35868206941536</v>
+        <v>18.77592484372025</v>
       </c>
       <c r="D8" t="n">
-        <v>30.0414797499524</v>
+        <v>30.12492830481337</v>
       </c>
     </row>
     <row r="9">
@@ -5857,10 +5857,10 @@
         <v>4.881249585515139</v>
       </c>
       <c r="C9" t="n">
-        <v>21.85468564423824</v>
+        <v>22.18749811597791</v>
       </c>
       <c r="D9" t="n">
-        <v>30.06405994715006</v>
+        <v>30.28593492830985</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.270602513473626</v>
+        <v>4.412955930589413</v>
       </c>
       <c r="C10" t="n">
         <v>21.35301256736813</v>
       </c>
       <c r="D10" t="n">
-        <v>33.45305302221006</v>
+        <v>33.73775985644164</v>
       </c>
     </row>
     <row r="11">
@@ -5885,10 +5885,10 @@
         <v>3.731623023842126</v>
       </c>
       <c r="C11" t="n">
-        <v>20.43507846389736</v>
+        <v>20.61277479836603</v>
       </c>
       <c r="D11" t="n">
-        <v>34.65078522139116</v>
+        <v>34.29539255245382</v>
       </c>
     </row>
     <row r="12">
@@ -5899,10 +5899,10 @@
         <v>3.037527396939631</v>
       </c>
       <c r="C12" t="n">
-        <v>19.96089432274615</v>
+        <v>20.17786056538469</v>
       </c>
       <c r="D12" t="n">
-        <v>31.67707142522758</v>
+        <v>32.32797015314322</v>
       </c>
     </row>
     <row r="13">
@@ -5913,10 +5913,10 @@
         <v>2.341468274628643</v>
       </c>
       <c r="C13" t="n">
-        <v>18.73174619702914</v>
+        <v>18.99190933865455</v>
       </c>
       <c r="D13" t="n">
-        <v>30.43908757017236</v>
+        <v>30.17892442854696</v>
       </c>
     </row>
     <row r="14">
@@ -5927,10 +5927,10 @@
         <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>17.51536079146734</v>
+        <v>17.8226478228966</v>
       </c>
       <c r="D14" t="n">
-        <v>29.49955501720816</v>
+        <v>29.80684204863741</v>
       </c>
     </row>
     <row r="15">
@@ -5941,10 +5941,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>15.76686813020377</v>
+        <v>16.12520604225386</v>
       </c>
       <c r="D15" t="n">
-        <v>27.95035713990669</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -5972,7 +5972,7 @@
         <v>16.52772260099505</v>
       </c>
       <c r="D17" t="n">
-        <v>23.61103228713579</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -5983,7 +5983,7 @@
         <v>1.070104997629023</v>
       </c>
       <c r="C18" t="n">
-        <v>17.12167996206437</v>
+        <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
         <v>20.33199495495144</v>
@@ -6011,7 +6011,7 @@
         <v>1.34499435481813</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.08745766113597</v>
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.049601222762625</v>
+        <v>7.068242384791311</v>
       </c>
       <c r="C21" t="n">
-        <v>66.09001146339961</v>
+        <v>67.14830265551744</v>
       </c>
       <c r="D21" t="n">
-        <v>4.406000764226641</v>
+        <v>5.301181788593483</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.220533380557038</v>
+        <v>4.468915549731481</v>
       </c>
       <c r="C2" t="n">
-        <v>5.237624002156734</v>
+        <v>4.968625131193107</v>
       </c>
       <c r="D2" t="n">
-        <v>21.50812870463912</v>
+        <v>25.40075835197772</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.29210315197582</v>
+        <v>15.64414966717292</v>
       </c>
       <c r="C3" t="n">
-        <v>38.96065764303467</v>
+        <v>32.27495577711389</v>
       </c>
       <c r="D3" t="n">
-        <v>72.62478642165779</v>
+        <v>57.81021356457343</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>24.0704902127233</v>
+        <v>24.87454158250144</v>
       </c>
       <c r="C4" t="n">
-        <v>65.65143247839271</v>
+        <v>43.54640116957152</v>
       </c>
       <c r="D4" t="n">
-        <v>88.6626169182337</v>
+        <v>49.3406761200362</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>25.86905200690346</v>
+        <v>27.66074156715389</v>
       </c>
       <c r="C5" t="n">
-        <v>75.5209421491859</v>
+        <v>48.79286090106649</v>
       </c>
       <c r="D5" t="n">
-        <v>59.98478472948013</v>
+        <v>35.36746104549135</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>19.11953654020664</v>
+        <v>22.13841073076558</v>
       </c>
       <c r="C6" t="n">
-        <v>62.47056991663305</v>
+        <v>56.63407981488576</v>
       </c>
       <c r="D6" t="n">
-        <v>39.40637110076273</v>
+        <v>33.48937768726721</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.342311153612647</v>
+        <v>10.77958979262998</v>
       </c>
       <c r="C7" t="n">
-        <v>37.36924461445059</v>
+        <v>42.33983324105218</v>
       </c>
       <c r="D7" t="n">
-        <v>33.59638818703009</v>
+        <v>33.77604801690726</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.507604620824606</v>
+        <v>5.674501730546564</v>
       </c>
       <c r="C8" t="n">
-        <v>22.86490403190821</v>
+        <v>25.36836067773758</v>
       </c>
       <c r="D8" t="n">
-        <v>32.12769362147687</v>
+        <v>32.04424506661589</v>
       </c>
     </row>
     <row r="9">
@@ -6168,10 +6168,10 @@
         <v>5.214062057254808</v>
       </c>
       <c r="C9" t="n">
-        <v>23.07499804061703</v>
+        <v>23.62968549351647</v>
       </c>
       <c r="D9" t="n">
-        <v>31.39530983410874</v>
+        <v>31.72812230584841</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.697662764820988</v>
+        <v>4.840016181936776</v>
       </c>
       <c r="C10" t="n">
-        <v>24.62714116103124</v>
+        <v>24.91184799526281</v>
       </c>
       <c r="D10" t="n">
-        <v>33.59540643932586</v>
+        <v>34.16482010778901</v>
       </c>
     </row>
     <row r="11">
@@ -6196,10 +6196,10 @@
         <v>4.08701569277947</v>
       </c>
       <c r="C11" t="n">
-        <v>23.10052348092744</v>
+        <v>23.45591614986479</v>
       </c>
       <c r="D11" t="n">
-        <v>35.36157055926586</v>
+        <v>34.82848155585983</v>
       </c>
     </row>
     <row r="12">
@@ -6210,10 +6210,10 @@
         <v>3.254493639578176</v>
       </c>
       <c r="C12" t="n">
-        <v>22.1305567491316</v>
+        <v>22.56448923440869</v>
       </c>
       <c r="D12" t="n">
-        <v>32.97886888105885</v>
+        <v>33.41280136633594</v>
       </c>
     </row>
     <row r="13">
@@ -6224,10 +6224,10 @@
         <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>20.81305133003238</v>
+        <v>21.33337761328319</v>
       </c>
       <c r="D13" t="n">
-        <v>30.69925071179776</v>
+        <v>30.95941385342317</v>
       </c>
     </row>
     <row r="14">
@@ -6238,10 +6238,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>19.35908298004286</v>
+        <v>19.66637001147211</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>29.80684204863741</v>
       </c>
     </row>
     <row r="15">
@@ -6252,10 +6252,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>17.5585576904542</v>
+        <v>17.91689560250429</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>28.66703296400686</v>
       </c>
     </row>
     <row r="16">
@@ -6269,7 +6269,7 @@
         <v>16.53263133951629</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>26.86552592671396</v>
       </c>
     </row>
     <row r="17">
@@ -6294,7 +6294,7 @@
         <v>1.070104997629023</v>
       </c>
       <c r="C18" t="n">
-        <v>17.12167996206437</v>
+        <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
         <v>20.86704745376595</v>
@@ -6311,7 +6311,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -6322,10 +6322,10 @@
         <v>0.672497177409065</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>10.08745766113597</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.26851249290506</v>
+        <v>7.296353744685441</v>
       </c>
       <c r="C21" t="n">
-        <v>75.41081711389</v>
+        <v>77.52375853728282</v>
       </c>
       <c r="D21" t="n">
-        <v>5.451384369678795</v>
+        <v>6.384309526599761</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.811144587886118</v>
+        <v>3.838633523605029</v>
       </c>
       <c r="C2" t="n">
-        <v>7.019496085364694</v>
+        <v>7.059747741238813</v>
       </c>
       <c r="D2" t="n">
-        <v>19.76847177271377</v>
+        <v>24.83330817892307</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.32017292477148</v>
+        <v>15.64414966717292</v>
       </c>
       <c r="C3" t="n">
-        <v>27.85709110800325</v>
+        <v>24.20498964820511</v>
       </c>
       <c r="D3" t="n">
-        <v>72.97821559518665</v>
+        <v>65.17823008494575</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.18008610270045</v>
+        <v>28.47362866627024</v>
       </c>
       <c r="C4" t="n">
-        <v>84.13185126313466</v>
+        <v>66.27680576599792</v>
       </c>
       <c r="D4" t="n">
-        <v>105.1903395192287</v>
+        <v>68.1912137892792</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>31.66136346195964</v>
+        <v>33.50214040742241</v>
       </c>
       <c r="C5" t="n">
-        <v>100.4818775296611</v>
+        <v>67.56878574478674</v>
       </c>
       <c r="D5" t="n">
-        <v>78.3189231062893</v>
+        <v>45.70035563268903</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>27.53213261789756</v>
+        <v>30.71201343195298</v>
       </c>
       <c r="C6" t="n">
-        <v>94.14862308956488</v>
+        <v>68.74982823299565</v>
       </c>
       <c r="D6" t="n">
-        <v>48.66425195181016</v>
+        <v>37.15227837181205</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>16.5287043486993</v>
+        <v>19.52303484665207</v>
       </c>
       <c r="C7" t="n">
-        <v>66.17470400475625</v>
+        <v>64.91708519561608</v>
       </c>
       <c r="D7" t="n">
-        <v>37.66867766424586</v>
+        <v>36.4110588551057</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.011061266653972</v>
+        <v>9.012443924985718</v>
       </c>
       <c r="C8" t="n">
-        <v>37.38495257771854</v>
+        <v>42.55876297909923</v>
       </c>
       <c r="D8" t="n">
-        <v>33.88011327355743</v>
+        <v>34.29735604786232</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.657812019574366</v>
+        <v>5.768749510154256</v>
       </c>
       <c r="C9" t="n">
-        <v>26.29218526743382</v>
+        <v>28.73281006019139</v>
       </c>
       <c r="D9" t="n">
-        <v>32.9484347022272</v>
+        <v>32.8374972116473</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.982369599052563</v>
+        <v>5.124723016168351</v>
       </c>
       <c r="C10" t="n">
-        <v>26.90479583488384</v>
+        <v>27.47420950334699</v>
       </c>
       <c r="D10" t="n">
-        <v>33.88011327355743</v>
+        <v>34.87658719336794</v>
       </c>
     </row>
     <row r="11">
@@ -6507,10 +6507,10 @@
         <v>4.442408361716816</v>
       </c>
       <c r="C11" t="n">
-        <v>26.47675383583222</v>
+        <v>27.00984283923824</v>
       </c>
       <c r="D11" t="n">
-        <v>35.89465956267188</v>
+        <v>35.18387422479719</v>
       </c>
     </row>
     <row r="12">
@@ -6521,10 +6521,10 @@
         <v>3.471459882216721</v>
       </c>
       <c r="C12" t="n">
-        <v>24.73415166079414</v>
+        <v>25.16808414607123</v>
       </c>
       <c r="D12" t="n">
-        <v>34.06370009425158</v>
+        <v>34.49763257952867</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>22.89435646303562</v>
+        <v>23.41468274628643</v>
       </c>
       <c r="D13" t="n">
-        <v>31.21957699504857</v>
+        <v>31.73990327829938</v>
       </c>
     </row>
     <row r="14">
@@ -6549,10 +6549,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>21.20280516861837</v>
+        <v>21.81737923147687</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>30.11412908006666</v>
       </c>
     </row>
     <row r="15">
@@ -6563,10 +6563,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>19.35024725070463</v>
+        <v>19.70858516275472</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>29.02537087605695</v>
       </c>
     </row>
     <row r="16">
@@ -6577,10 +6577,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>17.3592629064921</v>
+        <v>17.77257868998001</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>27.27884171020187</v>
       </c>
     </row>
     <row r="17">
@@ -6594,7 +6594,7 @@
         <v>17.47216389248049</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -6605,10 +6605,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>21.40209995258047</v>
       </c>
     </row>
     <row r="19">
@@ -6622,7 +6622,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>16.85071759569225</v>
       </c>
     </row>
     <row r="20">
@@ -6633,10 +6633,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>10.08745766113597</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.474616157350301</v>
+        <v>7.513466675730777</v>
       </c>
       <c r="C21" t="n">
-        <v>84.08943177019088</v>
+        <v>87.34405010537029</v>
       </c>
       <c r="D21" t="n">
-        <v>6.540289137681514</v>
+        <v>7.513466675730777</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_iteration_1_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_1_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497620036111</v>
+        <v>10.84497623615772</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907148246743</v>
+        <v>37.7890716071999</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.570035563268902</v>
+        <v>1.205586180815083</v>
       </c>
       <c r="C2" t="n">
-        <v>7.448519832120549</v>
+        <v>2.02829075697391</v>
       </c>
       <c r="D2" t="n">
-        <v>25.47733467290897</v>
+        <v>15.00306841629976</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.27952035826986</v>
+        <v>10.17090621599696</v>
       </c>
       <c r="C3" t="n">
-        <v>26.03594911662541</v>
+        <v>28.73084656478291</v>
       </c>
       <c r="D3" t="n">
-        <v>69.55191610736527</v>
+        <v>59.15520791939156</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.62227348023901</v>
+        <v>17.59979109403257</v>
       </c>
       <c r="C4" t="n">
-        <v>62.46075243959057</v>
+        <v>99.12804744550469</v>
       </c>
       <c r="D4" t="n">
-        <v>83.92764774065132</v>
+        <v>68.9314515582813</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>38.31270415823178</v>
+        <v>18.08870145074749</v>
       </c>
       <c r="C5" t="n">
-        <v>97.78207134298233</v>
+        <v>127.9708132485718</v>
       </c>
       <c r="D5" t="n">
-        <v>59.88660995905545</v>
+        <v>47.51658888554563</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>38.48058301565798</v>
+        <v>12.23650338573225</v>
       </c>
       <c r="C6" t="n">
-        <v>89.35867604054471</v>
+        <v>82.59639785369266</v>
       </c>
       <c r="D6" t="n">
-        <v>43.14977509705582</v>
+        <v>30.10823859384119</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>28.7455727803466</v>
+        <v>6.228207435741766</v>
       </c>
       <c r="C7" t="n">
-        <v>82.88306818333271</v>
+        <v>44.79518424937346</v>
       </c>
       <c r="D7" t="n">
-        <v>38.80652325346792</v>
+        <v>28.86534600026472</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>15.27108553955913</v>
+        <v>6.091744504851458</v>
       </c>
       <c r="C8" t="n">
-        <v>66.00780689503429</v>
+        <v>29.37389131106456</v>
       </c>
       <c r="D8" t="n">
-        <v>36.63391558396972</v>
+        <v>30.95941385342316</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.654686850012379</v>
+        <v>5.879687000734146</v>
       </c>
       <c r="C9" t="n">
-        <v>41.71249645803847</v>
+        <v>31.39530983410874</v>
       </c>
       <c r="D9" t="n">
-        <v>34.16874709860598</v>
+        <v>34.94530953266521</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.551783267515713</v>
+        <v>3.4164820107789</v>
       </c>
       <c r="C10" t="n">
-        <v>31.31775176547326</v>
+        <v>30.32127784566274</v>
       </c>
       <c r="D10" t="n">
-        <v>35.58835427894688</v>
+        <v>38.29306920414684</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.797801030654161</v>
+        <v>2.665445017030089</v>
       </c>
       <c r="C11" t="n">
-        <v>30.20837685967435</v>
+        <v>31.27455486648638</v>
       </c>
       <c r="D11" t="n">
-        <v>35.89465956267188</v>
+        <v>37.6716229073586</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.688426124855267</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>28.42257778564941</v>
+        <v>24.0832529328785</v>
       </c>
       <c r="D12" t="n">
-        <v>34.93156506480576</v>
+        <v>37.96909246174538</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>1.821141991377834</v>
       </c>
       <c r="C13" t="n">
-        <v>25.75615102091507</v>
+        <v>20.03256190515617</v>
       </c>
       <c r="D13" t="n">
-        <v>32.5203927031756</v>
+        <v>35.90251354430586</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>23.96838845148163</v>
+        <v>19.97365704290136</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>27.3485457972034</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>21.50027472300514</v>
+        <v>20.78359889890498</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>25.80032966760617</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>19.42584182393164</v>
+        <v>22.7323680918349</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>21.90573652485908</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>17.9443845382232</v>
+        <v>24.55547357862122</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>18.41660518396592</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>1.605157496443535</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>26.21757244191107</v>
       </c>
       <c r="D18" t="n">
-        <v>21.40209995258047</v>
+        <v>11.23610247510475</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>10.83260416865931</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>84.25358797846125</v>
       </c>
       <c r="D19" t="n">
-        <v>16.85071759569225</v>
+        <v>3.009056713516474</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.717424320421113</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>96.46780400526391</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8.682102360473753</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.158102438112742</v>
+        <v>1.063232763699296</v>
       </c>
       <c r="C2" t="n">
-        <v>10.28773419280233</v>
+        <v>7.766606088296517</v>
       </c>
       <c r="D2" t="n">
-        <v>19.91180693753381</v>
+        <v>15.20039970485336</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.79493790299943</v>
+        <v>6.99004365423729</v>
       </c>
       <c r="C3" t="n">
-        <v>27.48893571891069</v>
+        <v>16.56208377064369</v>
       </c>
       <c r="D3" t="n">
-        <v>73.09111658117503</v>
+        <v>57.99674562838032</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.23113698332128</v>
+        <v>18.76119862815655</v>
       </c>
       <c r="C4" t="n">
-        <v>63.76254989542184</v>
+        <v>83.69791877785757</v>
       </c>
       <c r="D4" t="n">
-        <v>98.11979255324322</v>
+        <v>82.30678228093984</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>41.25794727097221</v>
+        <v>22.70291566070749</v>
       </c>
       <c r="C5" t="n">
-        <v>105.513334513926</v>
+        <v>159.6076330179252</v>
       </c>
       <c r="D5" t="n">
-        <v>74.04832059281568</v>
+        <v>60.74563920027141</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>45.48437113775474</v>
+        <v>18.07299348747954</v>
       </c>
       <c r="C6" t="n">
-        <v>121.8417623309589</v>
+        <v>146.0330075113046</v>
       </c>
       <c r="D6" t="n">
-        <v>51.52211951887262</v>
+        <v>37.47429161880501</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>37.06981156465531</v>
+        <v>10.06095047312131</v>
       </c>
       <c r="C7" t="n">
-        <v>105.0411138681832</v>
+        <v>82.70340835345554</v>
       </c>
       <c r="D7" t="n">
-        <v>41.98051358129786</v>
+        <v>31.02126395879071</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>22.94835258676919</v>
+        <v>6.67588438887831</v>
       </c>
       <c r="C8" t="n">
-        <v>88.28857104291565</v>
+        <v>44.47807974090174</v>
       </c>
       <c r="D8" t="n">
-        <v>38.97047512007713</v>
+        <v>32.29459073119883</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>11.53749902030851</v>
+        <v>6.212499472473814</v>
       </c>
       <c r="C9" t="n">
-        <v>61.12655730951914</v>
+        <v>35.16718451382499</v>
       </c>
       <c r="D9" t="n">
-        <v>35.94374694788421</v>
+        <v>35.27812200440487</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.548257187326225</v>
+        <v>4.128249096357838</v>
       </c>
       <c r="C10" t="n">
-        <v>40.57072387799944</v>
+        <v>34.59188035913637</v>
       </c>
       <c r="D10" t="n">
-        <v>35.87306111317846</v>
+        <v>39.00483628972578</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.153193699591506</v>
+        <v>2.843141351498762</v>
       </c>
       <c r="C11" t="n">
-        <v>33.40691088011046</v>
+        <v>34.29539255245382</v>
       </c>
       <c r="D11" t="n">
-        <v>36.60544490054656</v>
+        <v>38.56010457970196</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.905392367493811</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>31.67707142522758</v>
+        <v>28.8565102709265</v>
       </c>
       <c r="D12" t="n">
-        <v>35.36549755008285</v>
+        <v>38.40302494702248</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>1.821141991377834</v>
       </c>
       <c r="C13" t="n">
-        <v>28.61794557879453</v>
+        <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
-        <v>33.30088212805181</v>
+        <v>36.68300296918207</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>1.229148125717007</v>
       </c>
       <c r="C14" t="n">
-        <v>25.81211064005714</v>
+        <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>28.5776939229204</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>23.65030219530566</v>
+        <v>22.57528845915541</v>
       </c>
       <c r="D15" t="n">
-        <v>29.74204670015712</v>
+        <v>25.80032966760617</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>20.66578917439536</v>
+        <v>25.62557857625024</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>21.49242074137117</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>18.88882582970863</v>
+        <v>26.44435616159209</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>17.47216389248049</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>8.560839981032187</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>50.82998738737861</v>
       </c>
       <c r="D18" t="n">
-        <v>21.40209995258047</v>
+        <v>9.095892479846698</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>45.7376620454504</v>
       </c>
       <c r="D19" t="n">
-        <v>16.85071759569225</v>
+        <v>1.805434028109884</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.907117735236974</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>105.7576997087945</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>9.883897169046218</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.099017649408686</v>
+        <v>0.5645049299419159</v>
       </c>
       <c r="C2" t="n">
-        <v>6.80842032895163</v>
+        <v>3.196570525027615</v>
       </c>
       <c r="D2" t="n">
-        <v>27.75695284217007</v>
+        <v>10.22686583513902</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.81595551541612</v>
+        <v>6.268459091615885</v>
       </c>
       <c r="C3" t="n">
-        <v>33.472687976295</v>
+        <v>24.60259746842507</v>
       </c>
       <c r="D3" t="n">
-        <v>71.68230862558086</v>
+        <v>58.72323892952296</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.77167905773377</v>
+        <v>20.56074217004095</v>
       </c>
       <c r="C4" t="n">
-        <v>65.98326320242812</v>
+        <v>74.78954010952202</v>
       </c>
       <c r="D4" t="n">
-        <v>108.3044432370996</v>
+        <v>92.4276193640202</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>42.04334543436966</v>
+        <v>23.0219836645877</v>
       </c>
       <c r="C5" t="n">
-        <v>109.8575681052181</v>
+        <v>178.0890335503714</v>
       </c>
       <c r="D5" t="n">
-        <v>89.38812847167209</v>
+        <v>67.91239744127311</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>49.99255659565609</v>
+        <v>14.41009280293469</v>
       </c>
       <c r="C6" t="n">
-        <v>141.6053253651515</v>
+        <v>187.9349812762627</v>
       </c>
       <c r="D6" t="n">
-        <v>60.37748381117885</v>
+        <v>38.11831811279092</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>44.73529763941441</v>
+        <v>4.371722527011046</v>
       </c>
       <c r="C7" t="n">
-        <v>137.8589761257456</v>
+        <v>79.17009836587128</v>
       </c>
       <c r="D7" t="n">
-        <v>46.59178254814513</v>
+        <v>32.93763547748049</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>30.62561963397925</v>
+        <v>4.255876297909922</v>
       </c>
       <c r="C8" t="n">
-        <v>111.2369236296849</v>
+        <v>41.55738032076748</v>
       </c>
       <c r="D8" t="n">
-        <v>40.80634332701867</v>
+        <v>35.9663271450819</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>16.75156107756332</v>
+        <v>2.884374755077128</v>
       </c>
       <c r="C9" t="n">
-        <v>83.6468678972367</v>
+        <v>26.40312275801371</v>
       </c>
       <c r="D9" t="n">
-        <v>37.71874679716245</v>
+        <v>40.82499653339935</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.541205026947251</v>
+        <v>1.992947839621025</v>
       </c>
       <c r="C10" t="n">
-        <v>54.52135875534661</v>
+        <v>26.90479583488384</v>
       </c>
       <c r="D10" t="n">
-        <v>36.44247478164161</v>
+        <v>30.17892442854695</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.508586368528851</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>39.80397892098267</v>
+        <v>23.10052348092744</v>
       </c>
       <c r="D11" t="n">
-        <v>37.13853390395258</v>
+        <v>30.74146586308036</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4.339324852770901</v>
+        <v>1.301797455831271</v>
       </c>
       <c r="C12" t="n">
-        <v>34.49763257952867</v>
+        <v>18.65909686691488</v>
       </c>
       <c r="D12" t="n">
-        <v>35.58246379272139</v>
+        <v>29.94134148411922</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.121957699504857</v>
+        <v>0.7804894248762143</v>
       </c>
       <c r="C13" t="n">
-        <v>31.73990327829938</v>
+        <v>17.43093048890212</v>
       </c>
       <c r="D13" t="n">
-        <v>33.82120841130262</v>
+        <v>23.67484588791184</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>27.9631198600619</v>
+        <v>18.74450891718435</v>
       </c>
       <c r="D14" t="n">
-        <v>31.03599017435442</v>
+        <v>21.51009220004762</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>25.083653843506</v>
+        <v>21.50027472300514</v>
       </c>
       <c r="D15" t="n">
-        <v>29.74204670015712</v>
+        <v>17.91689560250429</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>0.8266315669758143</v>
       </c>
       <c r="C16" t="n">
         <v>22.31905230834699</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>14.87936820556466</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>6.611089040398022</v>
       </c>
       <c r="C17" t="n">
-        <v>19.83326712119407</v>
+        <v>43.91652005407257</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>7.555530331883453</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>18.72683745850791</v>
+        <v>39.59388491227386</v>
       </c>
       <c r="D18" t="n">
-        <v>21.40209995258047</v>
+        <v>1.070104997629023</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>16.85071759569225</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8.082186654701907</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>114.1608864976644</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>11.11300665021512</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.33423618780042</v>
+        <v>0.6803511590430396</v>
       </c>
       <c r="C2" t="n">
-        <v>4.519966430352315</v>
+        <v>2.886338250485622</v>
       </c>
       <c r="D2" t="n">
-        <v>22.53307330787279</v>
+        <v>11.2203945118368</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.34042977366217</v>
+        <v>4.025165587411922</v>
       </c>
       <c r="C3" t="n">
-        <v>46.50538875017141</v>
+        <v>17.78435966243097</v>
       </c>
       <c r="D3" t="n">
-        <v>79.56574269068275</v>
+        <v>53.99612373357456</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>20.1906232855399</v>
+        <v>16.61706164208151</v>
       </c>
       <c r="C4" t="n">
-        <v>92.83602640898688</v>
+        <v>68.22950194974482</v>
       </c>
       <c r="D4" t="n">
-        <v>103.4163214176548</v>
+        <v>100.0214378563693</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>28.1516154192773</v>
+        <v>27.0716929446058</v>
       </c>
       <c r="C5" t="n">
-        <v>84.6021084134689</v>
+        <v>158.9694970101648</v>
       </c>
       <c r="D5" t="n">
-        <v>60.94198874112077</v>
+        <v>83.76762286485911</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>27.77364255314227</v>
+        <v>21.73589417202438</v>
       </c>
       <c r="C6" t="n">
-        <v>90.76748399613888</v>
+        <v>236.8407431633176</v>
       </c>
       <c r="D6" t="n">
-        <v>30.67176177607885</v>
+        <v>48.82525857530663</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>20.30156077611979</v>
+        <v>9.162651323735481</v>
       </c>
       <c r="C7" t="n">
-        <v>78.2119126065264</v>
+        <v>171.0361580430623</v>
       </c>
       <c r="D7" t="n">
-        <v>28.68568617038755</v>
+        <v>36.4110588551057</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.59934912567606</v>
+        <v>4.589670517353839</v>
       </c>
       <c r="C8" t="n">
-        <v>61.58503348740241</v>
+        <v>71.01472018669303</v>
       </c>
       <c r="D8" t="n">
-        <v>27.78836876870596</v>
+        <v>37.1346069131356</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.101561981893925</v>
+        <v>3.328124717396686</v>
       </c>
       <c r="C9" t="n">
-        <v>41.60155896745857</v>
+        <v>37.60780930658255</v>
       </c>
       <c r="D9" t="n">
-        <v>27.73437264497238</v>
+        <v>41.49062147687869</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.98589567924205</v>
+        <v>2.2776546738526</v>
       </c>
       <c r="C10" t="n">
-        <v>31.17539834835747</v>
+        <v>30.03657101143117</v>
       </c>
       <c r="D10" t="n">
-        <v>29.04009709162065</v>
+        <v>32.31422568528377</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.198534020436107</v>
+        <v>1.421570675749381</v>
       </c>
       <c r="C11" t="n">
-        <v>27.54293184264426</v>
+        <v>26.83214650476957</v>
       </c>
       <c r="D11" t="n">
-        <v>28.43141351498762</v>
+        <v>31.8076438698924</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.386628669023996</v>
+        <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>25.81898287398687</v>
+        <v>21.69662426385451</v>
       </c>
       <c r="D12" t="n">
-        <v>27.55471281509523</v>
+        <v>30.8092064546734</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.560978849752429</v>
+        <v>0.7804894248762143</v>
       </c>
       <c r="C13" t="n">
-        <v>23.15451960466103</v>
+        <v>20.81305133003238</v>
       </c>
       <c r="D13" t="n">
-        <v>25.49598787928967</v>
+        <v>23.93500902953724</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.921861094287755</v>
+        <v>0.6145740628585034</v>
       </c>
       <c r="C14" t="n">
-        <v>20.89551813718911</v>
+        <v>20.58823110575986</v>
       </c>
       <c r="D14" t="n">
-        <v>24.89024954576939</v>
+        <v>21.20280516861837</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>18.63357142660446</v>
+        <v>24.00864010735575</v>
       </c>
       <c r="D15" t="n">
-        <v>22.93362637120549</v>
+        <v>17.5585576904542</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0.4133157834879072</v>
+        <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>16.94594712300419</v>
+        <v>37.19842051391164</v>
       </c>
       <c r="D16" t="n">
-        <v>20.66578917439536</v>
+        <v>12.81278928812512</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>16.05550195525234</v>
+        <v>46.74984392852887</v>
       </c>
       <c r="D17" t="n">
-        <v>18.41660518396592</v>
+        <v>4.722206457427158</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>16.05157496443535</v>
+        <v>1.605157496443535</v>
       </c>
       <c r="D18" t="n">
-        <v>14.44641746799181</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>16.85071759569225</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>9.027170140549421</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>5.37997741927252</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>75.31968386981528</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>7.397468951499714</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.792491381505428</v>
+        <v>0.3769911184307752</v>
       </c>
       <c r="C2" t="n">
-        <v>2.487748682561417</v>
+        <v>2.079341637594744</v>
       </c>
       <c r="D2" t="n">
-        <v>16.26952295477814</v>
+        <v>8.146542449840032</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.18611545764617</v>
+        <v>3.308489763311751</v>
       </c>
       <c r="C3" t="n">
-        <v>31.9018916495001</v>
+        <v>14.59367962362884</v>
       </c>
       <c r="D3" t="n">
-        <v>80.38550202372883</v>
+        <v>51.16869034534376</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.97588258021711</v>
+        <v>13.40085616296896</v>
       </c>
       <c r="C4" t="n">
-        <v>107.0536966618892</v>
+        <v>58.42773287054467</v>
       </c>
       <c r="D4" t="n">
-        <v>117.1490083046591</v>
+        <v>104.1310337463464</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>31.02322745419922</v>
+        <v>28.12707172667112</v>
       </c>
       <c r="C5" t="n">
-        <v>127.4799393964484</v>
+        <v>150.0355929015188</v>
       </c>
       <c r="D5" t="n">
-        <v>79.37430188835464</v>
+        <v>97.41391595388978</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>33.2881194078966</v>
+        <v>26.68684784454105</v>
       </c>
       <c r="C6" t="n">
-        <v>113.751179500261</v>
+        <v>257.570345938489</v>
       </c>
       <c r="D6" t="n">
-        <v>37.83655652167208</v>
+        <v>58.96867585558468</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>19.3433750167749</v>
+        <v>10.30049691295753</v>
       </c>
       <c r="C7" t="n">
-        <v>101.2083708308037</v>
+        <v>236.0131298486374</v>
       </c>
       <c r="D7" t="n">
-        <v>31.08115056874977</v>
+        <v>39.82459562277186</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.846929473595507</v>
+        <v>4.339324852770902</v>
       </c>
       <c r="C8" t="n">
-        <v>78.35819301445918</v>
+        <v>111.6541664039897</v>
       </c>
       <c r="D8" t="n">
-        <v>29.04009709162065</v>
+        <v>39.8884092235479</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.992187076095029</v>
+        <v>2.884374755077128</v>
       </c>
       <c r="C9" t="n">
-        <v>48.7015583645715</v>
+        <v>50.14374574211007</v>
       </c>
       <c r="D9" t="n">
-        <v>29.06562253193106</v>
+        <v>41.26874649571891</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.2776546738526</v>
+        <v>1.423534171157875</v>
       </c>
       <c r="C10" t="n">
-        <v>33.88011327355743</v>
+        <v>32.45657910239955</v>
       </c>
       <c r="D10" t="n">
-        <v>29.89421759431538</v>
+        <v>33.45305302221006</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>0.7107853378746906</v>
       </c>
       <c r="C11" t="n">
-        <v>30.74146586308036</v>
+        <v>27.8983245115816</v>
       </c>
       <c r="D11" t="n">
-        <v>29.67528785626833</v>
+        <v>33.05151821117311</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.084831213192725</v>
+        <v>0.4339324852770902</v>
       </c>
       <c r="C12" t="n">
-        <v>21.69662426385451</v>
+        <v>23.21538796232432</v>
       </c>
       <c r="D12" t="n">
-        <v>28.63954402828795</v>
+        <v>29.50740899884213</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0.5203262832508095</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>17.17076734727672</v>
+        <v>16.91060420565131</v>
       </c>
       <c r="D13" t="n">
-        <v>26.27647730416588</v>
+        <v>24.45533531278805</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>15.36435157146258</v>
+        <v>19.97365704290136</v>
       </c>
       <c r="D14" t="n">
-        <v>19.0517959486136</v>
+        <v>16.59349969717959</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>3.941717032550943</v>
       </c>
       <c r="C15" t="n">
-        <v>14.33351648200343</v>
+        <v>31.53373626040754</v>
       </c>
       <c r="D15" t="n">
-        <v>17.5585576904542</v>
+        <v>10.75013736150257</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>13.63942085510094</v>
+        <v>40.09163099832699</v>
       </c>
       <c r="D16" t="n">
-        <v>15.70599977254047</v>
+        <v>3.719842051391165</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>13.69439872653876</v>
+        <v>0.9444412914854317</v>
       </c>
       <c r="D17" t="n">
-        <v>12.27773678931061</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>14.44641746799181</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>7.490734983403163</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>4.212679398923063</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>65.59743635465912</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>6.018113427032947</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.401755795215198</v>
+        <v>0.6410812508731673</v>
       </c>
       <c r="C2" t="n">
-        <v>7.064656479760047</v>
+        <v>17.42994874119787</v>
       </c>
       <c r="D2" t="n">
-        <v>16.57779173391164</v>
+        <v>16.7761047701695</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.95969159086365</v>
+        <v>2.292380889416302</v>
       </c>
       <c r="C3" t="n">
-        <v>19.76749002500953</v>
+        <v>11.10356653503143</v>
       </c>
       <c r="D3" t="n">
-        <v>74.99079838889261</v>
+        <v>46.30903920932204</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.47210713921825</v>
+        <v>9.967684441217866</v>
       </c>
       <c r="C4" t="n">
-        <v>92.55524656557229</v>
+        <v>47.73257338047992</v>
       </c>
       <c r="D4" t="n">
-        <v>129.4522705342802</v>
+        <v>105.6753228851267</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>36.37375244234433</v>
+        <v>25.18182861393069</v>
       </c>
       <c r="C5" t="n">
-        <v>164.4181967687346</v>
+        <v>129.5416095753667</v>
       </c>
       <c r="D5" t="n">
-        <v>100.7518581483289</v>
+        <v>110.2257234943107</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>37.6755498981756</v>
+        <v>31.83905979642831</v>
       </c>
       <c r="C6" t="n">
-        <v>156.4984380385756</v>
+        <v>250.0030346341545</v>
       </c>
       <c r="D6" t="n">
-        <v>51.4818678629985</v>
+        <v>72.69449050865934</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>28.02693346083794</v>
+        <v>18.74450891718435</v>
       </c>
       <c r="C7" t="n">
-        <v>132.7686142792259</v>
+        <v>301.6488543637622</v>
       </c>
       <c r="D7" t="n">
-        <v>34.43480072645687</v>
+        <v>45.93302983859552</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>14.18625432636641</v>
+        <v>6.926230053461247</v>
       </c>
       <c r="C8" t="n">
-        <v>105.4789733442773</v>
+        <v>199.9427374469054</v>
       </c>
       <c r="D8" t="n">
-        <v>30.62561963397925</v>
+        <v>41.39048321104552</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.767186925373262</v>
+        <v>3.439062207976575</v>
       </c>
       <c r="C9" t="n">
-        <v>70.88905648054941</v>
+        <v>87.19686759579318</v>
       </c>
       <c r="D9" t="n">
-        <v>30.17499743772996</v>
+        <v>42.15624642035802</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.989421759431538</v>
+        <v>1.70824100538945</v>
       </c>
       <c r="C10" t="n">
-        <v>44.84132639147307</v>
+        <v>43.56014563743098</v>
       </c>
       <c r="D10" t="n">
-        <v>30.60598467989432</v>
+        <v>35.44600086183109</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>0.7107853378746906</v>
       </c>
       <c r="C11" t="n">
-        <v>35.00617789032851</v>
+        <v>32.34073287329842</v>
       </c>
       <c r="D11" t="n">
-        <v>30.03068052520567</v>
+        <v>33.40691088011046</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.084831213192725</v>
+        <v>0.4339324852770902</v>
       </c>
       <c r="C12" t="n">
         <v>26.68684784454105</v>
       </c>
       <c r="D12" t="n">
-        <v>29.29044275620359</v>
+        <v>30.15830772675777</v>
       </c>
     </row>
     <row r="13">
@@ -2495,7 +2495,7 @@
         <v>19.77239876353076</v>
       </c>
       <c r="D13" t="n">
-        <v>26.53664044579129</v>
+        <v>24.97566159603886</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>16.90078672860884</v>
+        <v>20.28094407433061</v>
       </c>
       <c r="D14" t="n">
-        <v>19.97365704290136</v>
+        <v>17.20807376003809</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>2.5083653843506</v>
       </c>
       <c r="C15" t="n">
-        <v>15.76686813020377</v>
+        <v>32.25041208450772</v>
       </c>
       <c r="D15" t="n">
-        <v>17.5585576904542</v>
+        <v>10.39179944945249</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.87936820556466</v>
+        <v>40.91826256530281</v>
       </c>
       <c r="D16" t="n">
-        <v>15.29268398905256</v>
+        <v>3.306526267903257</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>14.63884001802419</v>
+        <v>0.4722206457427158</v>
       </c>
       <c r="D17" t="n">
-        <v>11.33329549782518</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>3.21031499288707</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>6.955682484588652</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>36.10868056219768</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>4.212679398923063</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.984112110282804</v>
+        <v>0.430005494460103</v>
       </c>
       <c r="C2" t="n">
-        <v>3.186753047985146</v>
+        <v>9.064476553310801</v>
       </c>
       <c r="D2" t="n">
-        <v>11.45797745626452</v>
+        <v>12.07844200534851</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.49827016986765</v>
+        <v>3.441025703385071</v>
       </c>
       <c r="C3" t="n">
-        <v>24.5780537758189</v>
+        <v>33.24688600431823</v>
       </c>
       <c r="D3" t="n">
-        <v>74.07286428542184</v>
+        <v>53.11745953827367</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.31368590593603</v>
+        <v>16.93612964596173</v>
       </c>
       <c r="C4" t="n">
-        <v>85.28049607710342</v>
+        <v>67.98701026679586</v>
       </c>
       <c r="D4" t="n">
-        <v>138.0160557584251</v>
+        <v>109.0191555657913</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>38.68085954732433</v>
+        <v>19.5613230071177</v>
       </c>
       <c r="C5" t="n">
-        <v>191.5389770985527</v>
+        <v>202.8045320047849</v>
       </c>
       <c r="D5" t="n">
-        <v>109.3421505604885</v>
+        <v>102.3226544751238</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>33.40887437551896</v>
+        <v>11.63272854762046</v>
       </c>
       <c r="C6" t="n">
-        <v>192.4431667341641</v>
+        <v>259.9049419791879</v>
       </c>
       <c r="D6" t="n">
-        <v>50.83784136901259</v>
+        <v>62.75233150775189</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.402197763571703</v>
+        <v>4.551382356888213</v>
       </c>
       <c r="C7" t="n">
-        <v>139.4759145946401</v>
+        <v>140.6137601838622</v>
       </c>
       <c r="D7" t="n">
-        <v>34.85400699617026</v>
+        <v>35.81219275551515</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.673119072214817</v>
+        <v>2.336559536107409</v>
       </c>
       <c r="C8" t="n">
-        <v>86.28580572625216</v>
+        <v>64.25538724295374</v>
       </c>
       <c r="D8" t="n">
-        <v>32.3780392860598</v>
+        <v>31.04286240828414</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.107812321017901</v>
+        <v>1.220312396378785</v>
       </c>
       <c r="C9" t="n">
-        <v>34.16874709860598</v>
+        <v>33.17030968338697</v>
       </c>
       <c r="D9" t="n">
-        <v>32.50468473990763</v>
+        <v>27.06874770149305</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.281180754042088</v>
+        <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>27.47420950334699</v>
+        <v>25.33890824661018</v>
       </c>
       <c r="D10" t="n">
-        <v>23.48831382410494</v>
+        <v>26.1930287493049</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.7107853378746906</v>
+        <v>0.1776963344686726</v>
       </c>
       <c r="C11" t="n">
         <v>21.32356013624072</v>
       </c>
       <c r="D11" t="n">
-        <v>23.45591614986479</v>
+        <v>24.16670148773948</v>
       </c>
     </row>
     <row r="12">
@@ -2792,7 +2792,7 @@
         <v>16.05550195525234</v>
       </c>
       <c r="D12" t="n">
-        <v>21.47965802121596</v>
+        <v>20.39482680802324</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>13.78864650614645</v>
+        <v>16.65044106402591</v>
       </c>
       <c r="D13" t="n">
-        <v>16.3902779224005</v>
+        <v>14.04880964777186</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>13.21334235145782</v>
+        <v>27.04125876577415</v>
       </c>
       <c r="D14" t="n">
-        <v>14.74977750860408</v>
+        <v>8.604036880019047</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.541826921753</v>
+        <v>34.75877746885832</v>
       </c>
       <c r="D15" t="n">
-        <v>12.90016483380309</v>
+        <v>2.5083653843506</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>12.39947350463721</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>9.506263020221864</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2.361103228713579</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>29.27768003604838</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>5.66664774891259</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>31.03304493124168</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>3.21031499288707</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.821542902005333</v>
+        <v>0.2100940087088174</v>
       </c>
       <c r="C2" t="n">
-        <v>5.6018524004323</v>
+        <v>3.897538385859837</v>
       </c>
       <c r="D2" t="n">
-        <v>9.715375281226436</v>
+        <v>8.92310488389926</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>11.70243263462198</v>
+        <v>2.444551783574558</v>
       </c>
       <c r="C3" t="n">
-        <v>18.18687622117216</v>
+        <v>34.49370558871168</v>
       </c>
       <c r="D3" t="n">
-        <v>67.26935269499145</v>
+        <v>50.35383975081891</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.54417563225577</v>
+        <v>11.11632925518663</v>
       </c>
       <c r="C4" t="n">
-        <v>73.8578615381918</v>
+        <v>73.50050537384594</v>
       </c>
       <c r="D4" t="n">
-        <v>142.725499495697</v>
+        <v>106.1347808107142</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>47.17297718905925</v>
+        <v>18.01507037292897</v>
       </c>
       <c r="C5" t="n">
-        <v>174.849266126357</v>
+        <v>148.4157091895116</v>
       </c>
       <c r="D5" t="n">
-        <v>129.9833960422777</v>
+        <v>106.0287520586555</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>41.53970886209105</v>
+        <v>11.5119735799981</v>
       </c>
       <c r="C6" t="n">
-        <v>248.0709551521968</v>
+        <v>242.2344650504495</v>
       </c>
       <c r="D6" t="n">
-        <v>69.15234479173684</v>
+        <v>65.32843748369551</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>19.52303484665207</v>
+        <v>3.952516257297658</v>
       </c>
       <c r="C7" t="n">
-        <v>201.2190094624262</v>
+        <v>177.9830047983127</v>
       </c>
       <c r="D7" t="n">
-        <v>39.64493579289469</v>
+        <v>34.49468733641593</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6.342090169434394</v>
+        <v>1.168279768053704</v>
       </c>
       <c r="C8" t="n">
-        <v>130.0128484734051</v>
+        <v>74.68645660057609</v>
       </c>
       <c r="D8" t="n">
-        <v>34.21390749300134</v>
+        <v>26.53664044579129</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.662499773917349</v>
+        <v>0.4437499623195582</v>
       </c>
       <c r="C9" t="n">
-        <v>61.90311974357836</v>
+        <v>31.72812230584841</v>
       </c>
       <c r="D9" t="n">
-        <v>33.50312215512664</v>
+        <v>21.74374815365835</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.423534171157875</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>32.88363935374691</v>
+        <v>18.64829764216817</v>
       </c>
       <c r="D10" t="n">
-        <v>25.0542014123786</v>
+        <v>19.92947839621025</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5330890034060179</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>25.41057582902019</v>
+        <v>13.50492141961912</v>
       </c>
       <c r="D11" t="n">
-        <v>24.16670148773948</v>
+        <v>17.59193711239859</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>18.44213062427633</v>
+        <v>11.49921085984289</v>
       </c>
       <c r="D12" t="n">
-        <v>21.91359050649305</v>
+        <v>13.66887328622834</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>16.3902779224005</v>
+        <v>14.04880964777186</v>
       </c>
       <c r="D13" t="n">
-        <v>16.3902779224005</v>
+        <v>8.325220532012953</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>14.13520344574558</v>
+        <v>16.59349969717959</v>
       </c>
       <c r="D14" t="n">
-        <v>14.74977750860408</v>
+        <v>2.765583282863265</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.61684065790326</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>12.18348900970292</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.653263133951629</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>23.1456838753228</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>8.266315669758143</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>35.41654843070368</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>4.722206457427158</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1.070104997629023</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>1.070104997629023</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.93306122966197</v>
+        <v>0.3661918936840602</v>
       </c>
       <c r="C2" t="n">
-        <v>2.911863690796039</v>
+        <v>5.962153807890879</v>
       </c>
       <c r="D2" t="n">
-        <v>7.381760988231767</v>
+        <v>7.270823497651877</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>10.95139564087317</v>
+        <v>1.492256510455152</v>
       </c>
       <c r="C3" t="n">
-        <v>20.30745126234527</v>
+        <v>23.10543221944868</v>
       </c>
       <c r="D3" t="n">
-        <v>61.75193059712438</v>
+        <v>45.80834788015617</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.30695254072654</v>
+        <v>7.798022014832415</v>
       </c>
       <c r="C4" t="n">
-        <v>63.21375292874787</v>
+        <v>80.97945938479815</v>
       </c>
       <c r="D4" t="n">
-        <v>144.0783478321491</v>
+        <v>107.6663072293392</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>51.44357970253288</v>
+        <v>17.84326452468578</v>
       </c>
       <c r="C5" t="n">
-        <v>163.9518666092173</v>
+        <v>142.9424657383356</v>
       </c>
       <c r="D5" t="n">
-        <v>145.1513980728909</v>
+        <v>120.6813365445392</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>48.46299367243955</v>
+        <v>17.95223851985718</v>
       </c>
       <c r="C6" t="n">
-        <v>271.0546506563189</v>
+        <v>240.1413789449953</v>
       </c>
       <c r="D6" t="n">
-        <v>82.11337798320324</v>
+        <v>83.15992103593032</v>
       </c>
     </row>
     <row r="7">
@@ -3338,10 +3338,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>18.92416874706152</v>
+        <v>8.503898614185871</v>
       </c>
       <c r="C7" t="n">
-        <v>259.30902112271</v>
+        <v>270.8072502348487</v>
       </c>
       <c r="D7" t="n">
         <v>44.55563780953724</v>
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.257258956241669</v>
+        <v>2.503456645829366</v>
       </c>
       <c r="C8" t="n">
-        <v>170.5688461358408</v>
+        <v>156.8832831386403</v>
       </c>
       <c r="D8" t="n">
-        <v>36.13322425480386</v>
+        <v>29.6242369756475</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.996874830438012</v>
+        <v>0.6656249434793372</v>
       </c>
       <c r="C9" t="n">
-        <v>73.99530621678632</v>
+        <v>61.79218225299847</v>
       </c>
       <c r="D9" t="n">
-        <v>33.05937219280708</v>
+        <v>23.62968549351647</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.5694136684631501</v>
+        <v>0.1423534171157875</v>
       </c>
       <c r="C10" t="n">
-        <v>34.30717352490479</v>
+        <v>27.90126975469435</v>
       </c>
       <c r="D10" t="n">
-        <v>25.76596849795754</v>
+        <v>20.64124548178919</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>24.6997904911455</v>
+        <v>17.41424077792992</v>
       </c>
       <c r="D11" t="n">
-        <v>24.52209415667683</v>
+        <v>18.30272245027328</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>18.44213062427633</v>
+        <v>13.23494080095125</v>
       </c>
       <c r="D12" t="n">
-        <v>20.39482680802324</v>
+        <v>14.31977201414398</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>11.70734137314322</v>
+        <v>14.30897278939726</v>
       </c>
       <c r="D13" t="n">
-        <v>16.65044106402591</v>
+        <v>8.845546815263763</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.36962016288231</v>
+        <v>17.20807376003809</v>
       </c>
       <c r="D14" t="n">
-        <v>11.67690719431156</v>
+        <v>3.072870314292517</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.075013736150257</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>19.35024725070463</v>
+        <v>3.583379120500858</v>
       </c>
       <c r="D15" t="n">
-        <v>6.808420328951629</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>30.17205219461722</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>3.719842051391165</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3481,10 +3481,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0.4722206457427158</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4722206457427158</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.229949946972006</v>
+        <v>0.9444412914854315</v>
       </c>
       <c r="C2" t="n">
-        <v>6.444191930676063</v>
+        <v>15.12185988851362</v>
       </c>
       <c r="D2" t="n">
-        <v>14.31584502332699</v>
+        <v>13.62862163035422</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>8.816094384136358</v>
+        <v>1.354811831860598</v>
       </c>
       <c r="C3" t="n">
-        <v>15.99757884070178</v>
+        <v>23.06125357275758</v>
       </c>
       <c r="D3" t="n">
-        <v>54.51645001682538</v>
+        <v>41.29230844062084</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>26.30396623988479</v>
+        <v>5.296528864411542</v>
       </c>
       <c r="C4" t="n">
-        <v>57.29185077673112</v>
+        <v>68.6506717148667</v>
       </c>
       <c r="D4" t="n">
-        <v>142.2277534096439</v>
+        <v>106.3645097735079</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>49.79915229791947</v>
+        <v>15.06982726018854</v>
       </c>
       <c r="C5" t="n">
-        <v>142.6233977344554</v>
+        <v>144.8568737616169</v>
       </c>
       <c r="D5" t="n">
-        <v>159.7303514809561</v>
+        <v>129.9343086570654</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>57.03659637362695</v>
+        <v>21.17237098978672</v>
       </c>
       <c r="C6" t="n">
-        <v>267.7540148746411</v>
+        <v>234.8684120254858</v>
       </c>
       <c r="D6" t="n">
-        <v>101.9976959850181</v>
+        <v>100.7498946529204</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>32.69808903764427</v>
+        <v>14.55244622005047</v>
       </c>
       <c r="C7" t="n">
-        <v>318.1775587124615</v>
+        <v>311.3504851771292</v>
       </c>
       <c r="D7" t="n">
-        <v>53.95783557310894</v>
+        <v>56.47307319138927</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.2641722479004</v>
+        <v>5.507604620824606</v>
       </c>
       <c r="C8" t="n">
-        <v>239.6642495607313</v>
+        <v>256.1870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>38.80357801035517</v>
+        <v>33.79666471869644</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.884374755077128</v>
+        <v>1.442187377538564</v>
       </c>
       <c r="C9" t="n">
-        <v>127.0234267139735</v>
+        <v>125.0265518835355</v>
       </c>
       <c r="D9" t="n">
-        <v>34.27968458918587</v>
+        <v>25.62656032395449</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.8541205026947251</v>
+        <v>0.2847068342315751</v>
       </c>
       <c r="C10" t="n">
-        <v>53.52488483553611</v>
+        <v>48.9695754878309</v>
       </c>
       <c r="D10" t="n">
-        <v>27.3318560862312</v>
+        <v>21.6377194015997</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>30.20837685967435</v>
+        <v>24.16670148773948</v>
       </c>
       <c r="D11" t="n">
-        <v>24.6997904911455</v>
+        <v>19.01350778814797</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>21.47965802121596</v>
+        <v>16.05550195525234</v>
       </c>
       <c r="D12" t="n">
-        <v>20.82875929330033</v>
+        <v>14.97067074205961</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>14.04880964777186</v>
+        <v>14.82929907264807</v>
       </c>
       <c r="D13" t="n">
-        <v>16.91060420565131</v>
+        <v>9.626036240139976</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.98419422574081</v>
+        <v>17.20807376003809</v>
       </c>
       <c r="D14" t="n">
-        <v>11.98419422574081</v>
+        <v>3.68744437715102</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0.7166758241001715</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>19.70858516275472</v>
+        <v>8.241771977151972</v>
       </c>
       <c r="D15" t="n">
-        <v>6.450082416901544</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>0.8266315669758143</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.870450360768427</v>
+        <v>4.75558587937155</v>
       </c>
       <c r="C2" t="n">
-        <v>6.939974521320702</v>
+        <v>10.44285033007332</v>
       </c>
       <c r="D2" t="n">
-        <v>8.588328916751097</v>
+        <v>13.57757074973339</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.06872233929727672</v>
+        <v>0.07363107781851078</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>4.138066573400306</v>
+        <v>4.196971435655114</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2.233476027161494</v>
+        <v>2.616357631817749</v>
       </c>
       <c r="C4" t="n">
-        <v>3.994731408580271</v>
+        <v>4.390375733391735</v>
       </c>
       <c r="D4" t="n">
-        <v>23.03670988015141</v>
+        <v>24.32574461582747</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>6.111379458936396</v>
+        <v>7.706719478337463</v>
       </c>
       <c r="C5" t="n">
-        <v>12.64000169217769</v>
+        <v>14.38260386721577</v>
       </c>
       <c r="D5" t="n">
-        <v>25.47635292520474</v>
+        <v>27.95526587842793</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.3258013690897</v>
+        <v>10.2641722479004</v>
       </c>
       <c r="C6" t="n">
-        <v>15.8994040702771</v>
+        <v>19.64280806657019</v>
       </c>
       <c r="D6" t="n">
-        <v>31.27553661419064</v>
+        <v>36.14598697495907</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.72537268471815</v>
+        <v>12.0970952117292</v>
       </c>
       <c r="C7" t="n">
-        <v>17.54677671800324</v>
+        <v>23.2360046641135</v>
       </c>
       <c r="D7" t="n">
-        <v>29.70375853969149</v>
+        <v>35.69241953559704</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.261406931236909</v>
+        <v>14.26970288122739</v>
       </c>
       <c r="C8" t="n">
-        <v>18.52557917913731</v>
+        <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>35.04839304161113</v>
+        <v>44.31118263117978</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.320311793491715</v>
+        <v>15.08749871886498</v>
       </c>
       <c r="C9" t="n">
-        <v>20.74531073843935</v>
+        <v>30.7296848906294</v>
       </c>
       <c r="D9" t="n">
-        <v>38.71718421238145</v>
+        <v>49.36718330805084</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.544731107136738</v>
+        <v>14.94710879715769</v>
       </c>
       <c r="C10" t="n">
-        <v>24.62714116103124</v>
+        <v>37.72365553568369</v>
       </c>
       <c r="D10" t="n">
-        <v>51.53193699591508</v>
+        <v>69.04140730115694</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.04167537193487</v>
+        <v>12.61643974727576</v>
       </c>
       <c r="C11" t="n">
-        <v>24.34439782220815</v>
+        <v>38.20471191076462</v>
       </c>
       <c r="D11" t="n">
-        <v>43.5356019448248</v>
+        <v>58.10670137125595</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5.207189823325082</v>
+        <v>11.28224461720434</v>
       </c>
       <c r="C12" t="n">
-        <v>22.56448923440869</v>
+        <v>36.66729500591412</v>
       </c>
       <c r="D12" t="n">
-        <v>42.52538355715483</v>
+        <v>59.44875048296136</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.682936549257286</v>
+        <v>10.926851948267</v>
       </c>
       <c r="C13" t="n">
-        <v>21.853703896534</v>
+        <v>36.94316611080748</v>
       </c>
       <c r="D13" t="n">
-        <v>43.70740779306801</v>
+        <v>60.87817514034472</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.916592502868027</v>
+        <v>11.67690719431156</v>
       </c>
       <c r="C14" t="n">
-        <v>23.04652735719387</v>
+        <v>39.33274002294421</v>
       </c>
       <c r="D14" t="n">
-        <v>44.55661955724149</v>
+        <v>63.60841550585509</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.733406592801372</v>
+        <v>13.61684065790326</v>
       </c>
       <c r="C15" t="n">
-        <v>25.80032966760617</v>
+        <v>45.50891483036089</v>
       </c>
       <c r="D15" t="n">
-        <v>41.92553570986004</v>
+        <v>61.27578296056467</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>6.199736752318607</v>
+        <v>14.87936820556466</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>51.25115715250048</v>
       </c>
       <c r="D16" t="n">
-        <v>40.09163099832699</v>
+        <v>57.864209688307</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.611089040398022</v>
+        <v>16.99994324673777</v>
       </c>
       <c r="C17" t="n">
-        <v>31.16656261901925</v>
+        <v>56.19425684338318</v>
       </c>
       <c r="D17" t="n">
-        <v>35.8887690764464</v>
+        <v>53.8331536146696</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4114,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.955682484588652</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="C18" t="n">
-        <v>33.70830742531424</v>
+        <v>62.06608986248335</v>
       </c>
       <c r="D18" t="n">
-        <v>30.49799243242716</v>
+        <v>45.47946239923349</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4128,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.823547455142832</v>
+        <v>20.46158565191202</v>
       </c>
       <c r="C19" t="n">
-        <v>36.10868056219768</v>
+        <v>66.80105904006572</v>
       </c>
       <c r="D19" t="n">
-        <v>22.8688310227252</v>
+        <v>34.9050578767911</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>7.397468951499714</v>
+        <v>20.84741249968101</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>73.30219233758808</v>
       </c>
       <c r="D20" t="n">
-        <v>13.4499435481813</v>
+        <v>20.17491532227195</v>
       </c>
     </row>
     <row r="21">
@@ -4156,13 +4156,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>11.44977350273866</v>
+        <v>27.41820207255788</v>
       </c>
       <c r="C21" t="n">
-        <v>54.95891281314559</v>
+        <v>99.77179087514119</v>
       </c>
       <c r="D21" t="n">
-        <v>0.763318233515911</v>
+        <v>0.761616724237719</v>
       </c>
     </row>
   </sheetData>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.284526907782328</v>
+        <v>1.207549676223577</v>
       </c>
       <c r="C2" t="n">
-        <v>3.607922813107028</v>
+        <v>9.12632665867835</v>
       </c>
       <c r="D2" t="n">
-        <v>10.53611636197677</v>
+        <v>17.4054050485917</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>12.16385405561798</v>
+        <v>2.199114857512855</v>
       </c>
       <c r="C3" t="n">
-        <v>21.24502031990098</v>
+        <v>40.54127144687203</v>
       </c>
       <c r="D3" t="n">
-        <v>60.06332454581985</v>
+        <v>42.01880174176349</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>37.30543101367455</v>
+        <v>3.994731408580271</v>
       </c>
       <c r="C4" t="n">
-        <v>81.86008707550754</v>
+        <v>63.21375292874787</v>
       </c>
       <c r="D4" t="n">
-        <v>147.4732313934346</v>
+        <v>102.2549138835308</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>33.96847056693964</v>
+        <v>12.0509530696296</v>
       </c>
       <c r="C5" t="n">
-        <v>219.248806050919</v>
+        <v>134.7694161004809</v>
       </c>
       <c r="D5" t="n">
-        <v>146.9921750183537</v>
+        <v>137.4446785945535</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>20.28683456055609</v>
+        <v>21.1321193339126</v>
       </c>
       <c r="C6" t="n">
-        <v>267.2709950041517</v>
+        <v>233.8218689727586</v>
       </c>
       <c r="D6" t="n">
-        <v>80.54356340411259</v>
+        <v>114.5964642736175</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>6.767186925373263</v>
+        <v>19.04394196697963</v>
       </c>
       <c r="C7" t="n">
-        <v>168.520920424782</v>
+        <v>327.2204368162789</v>
       </c>
       <c r="D7" t="n">
-        <v>34.6743471662931</v>
+        <v>69.58824077242241</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>2.002765316663493</v>
+        <v>9.763480918734528</v>
       </c>
       <c r="C8" t="n">
-        <v>93.6292785540183</v>
+        <v>324.9486726286518</v>
       </c>
       <c r="D8" t="n">
-        <v>25.20146356801562</v>
+        <v>39.55461500410399</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.5546874528994477</v>
+        <v>2.995312245657018</v>
       </c>
       <c r="C9" t="n">
-        <v>40.82499653339935</v>
+        <v>209.4499822148314</v>
       </c>
       <c r="D9" t="n">
-        <v>20.85624822901923</v>
+        <v>27.5124976638126</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>0.7117670855789376</v>
       </c>
       <c r="C10" t="n">
-        <v>23.63066724122073</v>
+        <v>89.96735961717772</v>
       </c>
       <c r="D10" t="n">
-        <v>19.3600647277471</v>
+        <v>22.776546738526</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>17.23654444346124</v>
+        <v>37.49392657288993</v>
       </c>
       <c r="D11" t="n">
-        <v>16.70345544005523</v>
+        <v>19.54659679155399</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>11.28224461720434</v>
+        <v>20.61179305066178</v>
       </c>
       <c r="D12" t="n">
-        <v>13.66887328622834</v>
+        <v>15.62156946997525</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>9.886199381765381</v>
+        <v>16.1301147807751</v>
       </c>
       <c r="D13" t="n">
-        <v>9.886199381765381</v>
+        <v>10.40652566501619</v>
       </c>
     </row>
     <row r="14">
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.3072870314292517</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>16.28621266575034</v>
+        <v>16.90078672860884</v>
       </c>
       <c r="D14" t="n">
-        <v>5.223879534297279</v>
+        <v>4.302018440009523</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>25.083653843506</v>
+        <v>11.46681318560274</v>
       </c>
       <c r="D15" t="n">
-        <v>2.5083653843506</v>
+        <v>0.3583379120500857</v>
       </c>
     </row>
     <row r="16">
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>2.89321048441535</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.94095626902495</v>
+        <v>5.142394474844792</v>
       </c>
       <c r="C2" t="n">
-        <v>3.787582642984194</v>
+        <v>9.751699946283567</v>
       </c>
       <c r="D2" t="n">
-        <v>10.94943214546467</v>
+        <v>16.6818569905618</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>10.35252954128262</v>
+        <v>7.66744957016759</v>
       </c>
       <c r="C3" t="n">
-        <v>17.48492661263569</v>
+        <v>20.61670178918302</v>
       </c>
       <c r="D3" t="n">
-        <v>10.34762080276138</v>
+        <v>12.2669375645639</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.008254892261474</v>
+        <v>0.9189158511750145</v>
       </c>
       <c r="C4" t="n">
-        <v>1.454950097693773</v>
+        <v>1.710204500797944</v>
       </c>
       <c r="D4" t="n">
-        <v>19.62906359871073</v>
+        <v>18.45489334443154</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.68784528777852</v>
+        <v>3.632466505713199</v>
       </c>
       <c r="C5" t="n">
-        <v>9.424777960769381</v>
+        <v>8.29576810088555</v>
       </c>
       <c r="D5" t="n">
-        <v>28.49522711576368</v>
+        <v>24.20008090968388</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.130834486572086</v>
+        <v>5.75598678999905</v>
       </c>
       <c r="C6" t="n">
-        <v>18.47551004622073</v>
+        <v>14.32958949118645</v>
       </c>
       <c r="D6" t="n">
-        <v>32.52333794628834</v>
+        <v>28.6591789823729</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>6.108434215823654</v>
       </c>
       <c r="C7" t="n">
-        <v>20.9603134856694</v>
+        <v>16.58859095865835</v>
       </c>
       <c r="D7" t="n">
-        <v>32.69808903764427</v>
+        <v>27.90716024091983</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.762098260402782</v>
+        <v>6.508987279156353</v>
       </c>
       <c r="C8" t="n">
-        <v>21.69662426385451</v>
+        <v>17.19040230136165</v>
       </c>
       <c r="D8" t="n">
-        <v>35.79943003535994</v>
+        <v>32.04424506661589</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.874999246391162</v>
+        <v>6.656249434793372</v>
       </c>
       <c r="C9" t="n">
-        <v>22.74218556887735</v>
+        <v>18.74843590800133</v>
       </c>
       <c r="D9" t="n">
-        <v>39.2718716652809</v>
+        <v>34.72343455150543</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.256498192715677</v>
+        <v>6.26355035309465</v>
       </c>
       <c r="C10" t="n">
-        <v>25.62361508084176</v>
+        <v>21.78007281871549</v>
       </c>
       <c r="D10" t="n">
-        <v>50.67781649322036</v>
+        <v>46.12250714551515</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.75246070980956</v>
+        <v>5.330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>27.36523550817559</v>
+        <v>22.7451308119901</v>
       </c>
       <c r="D11" t="n">
-        <v>46.37874329632356</v>
+        <v>41.04785326226338</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5.641122308602172</v>
+        <v>4.339324852770901</v>
       </c>
       <c r="C12" t="n">
-        <v>25.81898287398687</v>
+        <v>21.69662426385451</v>
       </c>
       <c r="D12" t="n">
-        <v>43.17628228507047</v>
+        <v>39.4878561602152</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.943099690882691</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C13" t="n">
-        <v>23.93500902953724</v>
+        <v>20.55288818840698</v>
       </c>
       <c r="D13" t="n">
-        <v>44.22773407631881</v>
+        <v>40.06512381031234</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.994731408580272</v>
       </c>
       <c r="C14" t="n">
-        <v>23.96838845148163</v>
+        <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>40.86917518009047</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.375068680751286</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>26.15866757965626</v>
+        <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
-        <v>42.28387362191012</v>
+        <v>39.77550823755952</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.7864209688307</v>
+        <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>26.03889435973815</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>36.78510473042374</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.138868394655306</v>
+        <v>5.194427103169874</v>
       </c>
       <c r="C17" t="n">
-        <v>31.63878326476196</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.36098972218912</v>
+        <v>34.47210713921825</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +4736,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.42062998577414</v>
+        <v>5.885577486959628</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>31.03304493124168</v>
       </c>
       <c r="D18" t="n">
-        <v>31.03304493124168</v>
+        <v>28.89283493598363</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.221736112439537</v>
+        <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.09962384868121</v>
       </c>
       <c r="D19" t="n">
-        <v>23.47064236542849</v>
+        <v>21.66520833731861</v>
       </c>
     </row>
     <row r="20">
@@ -4767,10 +4767,10 @@
         <v>6.724971774090649</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>14.12244072559037</v>
+        <v>12.77744637077223</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.3985002576928</v>
+        <v>11.67745464276753</v>
       </c>
       <c r="C21" t="n">
-        <v>70.14508958439173</v>
+        <v>59.94426716620664</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576294147963859</v>
+        <v>0.7784969761845018</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.322635141798706</v>
+        <v>2.924626410951248</v>
       </c>
       <c r="C2" t="n">
-        <v>3.499930565639879</v>
+        <v>6.348962403364123</v>
       </c>
       <c r="D2" t="n">
-        <v>14.54753748152924</v>
+        <v>18.72487396309942</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.48140053244621</v>
+        <v>14.10771451002667</v>
       </c>
       <c r="C3" t="n">
-        <v>15.76686813020378</v>
+        <v>32.27986451563513</v>
       </c>
       <c r="D3" t="n">
-        <v>17.04314014572463</v>
+        <v>23.86137795171873</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>12.12458414744811</v>
+        <v>9.546514676095985</v>
       </c>
       <c r="C4" t="n">
-        <v>27.60576369571606</v>
+        <v>34.05093737409637</v>
       </c>
       <c r="D4" t="n">
-        <v>20.49692856926491</v>
+        <v>20.72665753205866</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3.067961575771283</v>
+        <v>2.454369260617026</v>
       </c>
       <c r="C5" t="n">
-        <v>5.399612373357458</v>
+        <v>5.154175447295755</v>
       </c>
       <c r="D5" t="n">
-        <v>29.10881943091793</v>
+        <v>25.72178985126644</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.446556336712058</v>
+        <v>5.514476854754335</v>
       </c>
       <c r="C6" t="n">
-        <v>16.54343056426301</v>
+        <v>13.72581465307466</v>
       </c>
       <c r="D6" t="n">
-        <v>34.77743067523902</v>
+        <v>30.06798693796707</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.521970983489814</v>
+        <v>6.767186925373263</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>19.22360179685679</v>
       </c>
       <c r="D7" t="n">
-        <v>35.27321326588365</v>
+        <v>30.48228446915921</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.596583809012571</v>
+        <v>6.926230053461247</v>
       </c>
       <c r="C8" t="n">
-        <v>25.61870634232051</v>
+        <v>20.36144738607885</v>
       </c>
       <c r="D8" t="n">
-        <v>36.80081269369168</v>
+        <v>32.96217917008666</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.318749208710722</v>
+        <v>7.09999939711293</v>
       </c>
       <c r="C9" t="n">
-        <v>25.5156228333746</v>
+        <v>20.85624822901923</v>
       </c>
       <c r="D9" t="n">
-        <v>40.27030908049991</v>
+        <v>35.38905949498476</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.968265278294615</v>
+        <v>6.690610604442014</v>
       </c>
       <c r="C10" t="n">
-        <v>27.3318560862312</v>
+        <v>22.91890015564179</v>
       </c>
       <c r="D10" t="n">
-        <v>50.1084028247572</v>
+        <v>45.26838664282043</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7.463246047684251</v>
+        <v>5.863979037466197</v>
       </c>
       <c r="C11" t="n">
-        <v>29.49759152179966</v>
+        <v>24.87748682561417</v>
       </c>
       <c r="D11" t="n">
-        <v>47.97801030654161</v>
+        <v>43.35790561035613</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.075054793879263</v>
+        <v>4.773257338047991</v>
       </c>
       <c r="C12" t="n">
-        <v>29.29044275620359</v>
+        <v>24.5171854181556</v>
       </c>
       <c r="D12" t="n">
-        <v>44.69504598354028</v>
+        <v>40.57268737340794</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.203262832508096</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C13" t="n">
-        <v>26.79680358741669</v>
+        <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
-        <v>44.22773407631881</v>
+        <v>40.32528695193774</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>25.50482360862789</v>
+        <v>22.43195329433537</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>41.17646221151972</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.0167307687012</v>
+        <v>3.941717032550943</v>
       </c>
       <c r="C15" t="n">
-        <v>26.51700549170635</v>
+        <v>23.65030219530566</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>40.1338461496096</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.373105185342793</v>
+        <v>4.546473618366978</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>26.03889435973815</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>37.19842051391164</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.66664774891259</v>
+        <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>34.94432778496098</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5047,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.885577486959628</v>
+        <v>5.350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>29.42788743479814</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.619924769736241</v>
+        <v>5.416302084329653</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.09962384868121</v>
       </c>
       <c r="D19" t="n">
-        <v>24.07245370813179</v>
+        <v>22.26701968002191</v>
       </c>
     </row>
     <row r="20">
@@ -5078,10 +5078,10 @@
         <v>6.052474596681584</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>14.79493790299943</v>
+        <v>13.4499435481813</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.44338816602797</v>
+        <v>13.62729817612124</v>
       </c>
       <c r="C21" t="n">
-        <v>86.15784976836656</v>
+        <v>73.74773130606789</v>
       </c>
       <c r="D21" t="n">
-        <v>3.251239613900625</v>
+        <v>1.603211550131911</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.111559385385641</v>
+        <v>2.330669049881928</v>
       </c>
       <c r="C2" t="n">
-        <v>3.033600406122644</v>
+        <v>7.029313562407163</v>
       </c>
       <c r="D2" t="n">
-        <v>17.33668270929442</v>
+        <v>17.49867108049515</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.49827016986765</v>
+        <v>11.849694790259</v>
       </c>
       <c r="C3" t="n">
-        <v>14.46114368355552</v>
+        <v>27.5183881500381</v>
       </c>
       <c r="D3" t="n">
-        <v>24.72531593145592</v>
+        <v>33.82120841130261</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>25.4233385491754</v>
+        <v>20.30548776693678</v>
       </c>
       <c r="C4" t="n">
-        <v>34.34447993766616</v>
+        <v>63.02231212641975</v>
       </c>
       <c r="D4" t="n">
-        <v>24.44060909722434</v>
+        <v>28.42257778564941</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>11.04466167277662</v>
+        <v>8.982991493858316</v>
       </c>
       <c r="C5" t="n">
-        <v>31.83316931020283</v>
+        <v>39.785325714602</v>
       </c>
       <c r="D5" t="n">
-        <v>29.82058651649687</v>
+        <v>27.39076094848602</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.916993413495527</v>
+        <v>4.508185457901354</v>
       </c>
       <c r="C6" t="n">
-        <v>12.19625172985813</v>
+        <v>10.58618549489336</v>
       </c>
       <c r="D6" t="n">
-        <v>36.6290068454485</v>
+        <v>31.95981476405067</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.581857593448868</v>
+        <v>6.886960145291375</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>19.82246789644735</v>
       </c>
       <c r="D7" t="n">
-        <v>37.42913122440964</v>
+        <v>32.81786225756237</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.34762080276138</v>
+        <v>7.510369937488099</v>
       </c>
       <c r="C8" t="n">
-        <v>29.87458264023044</v>
+        <v>23.699389580518</v>
       </c>
       <c r="D8" t="n">
-        <v>38.55323234577224</v>
+        <v>33.96356182841841</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.09531164276995</v>
+        <v>7.432811868852599</v>
       </c>
       <c r="C9" t="n">
-        <v>29.39843500367073</v>
+        <v>23.96249796525614</v>
       </c>
       <c r="D9" t="n">
-        <v>41.26874649571891</v>
+        <v>36.49843440078366</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.395325529641976</v>
+        <v>7.117670855789377</v>
       </c>
       <c r="C10" t="n">
-        <v>29.89421759431538</v>
+        <v>24.76949457814703</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>44.69897297435728</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.351727720027615</v>
+        <v>6.397068040872215</v>
       </c>
       <c r="C11" t="n">
-        <v>31.45225120095506</v>
+        <v>26.47675383583222</v>
       </c>
       <c r="D11" t="n">
-        <v>49.75497365122833</v>
+        <v>44.42408361716816</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.508987279156352</v>
+        <v>5.207189823325082</v>
       </c>
       <c r="C12" t="n">
-        <v>32.11100391050467</v>
+        <v>27.12078032981814</v>
       </c>
       <c r="D12" t="n">
-        <v>45.77987719673301</v>
+        <v>42.09145107187774</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.463425974133501</v>
+        <v>4.162610266006476</v>
       </c>
       <c r="C13" t="n">
-        <v>29.91876128692155</v>
+        <v>25.49598787928967</v>
       </c>
       <c r="D13" t="n">
-        <v>45.00822350119503</v>
+        <v>41.10577637681396</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>27.9631198600619</v>
+        <v>24.27567548291088</v>
       </c>
       <c r="D14" t="n">
-        <v>45.7857676829585</v>
+        <v>41.48374924294897</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>3.583379120500858</v>
       </c>
       <c r="C15" t="n">
-        <v>27.5920192278566</v>
+        <v>24.36697801940583</v>
       </c>
       <c r="D15" t="n">
-        <v>43.35888735806038</v>
+        <v>40.1338461496096</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.959789401854886</v>
+        <v>4.133157834879071</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>26.45221014322606</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>37.61173629739955</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.194427103169874</v>
+        <v>4.249985811684442</v>
       </c>
       <c r="C17" t="n">
-        <v>32.58322455624739</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>37.30543101367455</v>
+        <v>35.41654843070368</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.350524988145117</v>
+        <v>4.815472489330605</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>29.42788743479814</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.018113427032947</v>
+        <v>4.814490741626358</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>22.8688310227252</v>
       </c>
     </row>
     <row r="20">
@@ -5389,10 +5389,10 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>15.46743508040849</v>
+        <v>14.12244072559037</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.7411718735065</v>
+        <v>14.83553582102871</v>
       </c>
       <c r="C21" t="n">
-        <v>102.1211484283897</v>
+        <v>87.36482205716906</v>
       </c>
       <c r="D21" t="n">
-        <v>5.02235156205195</v>
+        <v>2.472589303504785</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.417864669110647</v>
+        <v>1.506982726018854</v>
       </c>
       <c r="C2" t="n">
-        <v>7.330710107610932</v>
+        <v>4.593597508170825</v>
       </c>
       <c r="D2" t="n">
-        <v>26.40606800112646</v>
+        <v>17.72447305247191</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.17781950765569</v>
+        <v>9.714393533522189</v>
       </c>
       <c r="C3" t="n">
-        <v>12.88543861823939</v>
+        <v>27.42021337961341</v>
       </c>
       <c r="D3" t="n">
-        <v>32.39767424014475</v>
+        <v>39.97185777840889</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.8692729910817</v>
+        <v>21.84977690571701</v>
       </c>
       <c r="C4" t="n">
-        <v>35.40378571054848</v>
+        <v>66.5320601691021</v>
       </c>
       <c r="D4" t="n">
-        <v>30.71986741358695</v>
+        <v>38.97734735400687</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>24.86276061005048</v>
+        <v>20.44489594093983</v>
       </c>
       <c r="C5" t="n">
-        <v>49.23464736797755</v>
+        <v>83.49764224619123</v>
       </c>
       <c r="D5" t="n">
-        <v>32.0295188510522</v>
+        <v>31.26866438026092</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>10.465430527271</v>
+        <v>8.573602701187397</v>
       </c>
       <c r="C6" t="n">
-        <v>32.28182801104362</v>
+        <v>39.32586778901449</v>
       </c>
       <c r="D6" t="n">
-        <v>37.8768081775462</v>
+        <v>33.85164259013428</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>6.347980655659875</v>
       </c>
       <c r="C7" t="n">
-        <v>21.19985992550562</v>
+        <v>17.66654993792135</v>
       </c>
       <c r="D7" t="n">
-        <v>40.00425545264903</v>
+        <v>35.03366682604743</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.76486357706628</v>
+        <v>7.844164156932015</v>
       </c>
       <c r="C8" t="n">
-        <v>31.87734795689393</v>
+        <v>25.36836067773758</v>
       </c>
       <c r="D8" t="n">
-        <v>40.38910055271378</v>
+        <v>35.21529015133309</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.76093658624928</v>
+        <v>7.876561831172157</v>
       </c>
       <c r="C9" t="n">
-        <v>33.9468721174462</v>
+        <v>27.62343515439249</v>
       </c>
       <c r="D9" t="n">
-        <v>41.93437143919824</v>
+        <v>37.49687181600267</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.964739198105127</v>
+        <v>7.402377690020952</v>
       </c>
       <c r="C10" t="n">
-        <v>33.45305302221006</v>
+        <v>27.47420950334699</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>44.55661955724149</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.884816723433632</v>
+        <v>6.75246070980956</v>
       </c>
       <c r="C11" t="n">
-        <v>33.93999988351647</v>
+        <v>28.43141351498762</v>
       </c>
       <c r="D11" t="n">
-        <v>50.46575898910303</v>
+        <v>45.13486895504285</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.159886007071988</v>
+        <v>5.641122308602172</v>
       </c>
       <c r="C12" t="n">
-        <v>34.28066633689012</v>
+        <v>29.29044275620359</v>
       </c>
       <c r="D12" t="n">
-        <v>47.29864089520282</v>
+        <v>43.39324852770902</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.723589115758904</v>
+        <v>4.422773407631881</v>
       </c>
       <c r="C13" t="n">
-        <v>33.30088212805181</v>
+        <v>28.35778243716912</v>
       </c>
       <c r="D13" t="n">
-        <v>45.78871292607123</v>
+        <v>41.88626580169016</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>30.72870314292517</v>
+        <v>26.42668470291564</v>
       </c>
       <c r="D14" t="n">
-        <v>45.7857676829585</v>
+        <v>41.48374924294897</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.30005494460103</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>29.38370878810703</v>
+        <v>25.80032966760617</v>
       </c>
       <c r="D15" t="n">
-        <v>44.07556318216055</v>
+        <v>40.49218406165969</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.546473618366978</v>
+        <v>3.719842051391165</v>
       </c>
       <c r="C16" t="n">
-        <v>30.17205219461722</v>
+        <v>26.86552592671396</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>38.02505208088746</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>4.722206457427158</v>
+        <v>3.777765165941727</v>
       </c>
       <c r="C17" t="n">
-        <v>33.0554452019901</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>37.77765165941727</v>
+        <v>35.41654843070368</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>4.815472489330605</v>
+        <v>4.280419990516093</v>
       </c>
       <c r="C18" t="n">
-        <v>35.31346492175777</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>32.1031499288707</v>
+        <v>29.96293993361265</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>5.416302084329653</v>
+        <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>23.47064236542849</v>
       </c>
     </row>
     <row r="20">
@@ -5700,10 +5700,10 @@
         <v>4.707480241863455</v>
       </c>
       <c r="C20" t="n">
-        <v>39.67733346713483</v>
+        <v>35.64235040268044</v>
       </c>
       <c r="D20" t="n">
-        <v>16.13993225781756</v>
+        <v>14.79493790299943</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.0751107693642</v>
+        <v>16.07478633631209</v>
       </c>
       <c r="C21" t="n">
-        <v>117.9185797810903</v>
+        <v>101.5249663346027</v>
       </c>
       <c r="D21" t="n">
-        <v>6.885756483567316</v>
+        <v>3.384165544486757</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.784056562794707</v>
+        <v>2.517201113688822</v>
       </c>
       <c r="C2" t="n">
-        <v>9.740900721536853</v>
+        <v>6.975317438673588</v>
       </c>
       <c r="D2" t="n">
-        <v>29.46813909067226</v>
+        <v>17.28857707178633</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.55302705712722</v>
+        <v>7.215845626214056</v>
       </c>
       <c r="C3" t="n">
-        <v>20.68051538995906</v>
+        <v>21.8684301120977</v>
       </c>
       <c r="D3" t="n">
-        <v>42.57348919466293</v>
+        <v>44.55171081872026</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>21.19887817780138</v>
+        <v>20.3437759274024</v>
       </c>
       <c r="C4" t="n">
-        <v>28.15456066239003</v>
+        <v>67.70623042338129</v>
       </c>
       <c r="D4" t="n">
-        <v>34.2423781764245</v>
+        <v>49.63421868360599</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>21.25483779694345</v>
+        <v>26.87534340375644</v>
       </c>
       <c r="C5" t="n">
-        <v>42.87783098297945</v>
+        <v>104.801567428347</v>
       </c>
       <c r="D5" t="n">
-        <v>29.15790681613028</v>
+        <v>37.5518496874405</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>12.15600007398401</v>
+        <v>17.91198686398306</v>
       </c>
       <c r="C6" t="n">
-        <v>38.52083467153211</v>
+        <v>87.62785483795757</v>
       </c>
       <c r="D6" t="n">
-        <v>30.43025184083414</v>
+        <v>36.38749691020379</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.389794896314989</v>
+        <v>8.444012004226815</v>
       </c>
       <c r="C7" t="n">
-        <v>21.97838585497334</v>
+        <v>37.4890178343687</v>
       </c>
       <c r="D7" t="n">
-        <v>31.38058361854505</v>
+        <v>37.18958478457343</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.840016181936775</v>
+        <v>7.677267047210056</v>
       </c>
       <c r="C8" t="n">
-        <v>18.77592484372025</v>
+        <v>24.95111790343269</v>
       </c>
       <c r="D8" t="n">
-        <v>30.12492830481337</v>
+        <v>36.63391558396972</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.881249585515139</v>
+        <v>8.320311793491715</v>
       </c>
       <c r="C9" t="n">
-        <v>22.18749811597791</v>
+        <v>30.39687241888974</v>
       </c>
       <c r="D9" t="n">
-        <v>30.28593492830985</v>
+        <v>38.49530923122167</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.412955930589413</v>
+        <v>7.829437941368314</v>
       </c>
       <c r="C10" t="n">
-        <v>21.35301256736813</v>
+        <v>30.89069151412589</v>
       </c>
       <c r="D10" t="n">
-        <v>33.73775985644164</v>
+        <v>44.12955930589413</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.731623023842126</v>
+        <v>7.107853378746905</v>
       </c>
       <c r="C11" t="n">
-        <v>20.61277479836603</v>
+        <v>30.74146586308036</v>
       </c>
       <c r="D11" t="n">
-        <v>34.29539255245382</v>
+        <v>46.20104696185489</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.037527396939631</v>
+        <v>6.075054793879263</v>
       </c>
       <c r="C12" t="n">
-        <v>20.17786056538469</v>
+        <v>31.02617269731195</v>
       </c>
       <c r="D12" t="n">
-        <v>32.32797015314322</v>
+        <v>44.47807974090174</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.341468274628643</v>
+        <v>4.682936549257286</v>
       </c>
       <c r="C13" t="n">
-        <v>18.99190933865455</v>
+        <v>30.95941385342317</v>
       </c>
       <c r="D13" t="n">
-        <v>30.17892442854696</v>
+        <v>42.14642894331557</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>17.8226478228966</v>
+        <v>28.88498095434966</v>
       </c>
       <c r="D14" t="n">
-        <v>29.80684204863741</v>
+        <v>41.79103627437823</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>16.12520604225386</v>
+        <v>27.23368131580652</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>40.85052197370977</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>3.306526267903257</v>
       </c>
       <c r="C16" t="n">
-        <v>15.70599977254047</v>
+        <v>27.69215749368978</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>38.02505208088746</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.416661937228147</v>
+        <v>3.305544520199011</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>35.8887690764464</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.070104997629023</v>
+        <v>3.745367491701582</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>29.96293993361265</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.203622685406589</v>
+        <v>3.610868056219768</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>24.07245370813179</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.34499435481813</v>
+        <v>4.03498306445439</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>35.64235040268044</v>
       </c>
       <c r="D20" t="n">
-        <v>10.08745766113597</v>
+        <v>15.46743508040849</v>
       </c>
     </row>
     <row r="21">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.068242384791311</v>
+        <v>17.33936216807224</v>
       </c>
       <c r="C21" t="n">
-        <v>67.14830265551744</v>
+        <v>114.4397903092768</v>
       </c>
       <c r="D21" t="n">
-        <v>5.301181788593483</v>
+        <v>4.33484054201806</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.468915549731481</v>
+        <v>2.769510273680252</v>
       </c>
       <c r="C2" t="n">
-        <v>4.968625131193107</v>
+        <v>8.085674092176729</v>
       </c>
       <c r="D2" t="n">
-        <v>25.40075835197772</v>
+        <v>26.73397173434489</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.64414966717292</v>
+        <v>7.868707849538186</v>
       </c>
       <c r="C3" t="n">
-        <v>32.27495577711389</v>
+        <v>24.65168485363741</v>
       </c>
       <c r="D3" t="n">
-        <v>57.81021356457343</v>
+        <v>47.51658888554562</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>24.87454158250144</v>
+        <v>17.07651956766902</v>
       </c>
       <c r="C4" t="n">
-        <v>43.54640116957152</v>
+        <v>60.77607337910305</v>
       </c>
       <c r="D4" t="n">
-        <v>49.3406761200362</v>
+        <v>59.56361496435823</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>27.66074156715389</v>
+        <v>28.6424892714007</v>
       </c>
       <c r="C5" t="n">
-        <v>48.79286090106649</v>
+        <v>115.03628724512</v>
       </c>
       <c r="D5" t="n">
-        <v>35.36746104549135</v>
+        <v>45.4794623992335</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>22.13841073076558</v>
+        <v>26.76735115628929</v>
       </c>
       <c r="C6" t="n">
-        <v>56.63407981488576</v>
+        <v>126.3499477888603</v>
       </c>
       <c r="D6" t="n">
-        <v>33.48937768726721</v>
+        <v>39.9698942830004</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>10.77958979262998</v>
+        <v>14.43267300013236</v>
       </c>
       <c r="C7" t="n">
-        <v>42.33983324105218</v>
+        <v>79.88873768537994</v>
       </c>
       <c r="D7" t="n">
-        <v>33.77604801690726</v>
+        <v>39.46527596301753</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.674501730546564</v>
+        <v>8.595201150680824</v>
       </c>
       <c r="C8" t="n">
-        <v>25.36836067773758</v>
+        <v>37.21805546799658</v>
       </c>
       <c r="D8" t="n">
-        <v>32.04424506661589</v>
+        <v>38.05254101660637</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.214062057254808</v>
+        <v>8.320311793491715</v>
       </c>
       <c r="C9" t="n">
-        <v>23.62968549351647</v>
+        <v>31.50624732468863</v>
       </c>
       <c r="D9" t="n">
-        <v>31.72812230584841</v>
+        <v>39.49374664644068</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.840016181936776</v>
+        <v>8.256498192715677</v>
       </c>
       <c r="C10" t="n">
-        <v>24.91184799526281</v>
+        <v>33.88011327355743</v>
       </c>
       <c r="D10" t="n">
-        <v>34.16482010778901</v>
+        <v>43.84485247166256</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.08701569277947</v>
+        <v>7.285549713215578</v>
       </c>
       <c r="C11" t="n">
-        <v>23.45591614986479</v>
+        <v>33.7623035490478</v>
       </c>
       <c r="D11" t="n">
-        <v>34.82848155585983</v>
+        <v>46.91183229972957</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.254493639578176</v>
+        <v>6.292021036517808</v>
       </c>
       <c r="C12" t="n">
-        <v>22.56448923440869</v>
+        <v>33.41280136633594</v>
       </c>
       <c r="D12" t="n">
-        <v>33.41280136633594</v>
+        <v>44.91201222617883</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>4.943099690882691</v>
       </c>
       <c r="C13" t="n">
-        <v>21.33337761328319</v>
+        <v>32.780555844801</v>
       </c>
       <c r="D13" t="n">
-        <v>30.95941385342317</v>
+        <v>42.92691836819179</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>19.66637001147211</v>
+        <v>31.34327720578367</v>
       </c>
       <c r="D14" t="n">
-        <v>29.80684204863741</v>
+        <v>42.09832330580748</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>17.91689560250429</v>
+        <v>29.02537087605695</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>40.85052197370977</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>2.89321048441535</v>
       </c>
       <c r="C16" t="n">
-        <v>16.53263133951629</v>
+        <v>28.51878906066559</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>38.43836786437537</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>2.833323874456295</v>
       </c>
       <c r="C17" t="n">
-        <v>16.99994324673777</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>35.8887690764464</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.070104997629023</v>
+        <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>30.49799243242716</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>3.009056713516474</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>24.67426505083508</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.672497177409065</v>
+        <v>3.362485887045325</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>35.64235040268044</v>
       </c>
       <c r="D20" t="n">
-        <v>10.08745766113597</v>
+        <v>15.46743508040849</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.296353744685441</v>
+        <v>17.73658427070609</v>
       </c>
       <c r="C21" t="n">
-        <v>77.52375853728282</v>
+        <v>126.8165775355485</v>
       </c>
       <c r="D21" t="n">
-        <v>6.384309526599761</v>
+        <v>5.320975281211826</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.838633523605029</v>
+        <v>2.470077223884975</v>
       </c>
       <c r="C2" t="n">
-        <v>7.059747741238813</v>
+        <v>4.98040610364407</v>
       </c>
       <c r="D2" t="n">
-        <v>24.83330817892307</v>
+        <v>20.92791581142926</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.64414966717292</v>
+        <v>11.02502671869168</v>
       </c>
       <c r="C3" t="n">
-        <v>24.20498964820511</v>
+        <v>38.95574890451343</v>
       </c>
       <c r="D3" t="n">
-        <v>65.17823008494575</v>
+        <v>54.28573930632738</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.47362866627024</v>
+        <v>13.7582123273148</v>
       </c>
       <c r="C4" t="n">
-        <v>66.27680576599792</v>
+        <v>95.35028227956296</v>
       </c>
       <c r="D4" t="n">
-        <v>68.1912137892792</v>
+        <v>56.25807044415922</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>33.50214040742241</v>
+        <v>15.06982726018854</v>
       </c>
       <c r="C5" t="n">
-        <v>67.56878574478674</v>
+        <v>75.49639845657973</v>
       </c>
       <c r="D5" t="n">
-        <v>45.70035563268903</v>
+        <v>37.40458753180348</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>30.71201343195298</v>
+        <v>8.93586760405447</v>
       </c>
       <c r="C6" t="n">
-        <v>68.74982823299565</v>
+        <v>52.60891422747383</v>
       </c>
       <c r="D6" t="n">
-        <v>37.15227837181205</v>
+        <v>25.96231803880691</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>19.52303484665207</v>
+        <v>5.689227946110266</v>
       </c>
       <c r="C7" t="n">
-        <v>64.91708519561608</v>
+        <v>26.17044855210722</v>
       </c>
       <c r="D7" t="n">
-        <v>36.4110588551057</v>
+        <v>26.70942804173872</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.012443924985718</v>
+        <v>5.757950285407543</v>
       </c>
       <c r="C8" t="n">
-        <v>42.55876297909923</v>
+        <v>23.19869825135213</v>
       </c>
       <c r="D8" t="n">
-        <v>34.29735604786232</v>
+        <v>29.04009709162065</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.768749510154256</v>
+        <v>5.879687000734146</v>
       </c>
       <c r="C9" t="n">
-        <v>28.73281006019139</v>
+        <v>25.84843530511426</v>
       </c>
       <c r="D9" t="n">
-        <v>32.8374972116473</v>
+        <v>33.39218466454675</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.124723016168351</v>
+        <v>5.267076433284139</v>
       </c>
       <c r="C10" t="n">
-        <v>27.47420950334699</v>
+        <v>26.47773558353648</v>
       </c>
       <c r="D10" t="n">
-        <v>34.87658719336794</v>
+        <v>36.72718161587318</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.442408361716816</v>
+        <v>4.620104696185489</v>
       </c>
       <c r="C11" t="n">
-        <v>27.00984283923824</v>
+        <v>26.65445017030089</v>
       </c>
       <c r="D11" t="n">
-        <v>35.18387422479719</v>
+        <v>35.89465956267188</v>
       </c>
     </row>
     <row r="12">
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.471459882216721</v>
+        <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>25.16808414607123</v>
+        <v>26.68684784454105</v>
       </c>
       <c r="D12" t="n">
-        <v>34.49763257952867</v>
+        <v>34.93156506480576</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>23.41468274628643</v>
+        <v>25.75615102091507</v>
       </c>
       <c r="D13" t="n">
-        <v>31.73990327829938</v>
+        <v>34.86186097780424</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>2.458296251434013</v>
       </c>
       <c r="C14" t="n">
-        <v>21.81737923147687</v>
+        <v>24.27567548291088</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>34.10886048864694</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>2.150027472300515</v>
       </c>
       <c r="C15" t="n">
-        <v>19.70858516275472</v>
+        <v>24.00864010735575</v>
       </c>
       <c r="D15" t="n">
-        <v>29.02537087605695</v>
+        <v>32.6087499965578</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>2.066578917439536</v>
       </c>
       <c r="C16" t="n">
-        <v>17.77257868998001</v>
+        <v>24.79894700927443</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>30.58536797810513</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>17.47216389248049</v>
+        <v>26.9165768073348</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>25.97213551584937</v>
       </c>
     </row>
     <row r="18">
@@ -6602,10 +6602,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>2.140209995258047</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>28.89283493598363</v>
       </c>
       <c r="D18" t="n">
         <v>21.40209995258047</v>
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>2.407245370813179</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>30.69237847786803</v>
       </c>
       <c r="D19" t="n">
-        <v>16.85071759569225</v>
+        <v>13.23984953947248</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>13.4499435481813</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>96.16709636949629</v>
       </c>
       <c r="D20" t="n">
-        <v>10.08745766113597</v>
+        <v>4.03498306445439</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.513466675730777</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>87.34405010537029</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>7.513466675730777</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
